--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F342E7E-3167-4F23-9C59-21C10DF78695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E4DC57-B735-472B-B443-379BB2E00B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,6 +18,9 @@
     <sheet name="SkillTrigger" sheetId="4" r:id="rId3"/>
     <sheet name="TextData" sheetId="2" r:id="rId4"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="94">
   <si>
     <t>Id</t>
   </si>
@@ -102,9 +105,6 @@
     <t>Element5</t>
   </si>
   <si>
-    <t>Element6</t>
-  </si>
-  <si>
     <t>X</t>
   </si>
   <si>
@@ -159,39 +159,6 @@
     <t>Level</t>
   </si>
   <si>
-    <t>1010,1060</t>
-  </si>
-  <si>
-    <t>100110,100120</t>
-  </si>
-  <si>
-    <t>2010,2070</t>
-  </si>
-  <si>
-    <t>100210,100220</t>
-  </si>
-  <si>
-    <t>3010,3110</t>
-  </si>
-  <si>
-    <t>100310,100320</t>
-  </si>
-  <si>
-    <t>4010,4030</t>
-  </si>
-  <si>
-    <t>100410,100420</t>
-  </si>
-  <si>
-    <t>100510,100520</t>
-  </si>
-  <si>
-    <t>1010,5120,12040</t>
-  </si>
-  <si>
-    <t>100610,100620</t>
-  </si>
-  <si>
     <t>TriggerType1</t>
   </si>
   <si>
@@ -205,41 +172,20 @@
   </si>
   <si>
     <t>Feature</t>
-  </si>
-  <si>
-    <t>Alisha</t>
   </si>
   <si>
     <t>高い攻撃性能を持つアタッカー。
 全体的にステータスが高く、赤属性魔法を習得することでさらに攻撃性能を伸ばすことができる。</t>
   </si>
   <si>
-    <t>ソラ</t>
-  </si>
-  <si>
-    <t>Sora</t>
-  </si>
-  <si>
     <t>回避率を上げて攻撃を避けるアタッカー。
 打たれ弱いがSPDが高く、回避率をアップする雷属性魔法を習得しやすい。</t>
   </si>
   <si>
-    <t>リジェ</t>
-  </si>
-  <si>
-    <t>Ligier</t>
-  </si>
-  <si>
     <t>相手の攻撃を跳ね返すディフェンダー。
 受けた攻撃ダメージの一部を跳ね返す「カウンターオーラ」を使うことができる。</t>
   </si>
   <si>
-    <t>ミシェル</t>
-  </si>
-  <si>
-    <t>Michelle</t>
-  </si>
-  <si>
     <t>回復に特化したヒーラー。
 全体的にステータスが低いが、味方のHpを回復する「ヒーリング」を使うことができる。</t>
   </si>
@@ -247,45 +193,155 @@
     <t>シイナ</t>
   </si>
   <si>
-    <t>Shiina</t>
-  </si>
-  <si>
     <t>相手の攻撃性能を下げるジャマー。
 「シェイディークラウド」で味方が受けるダメージを抑えたり、「毒」でスリップダメージを与える魔法を使うことができる。</t>
   </si>
   <si>
-    <t>ルネ</t>
-  </si>
-  <si>
-    <t>Renee</t>
-  </si>
-  <si>
     <t>味方のCTを短縮することができるサポーター。
 CT（魔法を再使用するまでのターン数）を短縮しパーティ全体の補助をすることができる。</t>
   </si>
   <si>
+    <t>0007</t>
+  </si>
+  <si>
+    <t>0008</t>
+  </si>
+  <si>
+    <t>0009</t>
+  </si>
+  <si>
+    <t>0010</t>
+  </si>
+  <si>
+    <t>0011</t>
+  </si>
+  <si>
+    <t>11,21,31,1010,1060,100110,100120</t>
+  </si>
+  <si>
+    <t>11,21,31,2010,2070,100210,100220</t>
+  </si>
+  <si>
+    <t>11,21,31,3010,3020,100310,100320</t>
+  </si>
+  <si>
+    <t>11,21,31,4010,4030,100410,100420</t>
+  </si>
+  <si>
+    <t>11,21,31,5010,5070,100510,100520</t>
+  </si>
+  <si>
+    <t>11,21,31,1010,1030,100610,100620</t>
+  </si>
+  <si>
+    <t>11,21,31,2010,2040,100710,100720</t>
+  </si>
+  <si>
+    <t>11,21,31,3010,3070,100810,100820</t>
+  </si>
+  <si>
+    <t>11,21,31,1010,1050,100910,100920</t>
+  </si>
+  <si>
+    <t>11,21,31,2010,2030,101010,101020</t>
+  </si>
+  <si>
+    <t>11,21,31,3010,3050,101110,101120</t>
+  </si>
+  <si>
     <t>ミカ</t>
-    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>【煉獄棘姫】</t>
+  </si>
+  <si>
+    <t>エリザベート</t>
+  </si>
+  <si>
+    <t>【ChargeCommander】</t>
+  </si>
+  <si>
+    <t>アリエス</t>
+  </si>
+  <si>
+    <t>【怠惰な守護少女】</t>
+  </si>
+  <si>
+    <t>【イノセント・リメディ】</t>
+  </si>
+  <si>
+    <t>レダ</t>
+  </si>
+  <si>
+    <t>【Self-sacrifice】</t>
+  </si>
+  <si>
+    <t>リシェリ</t>
+  </si>
+  <si>
+    <t>【Faked-Magician】</t>
+  </si>
+  <si>
+    <t>ユニ</t>
+  </si>
+  <si>
+    <t>【奇跡の乙女】</t>
+  </si>
+  <si>
+    <t>味方の行動待機時間を短くするサポーター。
+「アウトオブオーダー」で両隣に配置した味方の行動待機時間を短縮したり、味方のATK・DEFをアップするバフ魔法を使うことができる。</t>
+  </si>
+  <si>
+    <t>マリーベル</t>
+  </si>
+  <si>
+    <t>【唯心の在処】</t>
+  </si>
+  <si>
+    <t>味方の攻撃を代わりに受け持つディフェンダー。
+「アクアミラージュ」で一定回数攻撃を無効にしたり、味方の攻撃を代わりに受けパーティの生存率を上げることができる。</t>
+  </si>
+  <si>
+    <t>ナツキ</t>
+  </si>
+  <si>
+    <t>【黄昏ニヒリスト】</t>
+  </si>
+  <si>
+    <t>攻撃回数の多い攻撃性能を持つアタッカー。
+Hpが低いがATKが高く、攻撃回数の多い「フレイムレイン」を使うことができる。</t>
+  </si>
+  <si>
+    <t>メリアドール</t>
+  </si>
+  <si>
+    <t>【怨嗟の鎖】</t>
+  </si>
+  <si>
+    <t>SPD性能に特化したジャマー。
+「ショックインパルス」で相手を行動不可にすることができる。</t>
+  </si>
+  <si>
+    <t>セリナ</t>
+  </si>
+  <si>
+    <t>【氷雪の勿忘草】</t>
+  </si>
+  <si>
+    <t>凍結攻撃を主体とするアタッカー。
+「ディープフリーズ」で攻撃時に一定量のダメージを受ける「凍結」状態にし、凍結効果をさらにアップすることで自滅に追い込むことができる。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -318,7 +374,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -326,9 +382,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -346,6 +399,161 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Actors"/>
+      <sheetName val="Learning"/>
+      <sheetName val="SkillTrigger"/>
+      <sheetName val="TextData"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="1">
+          <cell r="A1" t="str">
+            <v>Id</v>
+          </cell>
+          <cell r="B1" t="str">
+            <v>Text</v>
+          </cell>
+          <cell r="C1" t="str">
+            <v>SubName</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="A2">
+            <v>1</v>
+          </cell>
+          <cell r="B2" t="str">
+            <v>ミカ</v>
+          </cell>
+          <cell r="C2" t="str">
+            <v>【煉獄棘姫】</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>2</v>
+          </cell>
+          <cell r="B3" t="str">
+            <v>エリザベート</v>
+          </cell>
+          <cell r="C3" t="str">
+            <v>【ChargeCommander】</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>3</v>
+          </cell>
+          <cell r="B4" t="str">
+            <v>アリエス</v>
+          </cell>
+          <cell r="C4" t="str">
+            <v>【怠惰な守護少女】</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>4</v>
+          </cell>
+          <cell r="B5" t="str">
+            <v>シイナ</v>
+          </cell>
+          <cell r="C5" t="str">
+            <v>【イノセント・リメディ】</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>5</v>
+          </cell>
+          <cell r="B6" t="str">
+            <v>レダ</v>
+          </cell>
+          <cell r="C6" t="str">
+            <v>【Self-sacrifice】</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>6</v>
+          </cell>
+          <cell r="B7" t="str">
+            <v>リシェリ</v>
+          </cell>
+          <cell r="C7" t="str">
+            <v>【Faked-Magician】</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>7</v>
+          </cell>
+          <cell r="B8" t="str">
+            <v>ユニ</v>
+          </cell>
+          <cell r="C8" t="str">
+            <v>【奇跡の乙女】</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>8</v>
+          </cell>
+          <cell r="B9" t="str">
+            <v>マリーベル</v>
+          </cell>
+          <cell r="C9" t="str">
+            <v>【唯心の在処】</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>9</v>
+          </cell>
+          <cell r="B10" t="str">
+            <v>ナツキ</v>
+          </cell>
+          <cell r="C10" t="str">
+            <v>【黄昏ニヒリスト】</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>10</v>
+          </cell>
+          <cell r="B11" t="str">
+            <v>メリアドール</v>
+          </cell>
+          <cell r="C11" t="str">
+            <v>【怨嗟の鎖】</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>11</v>
+          </cell>
+          <cell r="B12" t="str">
+            <v>セリナ</v>
+          </cell>
+          <cell r="C12" t="str">
+            <v>【氷雪の勿忘草】</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -635,7 +843,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG7"/>
+  <dimension ref="A1:AF12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="11.6328125" customWidth="1"/>
@@ -650,7 +858,7 @@
     <col min="13" max="13" width="7.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -747,33 +955,30 @@
       <c r="AF1" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" t="s">
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B2,[1]TextData!A:A))</f>
+        <v>ミカ</v>
+      </c>
+      <c r="D2" t="str">
+        <f>INDEX([1]TextData!C:C,MATCH(B2,[1]TextData!A:A))</f>
+        <v>【煉獄棘姫】</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="str">
-        <f>INDEX(TextData!B:B,MATCH(B2,TextData!A:A))</f>
-        <v>ミカ</v>
-      </c>
-      <c r="D2" t="str">
-        <f>INDEX(TextData!C:C,MATCH(B2,TextData!A:A))</f>
-        <v>Alisha</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="G2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>99</v>
@@ -782,67 +987,67 @@
         <v>39</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L2">
         <v>15</v>
       </c>
       <c r="M2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="O2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>60</v>
       </c>
       <c r="Q2">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="R2">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="S2">
         <v>1</v>
       </c>
       <c r="T2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X2">
-        <v>2</v>
+        <v>-10</v>
       </c>
       <c r="Y2">
-        <v>-88</v>
+        <v>-54</v>
       </c>
       <c r="Z2">
-        <v>24</v>
+        <v>0.75</v>
       </c>
       <c r="AA2">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AB2">
         <v>0</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
@@ -850,11 +1055,8 @@
       <c r="AF2">
         <v>0</v>
       </c>
-      <c r="AG2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -862,21 +1064,21 @@
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <f>INDEX(TextData!B:B,MATCH(B3,TextData!A:A))</f>
-        <v>ソラ</v>
+        <f>INDEX([1]TextData!B:B,MATCH(B3,[1]TextData!A:A))</f>
+        <v>エリザベート</v>
       </c>
       <c r="D3" t="str">
-        <f>INDEX(TextData!C:C,MATCH(B3,TextData!A:A))</f>
-        <v>Sora</v>
+        <f>INDEX([1]TextData!C:C,MATCH(B3,[1]TextData!A:A))</f>
+        <v>【ChargeCommander】</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>99</v>
@@ -885,67 +1087,67 @@
         <v>29</v>
       </c>
       <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>21</v>
+      </c>
+      <c r="L3">
         <v>5</v>
       </c>
-      <c r="K3">
-        <v>25</v>
-      </c>
-      <c r="L3">
-        <v>10</v>
-      </c>
       <c r="M3">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="N3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="O3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>40</v>
       </c>
       <c r="Q3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R3">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="S3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T3">
         <v>1</v>
       </c>
       <c r="U3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V3">
         <v>7</v>
       </c>
       <c r="W3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X3">
-        <v>3</v>
+        <v>-20</v>
       </c>
       <c r="Y3">
-        <v>-20</v>
+        <v>-52</v>
       </c>
       <c r="Z3">
-        <v>-52</v>
+        <v>0.71</v>
       </c>
       <c r="AA3">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AB3">
         <v>0</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
@@ -953,11 +1155,8 @@
       <c r="AF3">
         <v>0</v>
       </c>
-      <c r="AG3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -965,57 +1164,57 @@
         <v>3</v>
       </c>
       <c r="C4" t="str">
-        <f>INDEX(TextData!B:B,MATCH(B4,TextData!A:A))</f>
-        <v>リジェ</v>
+        <f>INDEX([1]TextData!B:B,MATCH(B4,[1]TextData!A:A))</f>
+        <v>アリエス</v>
       </c>
       <c r="D4" t="str">
-        <f>INDEX(TextData!C:C,MATCH(B4,TextData!A:A))</f>
-        <v>Ligier</v>
+        <f>INDEX([1]TextData!C:C,MATCH(B4,[1]TextData!A:A))</f>
+        <v>【怠惰な守護少女】</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <v>99</v>
       </c>
       <c r="I4">
+        <v>35</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>17</v>
+      </c>
+      <c r="L4">
+        <v>17</v>
+      </c>
+      <c r="M4">
+        <v>9</v>
+      </c>
+      <c r="N4">
+        <v>85</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
         <v>25</v>
       </c>
-      <c r="J4">
-        <v>5</v>
-      </c>
-      <c r="K4">
-        <v>18</v>
-      </c>
-      <c r="L4">
-        <v>8</v>
-      </c>
-      <c r="M4">
-        <v>32</v>
-      </c>
-      <c r="N4">
-        <v>65</v>
-      </c>
-      <c r="O4">
-        <v>100</v>
-      </c>
-      <c r="P4">
-        <v>45</v>
-      </c>
       <c r="Q4">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="R4">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="S4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T4">
         <v>6</v>
@@ -1027,28 +1226,28 @@
         <v>2</v>
       </c>
       <c r="W4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>-10</v>
       </c>
       <c r="Y4">
-        <v>-96</v>
+        <v>-64</v>
       </c>
       <c r="Z4">
-        <v>-64</v>
+        <v>0.82</v>
       </c>
       <c r="AA4">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AB4">
         <v>0</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
@@ -1056,11 +1255,8 @@
       <c r="AF4">
         <v>0</v>
       </c>
-      <c r="AG4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1068,63 +1264,63 @@
         <v>4</v>
       </c>
       <c r="C5" t="str">
-        <f>INDEX(TextData!B:B,MATCH(B5,TextData!A:A))</f>
-        <v>ミシェル</v>
+        <f>INDEX([1]TextData!B:B,MATCH(B5,[1]TextData!A:A))</f>
+        <v>シイナ</v>
       </c>
       <c r="D5" t="str">
-        <f>INDEX(TextData!C:C,MATCH(B5,TextData!A:A))</f>
-        <v>Michelle</v>
+        <f>INDEX([1]TextData!C:C,MATCH(B5,[1]TextData!A:A))</f>
+        <v>【イノセント・リメディ】</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <v>99</v>
       </c>
       <c r="I5">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L5">
         <v>7</v>
       </c>
       <c r="M5">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="N5">
         <v>85</v>
       </c>
       <c r="O5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P5">
         <v>35</v>
       </c>
       <c r="Q5">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="R5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="S5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="V5">
         <v>1</v>
@@ -1133,25 +1329,25 @@
         <v>7</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>-4</v>
       </c>
       <c r="Y5">
-        <v>-4</v>
+        <v>-68</v>
       </c>
       <c r="Z5">
-        <v>-68</v>
+        <v>0.8</v>
       </c>
       <c r="AA5">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AB5">
         <v>0</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
@@ -1159,11 +1355,8 @@
       <c r="AF5">
         <v>0</v>
       </c>
-      <c r="AG5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1171,18 +1364,18 @@
         <v>5</v>
       </c>
       <c r="C6" t="str">
-        <f>INDEX(TextData!B:B,MATCH(B6,TextData!A:A))</f>
-        <v>シイナ</v>
+        <f>INDEX([1]TextData!B:B,MATCH(B6,[1]TextData!A:A))</f>
+        <v>レダ</v>
       </c>
       <c r="D6" t="str">
-        <f>INDEX(TextData!C:C,MATCH(B6,TextData!A:A))</f>
-        <v>Shiina</v>
+        <f>INDEX([1]TextData!C:C,MATCH(B6,[1]TextData!A:A))</f>
+        <v>【Self-sacrifice】</v>
       </c>
       <c r="E6">
         <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1191,70 +1384,70 @@
         <v>99</v>
       </c>
       <c r="I6">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="N6">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="O6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="Q6">
+        <v>40</v>
+      </c>
+      <c r="R6">
         <v>45</v>
       </c>
-      <c r="R6">
-        <v>30</v>
-      </c>
       <c r="S6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U6">
         <v>2</v>
       </c>
       <c r="V6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W6">
         <v>1</v>
       </c>
       <c r="X6">
-        <v>3</v>
+        <v>-8</v>
       </c>
       <c r="Y6">
-        <v>-8</v>
+        <v>-44</v>
       </c>
       <c r="Z6">
-        <v>-44</v>
+        <v>0.82</v>
       </c>
       <c r="AA6">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AB6">
         <v>0</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE6">
         <v>0</v>
@@ -1262,11 +1455,8 @@
       <c r="AF6">
         <v>0</v>
       </c>
-      <c r="AG6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1274,21 +1464,21 @@
         <v>6</v>
       </c>
       <c r="C7" t="str">
-        <f>INDEX(TextData!B:B,MATCH(B7,TextData!A:A))</f>
-        <v>ルネ</v>
+        <f>INDEX([1]TextData!B:B,MATCH(B7,[1]TextData!A:A))</f>
+        <v>リシェリ</v>
       </c>
       <c r="D7" t="str">
-        <f>INDEX(TextData!C:C,MATCH(B7,TextData!A:A))</f>
-        <v>Renee</v>
+        <f>INDEX([1]TextData!C:C,MATCH(B7,[1]TextData!A:A))</f>
+        <v>【Faked-Magician】</v>
       </c>
       <c r="E7">
         <v>6</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <v>99</v>
@@ -1297,80 +1487,577 @@
         <v>30</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K7">
         <v>20</v>
       </c>
       <c r="L7">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="M7">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N7">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="O7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P7">
         <v>50</v>
       </c>
       <c r="Q7">
+        <v>50</v>
+      </c>
+      <c r="R7">
+        <v>50</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
+      <c r="T7">
+        <v>6</v>
+      </c>
+      <c r="U7">
+        <v>2</v>
+      </c>
+      <c r="V7">
+        <v>6</v>
+      </c>
+      <c r="W7">
+        <v>3</v>
+      </c>
+      <c r="X7">
+        <v>48</v>
+      </c>
+      <c r="Y7">
+        <v>-68</v>
+      </c>
+      <c r="Z7">
+        <v>0.76</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>1</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B8,[1]TextData!A:A))</f>
+        <v>ユニ</v>
+      </c>
+      <c r="D8" t="str">
+        <f>INDEX([1]TextData!C:C,MATCH(B8,[1]TextData!A:A))</f>
+        <v>【奇跡の乙女】</v>
+      </c>
+      <c r="E8">
+        <v>7</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>99</v>
+      </c>
+      <c r="I8">
+        <v>40</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>22</v>
+      </c>
+      <c r="L8">
+        <v>18</v>
+      </c>
+      <c r="M8">
+        <v>16</v>
+      </c>
+      <c r="N8">
+        <v>65</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>45</v>
+      </c>
+      <c r="Q8">
+        <v>40</v>
+      </c>
+      <c r="R8">
         <v>30</v>
       </c>
-      <c r="R7">
+      <c r="S8">
+        <v>4</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>4</v>
+      </c>
+      <c r="V8">
+        <v>3</v>
+      </c>
+      <c r="W8">
+        <v>4</v>
+      </c>
+      <c r="X8">
+        <v>-20</v>
+      </c>
+      <c r="Y8">
+        <v>-60</v>
+      </c>
+      <c r="Z8">
+        <v>0.79</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B9,[1]TextData!A:A))</f>
+        <v>マリーベル</v>
+      </c>
+      <c r="D9" t="str">
+        <f>INDEX([1]TextData!C:C,MATCH(B9,[1]TextData!A:A))</f>
+        <v>【唯心の在処】</v>
+      </c>
+      <c r="E9">
+        <v>8</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>99</v>
+      </c>
+      <c r="I9">
+        <v>37</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>15</v>
+      </c>
+      <c r="L9">
+        <v>21</v>
+      </c>
+      <c r="M9">
+        <v>16</v>
+      </c>
+      <c r="N9">
+        <v>80</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>40</v>
+      </c>
+      <c r="Q9">
+        <v>60</v>
+      </c>
+      <c r="R9">
+        <v>35</v>
+      </c>
+      <c r="S9">
+        <v>6</v>
+      </c>
+      <c r="T9">
+        <v>2</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9">
+        <v>5</v>
+      </c>
+      <c r="W9">
+        <v>4</v>
+      </c>
+      <c r="X9">
+        <v>-52</v>
+      </c>
+      <c r="Y9">
+        <v>-52</v>
+      </c>
+      <c r="Z9">
+        <v>0.8</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>1</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B10,[1]TextData!A:A))</f>
+        <v>ナツキ</v>
+      </c>
+      <c r="D10" t="str">
+        <f>INDEX([1]TextData!C:C,MATCH(B10,[1]TextData!A:A))</f>
+        <v>【黄昏ニヒリスト】</v>
+      </c>
+      <c r="E10">
+        <v>9</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>99</v>
+      </c>
+      <c r="I10">
+        <v>34</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>25</v>
+      </c>
+      <c r="L10">
+        <v>12</v>
+      </c>
+      <c r="M10">
+        <v>24</v>
+      </c>
+      <c r="N10">
+        <v>25</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>65</v>
+      </c>
+      <c r="Q10">
         <v>30</v>
       </c>
-      <c r="S7">
+      <c r="R10">
+        <v>50</v>
+      </c>
+      <c r="S10">
+        <v>1</v>
+      </c>
+      <c r="T10">
+        <v>4</v>
+      </c>
+      <c r="U10">
+        <v>4</v>
+      </c>
+      <c r="V10">
+        <v>7</v>
+      </c>
+      <c r="W10">
+        <v>2</v>
+      </c>
+      <c r="X10">
+        <v>-16</v>
+      </c>
+      <c r="Y10">
+        <v>-52</v>
+      </c>
+      <c r="Z10">
+        <v>0.75</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>1</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B11,[1]TextData!A:A))</f>
+        <v>メリアドール</v>
+      </c>
+      <c r="D11" t="str">
+        <f>INDEX([1]TextData!C:C,MATCH(B11,[1]TextData!A:A))</f>
+        <v>【怨嗟の鎖】</v>
+      </c>
+      <c r="E11">
+        <v>10</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>99</v>
+      </c>
+      <c r="I11">
+        <v>30</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>17</v>
+      </c>
+      <c r="L11">
+        <v>7</v>
+      </c>
+      <c r="M11">
+        <v>31</v>
+      </c>
+      <c r="N11">
+        <v>45</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>30</v>
+      </c>
+      <c r="Q11">
+        <v>20</v>
+      </c>
+      <c r="R11">
+        <v>75</v>
+      </c>
+      <c r="S11">
+        <v>4</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11">
+        <v>6</v>
+      </c>
+      <c r="V11">
+        <v>5</v>
+      </c>
+      <c r="W11">
+        <v>2</v>
+      </c>
+      <c r="X11">
+        <v>12</v>
+      </c>
+      <c r="Y11">
+        <v>-64</v>
+      </c>
+      <c r="Z11">
+        <v>0.77</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>1</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B12,[1]TextData!A:A))</f>
+        <v>セリナ</v>
+      </c>
+      <c r="D12" t="str">
+        <f>INDEX([1]TextData!C:C,MATCH(B12,[1]TextData!A:A))</f>
+        <v>【氷雪の勿忘草】</v>
+      </c>
+      <c r="E12">
+        <v>11</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>99</v>
+      </c>
+      <c r="I12">
+        <v>33</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>21</v>
+      </c>
+      <c r="L12">
+        <v>16</v>
+      </c>
+      <c r="M12">
+        <v>18</v>
+      </c>
+      <c r="N12">
+        <v>65</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>40</v>
+      </c>
+      <c r="Q12">
+        <v>25</v>
+      </c>
+      <c r="R12">
+        <v>30</v>
+      </c>
+      <c r="S12">
+        <v>6</v>
+      </c>
+      <c r="T12">
+        <v>6</v>
+      </c>
+      <c r="U12">
+        <v>1</v>
+      </c>
+      <c r="V12">
         <v>3</v>
       </c>
-      <c r="T7">
-        <v>3</v>
-      </c>
-      <c r="U7">
-        <v>3</v>
-      </c>
-      <c r="V7">
-        <v>4</v>
-      </c>
-      <c r="W7">
-        <v>4</v>
-      </c>
-      <c r="X7">
-        <v>1</v>
-      </c>
-      <c r="Y7">
-        <v>48</v>
-      </c>
-      <c r="Z7">
-        <v>-68</v>
-      </c>
-      <c r="AA7">
-        <v>0.75</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>1</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
-      <c r="AG7">
+      <c r="W12">
+        <v>2</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>-54</v>
+      </c>
+      <c r="Z12">
+        <v>0.87</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>1</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -1378,7 +2065,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="44.26953125" style="2" customWidth="1"/>
@@ -1386,21 +2073,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" t="s">
         <v>39</v>
-      </c>
-      <c r="C1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>41</v>
+      <c r="B2" t="s">
+        <v>57</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1408,168 +2095,174 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>11060</v>
+      </c>
+      <c r="C3">
         <v>11</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>11</v>
-      </c>
-      <c r="B4" s="2">
-        <v>11060</v>
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>401060</v>
       </c>
       <c r="C4">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2">
-        <v>401060</v>
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>1020</v>
       </c>
       <c r="C5">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>11</v>
-      </c>
-      <c r="B6" s="2">
-        <v>1020</v>
-      </c>
-      <c r="C6">
-        <v>41</v>
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>43</v>
+      <c r="B7">
+        <v>12080</v>
+      </c>
+      <c r="C7">
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>12</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>44</v>
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <v>12040</v>
+      </c>
+      <c r="C8">
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>12</v>
-      </c>
-      <c r="B9" s="2">
-        <v>12080</v>
+        <v>2</v>
+      </c>
+      <c r="B9">
+        <v>2060</v>
       </c>
       <c r="C9">
-        <v>11</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>12</v>
-      </c>
-      <c r="B10" s="2">
-        <v>12040</v>
-      </c>
-      <c r="C10">
-        <v>26</v>
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>12</v>
-      </c>
-      <c r="B11" s="2">
-        <v>2060</v>
+        <v>3</v>
+      </c>
+      <c r="B11">
+        <v>13080</v>
       </c>
       <c r="C11">
-        <v>41</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>3</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>45</v>
+      <c r="B12">
+        <v>403010</v>
+      </c>
+      <c r="C12">
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>13</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>46</v>
+        <v>3</v>
+      </c>
+      <c r="B13">
+        <v>3040</v>
+      </c>
+      <c r="C13">
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2">
-        <v>13080</v>
-      </c>
-      <c r="C14">
-        <v>11</v>
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2">
-        <v>403010</v>
+        <v>4</v>
+      </c>
+      <c r="B15">
+        <v>14080</v>
       </c>
       <c r="C15">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>13</v>
-      </c>
-      <c r="B16" s="2">
-        <v>3040</v>
+        <v>4</v>
+      </c>
+      <c r="B16">
+        <v>404030</v>
       </c>
       <c r="C16">
-        <v>41</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>4</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>47</v>
+      <c r="B17">
+        <v>4060</v>
+      </c>
+      <c r="C17">
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>14</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>48</v>
+        <v>5</v>
+      </c>
+      <c r="B18" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>14</v>
-      </c>
-      <c r="B19" s="2">
-        <v>14080</v>
+        <v>5</v>
+      </c>
+      <c r="B19">
+        <v>15090</v>
       </c>
       <c r="C19">
         <v>11</v>
@@ -1577,10 +2270,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>14</v>
-      </c>
-      <c r="B20" s="2">
-        <v>404030</v>
+        <v>5</v>
+      </c>
+      <c r="B20">
+        <v>405070</v>
       </c>
       <c r="C20">
         <v>26</v>
@@ -1588,10 +2281,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>14</v>
-      </c>
-      <c r="B21" s="2">
-        <v>4060</v>
+        <v>5</v>
+      </c>
+      <c r="B21">
+        <v>5040</v>
       </c>
       <c r="C21">
         <v>41</v>
@@ -1599,104 +2292,252 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>5</v>
-      </c>
-      <c r="B22" s="2">
-        <v>5010</v>
+        <v>6</v>
+      </c>
+      <c r="B22" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>15</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>49</v>
+        <v>6</v>
+      </c>
+      <c r="B23">
+        <v>11040</v>
+      </c>
+      <c r="C23">
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>15</v>
-      </c>
-      <c r="B24" s="2">
-        <v>15090</v>
+        <v>6</v>
+      </c>
+      <c r="B24">
+        <v>401030</v>
       </c>
       <c r="C24">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>15</v>
-      </c>
-      <c r="B25" s="2">
-        <v>405070</v>
+        <v>6</v>
+      </c>
+      <c r="B25">
+        <v>1070</v>
       </c>
       <c r="C25">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>15</v>
-      </c>
-      <c r="B26" s="2">
-        <v>5040</v>
-      </c>
-      <c r="C26">
-        <v>41</v>
+        <v>7</v>
+      </c>
+      <c r="B26" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>6</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>50</v>
+        <v>7</v>
+      </c>
+      <c r="B27">
+        <v>12090</v>
+      </c>
+      <c r="C27">
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>16</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>51</v>
+        <v>7</v>
+      </c>
+      <c r="B28">
+        <v>412090</v>
+      </c>
+      <c r="C28">
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>16</v>
-      </c>
-      <c r="B29" s="2">
-        <v>11040</v>
+        <v>7</v>
+      </c>
+      <c r="B29">
+        <v>2050</v>
       </c>
       <c r="C29">
-        <v>11</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>16</v>
-      </c>
-      <c r="B30" s="2">
-        <v>401030</v>
-      </c>
-      <c r="C30">
-        <v>26</v>
+        <v>8</v>
+      </c>
+      <c r="B30" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>16</v>
-      </c>
-      <c r="B31" s="2">
-        <v>1070</v>
+        <v>8</v>
+      </c>
+      <c r="B31">
+        <v>13060</v>
       </c>
       <c r="C31">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>8</v>
+      </c>
+      <c r="B32">
+        <v>403070</v>
+      </c>
+      <c r="C32">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>8</v>
+      </c>
+      <c r="B33">
+        <v>3060</v>
+      </c>
+      <c r="C33">
         <v>41</v>
       </c>
     </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>9</v>
+      </c>
+      <c r="B34" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>9</v>
+      </c>
+      <c r="B35">
+        <v>11070</v>
+      </c>
+      <c r="C35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>9</v>
+      </c>
+      <c r="B36">
+        <v>401050</v>
+      </c>
+      <c r="C36">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>9</v>
+      </c>
+      <c r="B37">
+        <v>1080</v>
+      </c>
+      <c r="C37">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>10</v>
+      </c>
+      <c r="B38" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>10</v>
+      </c>
+      <c r="B39">
+        <v>12010</v>
+      </c>
+      <c r="C39">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>10</v>
+      </c>
+      <c r="B40">
+        <v>402030</v>
+      </c>
+      <c r="C40">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>10</v>
+      </c>
+      <c r="B41">
+        <v>2080</v>
+      </c>
+      <c r="C41">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>11</v>
+      </c>
+      <c r="B42" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>11</v>
+      </c>
+      <c r="B43">
+        <v>13090</v>
+      </c>
+      <c r="C43">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>11</v>
+      </c>
+      <c r="B44">
+        <v>403050</v>
+      </c>
+      <c r="C44">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>11</v>
+      </c>
+      <c r="B45">
+        <v>3080</v>
+      </c>
+      <c r="C45">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1711,16 +2552,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" t="s">
         <v>38</v>
       </c>
-      <c r="B1" t="s">
-        <v>39</v>
-      </c>
       <c r="C1" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -2564,14 +3405,14 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="20.54296875" customWidth="1"/>
@@ -2583,27 +3424,27 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C1" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D1" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="39" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>74</v>
+      <c r="B2" t="s">
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="39" x14ac:dyDescent="0.2">
@@ -2611,13 +3452,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="39" x14ac:dyDescent="0.2">
@@ -2625,13 +3466,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="39" x14ac:dyDescent="0.2">
@@ -2639,13 +3480,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="52" x14ac:dyDescent="0.2">
@@ -2653,13 +3494,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="39" x14ac:dyDescent="0.2">
@@ -2667,17 +3508,87 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>73</v>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="52" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="52" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="39" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="39" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="52" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E4DC57-B735-472B-B443-379BB2E00B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{599B7C2E-64CD-4BD0-BC13-E05E41B2335B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -2544,7 +2544,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D112"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="4" width="12.90625" customWidth="1"/>
@@ -3401,6 +3401,720 @@
         <v>0</v>
       </c>
       <c r="D61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>7</v>
+      </c>
+      <c r="B62">
+        <v>2040</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>7</v>
+      </c>
+      <c r="B63">
+        <v>100720</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>7</v>
+      </c>
+      <c r="B64">
+        <v>2010</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>7</v>
+      </c>
+      <c r="B65">
+        <v>100710</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>7</v>
+      </c>
+      <c r="B66">
+        <v>0</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>7</v>
+      </c>
+      <c r="B67">
+        <v>0</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>7</v>
+      </c>
+      <c r="B68">
+        <v>0</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>7</v>
+      </c>
+      <c r="B69">
+        <v>0</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>7</v>
+      </c>
+      <c r="B70">
+        <v>0</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <v>7</v>
+      </c>
+      <c r="B71">
+        <v>0</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <v>8</v>
+      </c>
+      <c r="B72">
+        <v>100820</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <v>8</v>
+      </c>
+      <c r="B73">
+        <v>3070</v>
+      </c>
+      <c r="C73">
+        <v>14114</v>
+      </c>
+      <c r="D73">
+        <v>9120</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>8</v>
+      </c>
+      <c r="B74">
+        <v>3010</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <v>8</v>
+      </c>
+      <c r="B75">
+        <v>100810</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A76">
+        <v>8</v>
+      </c>
+      <c r="B76">
+        <v>0</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A77">
+        <v>8</v>
+      </c>
+      <c r="B77">
+        <v>0</v>
+      </c>
+      <c r="C77">
+        <v>0</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <v>8</v>
+      </c>
+      <c r="B78">
+        <v>0</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
+      <c r="D78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <v>8</v>
+      </c>
+      <c r="B79">
+        <v>0</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
+      <c r="D79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A80">
+        <v>8</v>
+      </c>
+      <c r="B80">
+        <v>0</v>
+      </c>
+      <c r="C80">
+        <v>0</v>
+      </c>
+      <c r="D80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A81">
+        <v>8</v>
+      </c>
+      <c r="B81">
+        <v>0</v>
+      </c>
+      <c r="C81">
+        <v>0</v>
+      </c>
+      <c r="D81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A82">
+        <v>9</v>
+      </c>
+      <c r="B82">
+        <v>100920</v>
+      </c>
+      <c r="C82">
+        <v>0</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A83">
+        <v>9</v>
+      </c>
+      <c r="B83">
+        <v>1050</v>
+      </c>
+      <c r="C83">
+        <v>0</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A84">
+        <v>9</v>
+      </c>
+      <c r="B84">
+        <v>1010</v>
+      </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A85">
+        <v>9</v>
+      </c>
+      <c r="B85">
+        <v>100910</v>
+      </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A86">
+        <v>9</v>
+      </c>
+      <c r="B86">
+        <v>0</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A87">
+        <v>9</v>
+      </c>
+      <c r="B87">
+        <v>0</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+      <c r="D87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A88">
+        <v>9</v>
+      </c>
+      <c r="B88">
+        <v>0</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A89">
+        <v>9</v>
+      </c>
+      <c r="B89">
+        <v>0</v>
+      </c>
+      <c r="C89">
+        <v>0</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A90">
+        <v>9</v>
+      </c>
+      <c r="B90">
+        <v>0</v>
+      </c>
+      <c r="C90">
+        <v>0</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A91">
+        <v>9</v>
+      </c>
+      <c r="B91">
+        <v>0</v>
+      </c>
+      <c r="C91">
+        <v>0</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A92">
+        <v>10</v>
+      </c>
+      <c r="B92">
+        <v>2030</v>
+      </c>
+      <c r="C92">
+        <v>0</v>
+      </c>
+      <c r="D92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A93">
+        <v>10</v>
+      </c>
+      <c r="B93">
+        <v>101020</v>
+      </c>
+      <c r="C93">
+        <v>0</v>
+      </c>
+      <c r="D93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A94">
+        <v>10</v>
+      </c>
+      <c r="B94">
+        <v>2010</v>
+      </c>
+      <c r="C94">
+        <v>0</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A95">
+        <v>10</v>
+      </c>
+      <c r="B95">
+        <v>101010</v>
+      </c>
+      <c r="C95">
+        <v>0</v>
+      </c>
+      <c r="D95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A96">
+        <v>10</v>
+      </c>
+      <c r="B96">
+        <v>0</v>
+      </c>
+      <c r="C96">
+        <v>0</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A97">
+        <v>10</v>
+      </c>
+      <c r="B97">
+        <v>0</v>
+      </c>
+      <c r="C97">
+        <v>0</v>
+      </c>
+      <c r="D97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A98">
+        <v>10</v>
+      </c>
+      <c r="B98">
+        <v>0</v>
+      </c>
+      <c r="C98">
+        <v>0</v>
+      </c>
+      <c r="D98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A99">
+        <v>10</v>
+      </c>
+      <c r="B99">
+        <v>0</v>
+      </c>
+      <c r="C99">
+        <v>0</v>
+      </c>
+      <c r="D99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A100">
+        <v>10</v>
+      </c>
+      <c r="B100">
+        <v>0</v>
+      </c>
+      <c r="C100">
+        <v>0</v>
+      </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A101">
+        <v>10</v>
+      </c>
+      <c r="B101">
+        <v>0</v>
+      </c>
+      <c r="C101">
+        <v>0</v>
+      </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A102">
+        <v>11</v>
+      </c>
+      <c r="B102">
+        <v>3050</v>
+      </c>
+      <c r="C102">
+        <v>6712</v>
+      </c>
+      <c r="D102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A103">
+        <v>11</v>
+      </c>
+      <c r="B103">
+        <v>101120</v>
+      </c>
+      <c r="C103">
+        <v>0</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A104">
+        <v>11</v>
+      </c>
+      <c r="B104">
+        <v>3010</v>
+      </c>
+      <c r="C104">
+        <v>0</v>
+      </c>
+      <c r="D104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A105">
+        <v>11</v>
+      </c>
+      <c r="B105">
+        <v>101110</v>
+      </c>
+      <c r="C105">
+        <v>0</v>
+      </c>
+      <c r="D105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A106">
+        <v>11</v>
+      </c>
+      <c r="B106">
+        <v>0</v>
+      </c>
+      <c r="C106">
+        <v>0</v>
+      </c>
+      <c r="D106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A107">
+        <v>11</v>
+      </c>
+      <c r="B107">
+        <v>0</v>
+      </c>
+      <c r="C107">
+        <v>0</v>
+      </c>
+      <c r="D107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A108">
+        <v>11</v>
+      </c>
+      <c r="B108">
+        <v>0</v>
+      </c>
+      <c r="C108">
+        <v>0</v>
+      </c>
+      <c r="D108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A109">
+        <v>11</v>
+      </c>
+      <c r="B109">
+        <v>0</v>
+      </c>
+      <c r="C109">
+        <v>0</v>
+      </c>
+      <c r="D109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A110">
+        <v>11</v>
+      </c>
+      <c r="B110">
+        <v>0</v>
+      </c>
+      <c r="C110">
+        <v>0</v>
+      </c>
+      <c r="D110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A111">
+        <v>11</v>
+      </c>
+      <c r="B111">
+        <v>0</v>
+      </c>
+      <c r="C111">
+        <v>0</v>
+      </c>
+      <c r="D111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A112">
+        <v>11</v>
+      </c>
+      <c r="B112">
+        <v>0</v>
+      </c>
+      <c r="C112">
+        <v>0</v>
+      </c>
+      <c r="D112">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{599B7C2E-64CD-4BD0-BC13-E05E41B2335B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06C31B8A-A137-48E2-B883-B6DCCCBD4A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -987,7 +987,7 @@
         <v>39</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K2">
         <v>30</v>
@@ -1087,7 +1087,7 @@
         <v>29</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K3">
         <v>21</v>
@@ -1187,7 +1187,7 @@
         <v>35</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K4">
         <v>17</v>
@@ -1287,7 +1287,7 @@
         <v>32</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K5">
         <v>15</v>
@@ -1387,7 +1387,7 @@
         <v>29</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K6">
         <v>12</v>
@@ -1487,7 +1487,7 @@
         <v>30</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>20</v>
@@ -1587,7 +1587,7 @@
         <v>40</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K8">
         <v>22</v>
@@ -1687,7 +1687,7 @@
         <v>37</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K9">
         <v>15</v>
@@ -1787,7 +1787,7 @@
         <v>34</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K10">
         <v>25</v>
@@ -1887,7 +1887,7 @@
         <v>30</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K11">
         <v>17</v>
@@ -1987,7 +1987,7 @@
         <v>33</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K12">
         <v>21</v>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06C31B8A-A137-48E2-B883-B6DCCCBD4A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5B8706-F027-49F9-A981-F236045585BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -987,7 +987,7 @@
         <v>39</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K2">
         <v>30</v>
@@ -1087,7 +1087,7 @@
         <v>29</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K3">
         <v>21</v>
@@ -1187,7 +1187,7 @@
         <v>35</v>
       </c>
       <c r="J4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K4">
         <v>17</v>
@@ -1287,7 +1287,7 @@
         <v>32</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K5">
         <v>15</v>
@@ -1387,7 +1387,7 @@
         <v>29</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>12</v>
@@ -1487,7 +1487,7 @@
         <v>30</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K7">
         <v>20</v>
@@ -1587,7 +1587,7 @@
         <v>40</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K8">
         <v>22</v>
@@ -1687,7 +1687,7 @@
         <v>37</v>
       </c>
       <c r="J9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K9">
         <v>15</v>
@@ -1787,7 +1787,7 @@
         <v>34</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K10">
         <v>25</v>
@@ -1887,7 +1887,7 @@
         <v>30</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K11">
         <v>17</v>
@@ -1987,7 +1987,7 @@
         <v>33</v>
       </c>
       <c r="J12">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K12">
         <v>21</v>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5B8706-F027-49F9-A981-F236045585BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A59A0CA2-B95A-4051-98ED-7653647FAA2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="96">
   <si>
     <t>Id</t>
   </si>
@@ -330,13 +330,21 @@
   <si>
     <t>凍結攻撃を主体とするアタッカー。
 「ディープフリーズ」で攻撃時に一定量のダメージを受ける「凍結」状態にし、凍結効果をさらにアップすることで自滅に追い込むことができる。</t>
+  </si>
+  <si>
+    <t>InitMov</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GrowthMov</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -346,6 +354,14 @@
     </font>
     <font>
       <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -374,7 +390,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -382,6 +398,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -843,7 +862,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF12"/>
+  <dimension ref="A1:AH12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="11.6328125" customWidth="1"/>
@@ -855,10 +874,10 @@
     <col min="9" max="9" width="6.453125" customWidth="1"/>
     <col min="10" max="10" width="6.6328125" customWidth="1"/>
     <col min="11" max="12" width="7.08984375" customWidth="1"/>
-    <col min="13" max="13" width="7.36328125" customWidth="1"/>
+    <col min="13" max="14" width="7.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -898,65 +917,71 @@
       <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="U1" t="s">
         <v>17</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>18</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>19</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>20</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>21</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -999,64 +1024,70 @@
         <v>15</v>
       </c>
       <c r="N2">
+        <v>2</v>
+      </c>
+      <c r="O2">
         <v>55</v>
       </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
       <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
         <v>60</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <v>30</v>
       </c>
-      <c r="R2">
+      <c r="S2">
         <v>35</v>
       </c>
-      <c r="S2">
-        <v>1</v>
-      </c>
       <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>1</v>
+      </c>
+      <c r="V2">
         <v>2</v>
-      </c>
-      <c r="U2">
-        <v>6</v>
-      </c>
-      <c r="V2">
-        <v>3</v>
       </c>
       <c r="W2">
         <v>6</v>
       </c>
       <c r="X2">
+        <v>3</v>
+      </c>
+      <c r="Y2">
+        <v>6</v>
+      </c>
+      <c r="Z2">
         <v>-10</v>
       </c>
-      <c r="Y2">
+      <c r="AA2">
         <v>-54</v>
       </c>
-      <c r="Z2">
+      <c r="AB2">
         <v>0.75</v>
       </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
       <c r="AC2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2">
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1099,64 +1130,70 @@
         <v>28</v>
       </c>
       <c r="N3">
+        <v>3</v>
+      </c>
+      <c r="O3">
         <v>60</v>
       </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
       <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
         <v>40</v>
       </c>
-      <c r="Q3">
+      <c r="R3">
         <v>25</v>
       </c>
-      <c r="R3">
+      <c r="S3">
         <v>70</v>
       </c>
-      <c r="S3">
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
         <v>2</v>
       </c>
-      <c r="T3">
-        <v>1</v>
-      </c>
-      <c r="U3">
+      <c r="V3">
+        <v>1</v>
+      </c>
+      <c r="W3">
         <v>5</v>
       </c>
-      <c r="V3">
+      <c r="X3">
         <v>7</v>
       </c>
-      <c r="W3">
+      <c r="Y3">
         <v>3</v>
       </c>
-      <c r="X3">
+      <c r="Z3">
         <v>-20</v>
       </c>
-      <c r="Y3">
+      <c r="AA3">
         <v>-52</v>
       </c>
-      <c r="Z3">
+      <c r="AB3">
         <v>0.71</v>
       </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
       <c r="AC3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD3">
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1199,64 +1236,70 @@
         <v>9</v>
       </c>
       <c r="N4">
+        <v>2</v>
+      </c>
+      <c r="O4">
         <v>85</v>
       </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
       <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
         <v>25</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>50</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <v>25</v>
       </c>
-      <c r="S4">
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
         <v>3</v>
       </c>
-      <c r="T4">
+      <c r="V4">
         <v>6</v>
       </c>
-      <c r="U4">
-        <v>1</v>
-      </c>
-      <c r="V4">
+      <c r="W4">
+        <v>1</v>
+      </c>
+      <c r="X4">
         <v>2</v>
       </c>
-      <c r="W4">
+      <c r="Y4">
         <v>6</v>
       </c>
-      <c r="X4">
+      <c r="Z4">
         <v>-10</v>
       </c>
-      <c r="Y4">
+      <c r="AA4">
         <v>-64</v>
       </c>
-      <c r="Z4">
+      <c r="AB4">
         <v>0.82</v>
       </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
       <c r="AC4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD4">
         <v>0</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1299,64 +1342,70 @@
         <v>21</v>
       </c>
       <c r="N5">
+        <v>2</v>
+      </c>
+      <c r="O5">
         <v>85</v>
       </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
       <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
         <v>35</v>
       </c>
-      <c r="Q5">
+      <c r="R5">
         <v>15</v>
       </c>
-      <c r="R5">
+      <c r="S5">
         <v>30</v>
       </c>
-      <c r="S5">
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
         <v>4</v>
       </c>
-      <c r="T5">
+      <c r="V5">
         <v>3</v>
       </c>
-      <c r="U5">
+      <c r="W5">
         <v>3</v>
       </c>
-      <c r="V5">
-        <v>1</v>
-      </c>
-      <c r="W5">
+      <c r="X5">
+        <v>1</v>
+      </c>
+      <c r="Y5">
         <v>7</v>
       </c>
-      <c r="X5">
+      <c r="Z5">
         <v>-4</v>
       </c>
-      <c r="Y5">
+      <c r="AA5">
         <v>-68</v>
       </c>
-      <c r="Z5">
+      <c r="AB5">
         <v>0.8</v>
       </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0</v>
-      </c>
       <c r="AC5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD5">
         <v>0</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1399,64 +1448,70 @@
         <v>12</v>
       </c>
       <c r="N6">
+        <v>2</v>
+      </c>
+      <c r="O6">
         <v>70</v>
       </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
       <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
         <v>30</v>
       </c>
-      <c r="Q6">
+      <c r="R6">
         <v>40</v>
       </c>
-      <c r="R6">
+      <c r="S6">
         <v>45</v>
       </c>
-      <c r="S6">
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
         <v>4</v>
       </c>
-      <c r="T6">
+      <c r="V6">
         <v>6</v>
       </c>
-      <c r="U6">
+      <c r="W6">
         <v>2</v>
       </c>
-      <c r="V6">
+      <c r="X6">
         <v>5</v>
       </c>
-      <c r="W6">
-        <v>1</v>
-      </c>
-      <c r="X6">
+      <c r="Y6">
+        <v>1</v>
+      </c>
+      <c r="Z6">
         <v>-8</v>
       </c>
-      <c r="Y6">
+      <c r="AA6">
         <v>-44</v>
       </c>
-      <c r="Z6">
+      <c r="AB6">
         <v>0.82</v>
       </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0</v>
-      </c>
       <c r="AC6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD6">
         <v>0</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1499,13 +1554,13 @@
         <v>20</v>
       </c>
       <c r="N7">
+        <v>2</v>
+      </c>
+      <c r="O7">
         <v>40</v>
       </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
       <c r="P7">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Q7">
         <v>50</v>
@@ -1514,49 +1569,55 @@
         <v>50</v>
       </c>
       <c r="S7">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V7">
         <v>6</v>
       </c>
       <c r="W7">
+        <v>2</v>
+      </c>
+      <c r="X7">
+        <v>6</v>
+      </c>
+      <c r="Y7">
         <v>3</v>
       </c>
-      <c r="X7">
+      <c r="Z7">
         <v>48</v>
       </c>
-      <c r="Y7">
+      <c r="AA7">
         <v>-68</v>
       </c>
-      <c r="Z7">
+      <c r="AB7">
         <v>0.76</v>
       </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
       <c r="AC7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD7">
         <v>0</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1599,64 +1660,70 @@
         <v>16</v>
       </c>
       <c r="N8">
+        <v>3</v>
+      </c>
+      <c r="O8">
         <v>65</v>
       </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
       <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
         <v>45</v>
       </c>
-      <c r="Q8">
+      <c r="R8">
         <v>40</v>
       </c>
-      <c r="R8">
+      <c r="S8">
         <v>30</v>
       </c>
-      <c r="S8">
-        <v>4</v>
-      </c>
       <c r="T8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8">
         <v>4</v>
       </c>
       <c r="V8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W8">
         <v>4</v>
       </c>
       <c r="X8">
+        <v>3</v>
+      </c>
+      <c r="Y8">
+        <v>4</v>
+      </c>
+      <c r="Z8">
         <v>-20</v>
       </c>
-      <c r="Y8">
+      <c r="AA8">
         <v>-60</v>
       </c>
-      <c r="Z8">
+      <c r="AB8">
         <v>0.79</v>
       </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0</v>
-      </c>
       <c r="AC8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD8">
         <v>0</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1699,64 +1766,70 @@
         <v>16</v>
       </c>
       <c r="N9">
+        <v>2</v>
+      </c>
+      <c r="O9">
         <v>80</v>
       </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
       <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
         <v>40</v>
       </c>
-      <c r="Q9">
+      <c r="R9">
         <v>60</v>
       </c>
-      <c r="R9">
+      <c r="S9">
         <v>35</v>
       </c>
-      <c r="S9">
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
         <v>6</v>
       </c>
-      <c r="T9">
+      <c r="V9">
         <v>2</v>
       </c>
-      <c r="U9">
-        <v>1</v>
-      </c>
-      <c r="V9">
+      <c r="W9">
+        <v>1</v>
+      </c>
+      <c r="X9">
         <v>5</v>
       </c>
-      <c r="W9">
+      <c r="Y9">
         <v>4</v>
       </c>
-      <c r="X9">
+      <c r="Z9">
         <v>-52</v>
       </c>
-      <c r="Y9">
+      <c r="AA9">
         <v>-52</v>
       </c>
-      <c r="Z9">
+      <c r="AB9">
         <v>0.8</v>
       </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>0</v>
-      </c>
       <c r="AC9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD9">
         <v>0</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1799,64 +1872,70 @@
         <v>24</v>
       </c>
       <c r="N10">
+        <v>2</v>
+      </c>
+      <c r="O10">
         <v>25</v>
       </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
       <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
         <v>65</v>
       </c>
-      <c r="Q10">
+      <c r="R10">
         <v>30</v>
       </c>
-      <c r="R10">
+      <c r="S10">
         <v>50</v>
       </c>
-      <c r="S10">
-        <v>1</v>
-      </c>
       <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>1</v>
+      </c>
+      <c r="V10">
         <v>4</v>
       </c>
-      <c r="U10">
+      <c r="W10">
         <v>4</v>
       </c>
-      <c r="V10">
+      <c r="X10">
         <v>7</v>
       </c>
-      <c r="W10">
+      <c r="Y10">
         <v>2</v>
       </c>
-      <c r="X10">
+      <c r="Z10">
         <v>-16</v>
       </c>
-      <c r="Y10">
+      <c r="AA10">
         <v>-52</v>
       </c>
-      <c r="Z10">
+      <c r="AB10">
         <v>0.75</v>
       </c>
-      <c r="AA10">
-        <v>0</v>
-      </c>
-      <c r="AB10">
-        <v>0</v>
-      </c>
       <c r="AC10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD10">
         <v>0</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1899,64 +1978,70 @@
         <v>31</v>
       </c>
       <c r="N11">
+        <v>3</v>
+      </c>
+      <c r="O11">
         <v>45</v>
       </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
       <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
         <v>30</v>
       </c>
-      <c r="Q11">
+      <c r="R11">
         <v>20</v>
       </c>
-      <c r="R11">
+      <c r="S11">
         <v>75</v>
       </c>
-      <c r="S11">
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
         <v>4</v>
       </c>
-      <c r="T11">
-        <v>1</v>
-      </c>
-      <c r="U11">
+      <c r="V11">
+        <v>1</v>
+      </c>
+      <c r="W11">
         <v>6</v>
       </c>
-      <c r="V11">
+      <c r="X11">
         <v>5</v>
       </c>
-      <c r="W11">
+      <c r="Y11">
         <v>2</v>
       </c>
-      <c r="X11">
+      <c r="Z11">
         <v>12</v>
       </c>
-      <c r="Y11">
+      <c r="AA11">
         <v>-64</v>
       </c>
-      <c r="Z11">
+      <c r="AB11">
         <v>0.77</v>
       </c>
-      <c r="AA11">
-        <v>0</v>
-      </c>
-      <c r="AB11">
-        <v>0</v>
-      </c>
       <c r="AC11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD11">
         <v>0</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1999,60 +2084,66 @@
         <v>18</v>
       </c>
       <c r="N12">
+        <v>2</v>
+      </c>
+      <c r="O12">
         <v>65</v>
       </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
       <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
         <v>40</v>
       </c>
-      <c r="Q12">
+      <c r="R12">
         <v>25</v>
       </c>
-      <c r="R12">
+      <c r="S12">
         <v>30</v>
       </c>
-      <c r="S12">
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
         <v>6</v>
       </c>
-      <c r="T12">
+      <c r="V12">
         <v>6</v>
       </c>
-      <c r="U12">
-        <v>1</v>
-      </c>
-      <c r="V12">
+      <c r="W12">
+        <v>1</v>
+      </c>
+      <c r="X12">
         <v>3</v>
       </c>
-      <c r="W12">
+      <c r="Y12">
         <v>2</v>
       </c>
-      <c r="X12">
-        <v>0</v>
-      </c>
-      <c r="Y12">
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
         <v>-54</v>
       </c>
-      <c r="Z12">
+      <c r="AB12">
         <v>0.87</v>
       </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>0</v>
-      </c>
       <c r="AC12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD12">
         <v>0</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A59A0CA2-B95A-4051-98ED-7653647FAA2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9272077-47A4-4F44-B3BF-EA7A8A48579D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   <externalReferences>
     <externalReference r:id="rId5"/>
   </externalReferences>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1024,7 +1024,7 @@
         <v>15</v>
       </c>
       <c r="N2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O2">
         <v>55</v>
@@ -1130,7 +1130,7 @@
         <v>28</v>
       </c>
       <c r="N3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O3">
         <v>60</v>
@@ -1236,7 +1236,7 @@
         <v>9</v>
       </c>
       <c r="N4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O4">
         <v>85</v>
@@ -1342,7 +1342,7 @@
         <v>21</v>
       </c>
       <c r="N5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O5">
         <v>85</v>
@@ -1448,7 +1448,7 @@
         <v>12</v>
       </c>
       <c r="N6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O6">
         <v>70</v>
@@ -1554,7 +1554,7 @@
         <v>20</v>
       </c>
       <c r="N7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O7">
         <v>40</v>
@@ -1660,7 +1660,7 @@
         <v>16</v>
       </c>
       <c r="N8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O8">
         <v>65</v>
@@ -1766,7 +1766,7 @@
         <v>16</v>
       </c>
       <c r="N9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O9">
         <v>80</v>
@@ -1872,7 +1872,7 @@
         <v>24</v>
       </c>
       <c r="N10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O10">
         <v>25</v>
@@ -1978,7 +1978,7 @@
         <v>31</v>
       </c>
       <c r="N11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O11">
         <v>45</v>
@@ -2084,7 +2084,7 @@
         <v>18</v>
       </c>
       <c r="N12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O12">
         <v>65</v>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9272077-47A4-4F44-B3BF-EA7A8A48579D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="19200" windowHeight="7820" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -21,18 +15,7 @@
   <externalReferences>
     <externalReference r:id="rId5"/>
   </externalReferences>
-  <calcPr calcId="191029" concurrentCalc="0"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525" concurrentCalc="0"/>
 </workbook>
 </file>
 
@@ -75,6 +58,9 @@
     <t>InitSpd</t>
   </si>
   <si>
+    <t>InitMov</t>
+  </si>
+  <si>
     <t>GrowthHp</t>
   </si>
   <si>
@@ -90,6 +76,9 @@
     <t>GrowthSpd</t>
   </si>
   <si>
+    <t>GrowthMov</t>
+  </si>
+  <si>
     <t>Element1</t>
   </si>
   <si>
@@ -150,6 +139,21 @@
     <t>0006</t>
   </si>
   <si>
+    <t>0007</t>
+  </si>
+  <si>
+    <t>0008</t>
+  </si>
+  <si>
+    <t>0009</t>
+  </si>
+  <si>
+    <t>0010</t>
+  </si>
+  <si>
+    <t>0011</t>
+  </si>
+  <si>
     <t>ActorId</t>
   </si>
   <si>
@@ -159,6 +163,39 @@
     <t>Level</t>
   </si>
   <si>
+    <t>11,21,31,1010,1060,100110,100120</t>
+  </si>
+  <si>
+    <t>11,21,31,2010,2070,100210,100220</t>
+  </si>
+  <si>
+    <t>11,21,31,3010,3020,100310,100320</t>
+  </si>
+  <si>
+    <t>11,21,31,4010,4030,100410,100420</t>
+  </si>
+  <si>
+    <t>11,21,31,5010,5070,100510,100520</t>
+  </si>
+  <si>
+    <t>11,21,31,1010,1030,100610,100620</t>
+  </si>
+  <si>
+    <t>11,21,31,2010,2040,100710,100720</t>
+  </si>
+  <si>
+    <t>11,21,31,3010,3070,100810,100820</t>
+  </si>
+  <si>
+    <t>11,21,31,1010,1050,100910,100920</t>
+  </si>
+  <si>
+    <t>11,21,31,2010,2030,101010,101020</t>
+  </si>
+  <si>
+    <t>11,21,31,3010,3050,101110,101120</t>
+  </si>
+  <si>
     <t>TriggerType1</t>
   </si>
   <si>
@@ -172,116 +209,68 @@
   </si>
   <si>
     <t>Feature</t>
+  </si>
+  <si>
+    <t>ミカ</t>
+  </si>
+  <si>
+    <t>【煉獄棘姫】</t>
   </si>
   <si>
     <t>高い攻撃性能を持つアタッカー。
 全体的にステータスが高く、赤属性魔法を習得することでさらに攻撃性能を伸ばすことができる。</t>
   </si>
   <si>
+    <t>エリザベート</t>
+  </si>
+  <si>
+    <t>【ChargeCommander】</t>
+  </si>
+  <si>
     <t>回避率を上げて攻撃を避けるアタッカー。
 打たれ弱いがSPDが高く、回避率をアップする雷属性魔法を習得しやすい。</t>
   </si>
   <si>
+    <t>アリエス</t>
+  </si>
+  <si>
+    <t>【怠惰な守護少女】</t>
+  </si>
+  <si>
     <t>相手の攻撃を跳ね返すディフェンダー。
 受けた攻撃ダメージの一部を跳ね返す「カウンターオーラ」を使うことができる。</t>
   </si>
   <si>
+    <t>シイナ</t>
+  </si>
+  <si>
+    <t>【イノセント・リメディ】</t>
+  </si>
+  <si>
     <t>回復に特化したヒーラー。
 全体的にステータスが低いが、味方のHpを回復する「ヒーリング」を使うことができる。</t>
   </si>
   <si>
-    <t>シイナ</t>
+    <t>レダ</t>
+  </si>
+  <si>
+    <t>【Self-sacrifice】</t>
   </si>
   <si>
     <t>相手の攻撃性能を下げるジャマー。
 「シェイディークラウド」で味方が受けるダメージを抑えたり、「毒」でスリップダメージを与える魔法を使うことができる。</t>
   </si>
   <si>
+    <t>リシェリ</t>
+  </si>
+  <si>
+    <t>【Faked-Magician】</t>
+  </si>
+  <si>
     <t>味方のCTを短縮することができるサポーター。
 CT（魔法を再使用するまでのターン数）を短縮しパーティ全体の補助をすることができる。</t>
   </si>
   <si>
-    <t>0007</t>
-  </si>
-  <si>
-    <t>0008</t>
-  </si>
-  <si>
-    <t>0009</t>
-  </si>
-  <si>
-    <t>0010</t>
-  </si>
-  <si>
-    <t>0011</t>
-  </si>
-  <si>
-    <t>11,21,31,1010,1060,100110,100120</t>
-  </si>
-  <si>
-    <t>11,21,31,2010,2070,100210,100220</t>
-  </si>
-  <si>
-    <t>11,21,31,3010,3020,100310,100320</t>
-  </si>
-  <si>
-    <t>11,21,31,4010,4030,100410,100420</t>
-  </si>
-  <si>
-    <t>11,21,31,5010,5070,100510,100520</t>
-  </si>
-  <si>
-    <t>11,21,31,1010,1030,100610,100620</t>
-  </si>
-  <si>
-    <t>11,21,31,2010,2040,100710,100720</t>
-  </si>
-  <si>
-    <t>11,21,31,3010,3070,100810,100820</t>
-  </si>
-  <si>
-    <t>11,21,31,1010,1050,100910,100920</t>
-  </si>
-  <si>
-    <t>11,21,31,2010,2030,101010,101020</t>
-  </si>
-  <si>
-    <t>11,21,31,3010,3050,101110,101120</t>
-  </si>
-  <si>
-    <t>ミカ</t>
-  </si>
-  <si>
-    <t>【煉獄棘姫】</t>
-  </si>
-  <si>
-    <t>エリザベート</t>
-  </si>
-  <si>
-    <t>【ChargeCommander】</t>
-  </si>
-  <si>
-    <t>アリエス</t>
-  </si>
-  <si>
-    <t>【怠惰な守護少女】</t>
-  </si>
-  <si>
-    <t>【イノセント・リメディ】</t>
-  </si>
-  <si>
-    <t>レダ</t>
-  </si>
-  <si>
-    <t>【Self-sacrifice】</t>
-  </si>
-  <si>
-    <t>リシェリ</t>
-  </si>
-  <si>
-    <t>【Faked-Magician】</t>
-  </si>
-  <si>
     <t>ユニ</t>
   </si>
   <si>
@@ -330,21 +319,19 @@
   <si>
     <t>凍結攻撃を主体とするアタッカー。
 「ディープフリーズ」で攻撃時に一定量のダメージを受ける「凍結」状態にし、凍結効果をさらにアップすることで自滅に追い込むことができる。</t>
-  </si>
-  <si>
-    <t>InitMov</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>GrowthMov</t>
-    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -353,9 +340,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="6"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -363,20 +350,342 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -384,9 +693,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -400,37 +951,79 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="桁区切り[0]" xfId="1" builtinId="6"/>
+    <cellStyle name="入力" xfId="2" builtinId="20"/>
+    <cellStyle name="桁区切り" xfId="3" builtinId="3"/>
+    <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
+    <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
+    <cellStyle name="通貨" xfId="6" builtinId="4"/>
+    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
+    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
+    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="良い" xfId="13" builtinId="26"/>
+    <cellStyle name="警告文" xfId="14" builtinId="11"/>
+    <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
+    <cellStyle name="タイトル" xfId="16" builtinId="15"/>
+    <cellStyle name="説明文" xfId="17" builtinId="53"/>
+    <cellStyle name="アクセント 6" xfId="18" builtinId="49"/>
+    <cellStyle name="出力" xfId="19" builtinId="21"/>
+    <cellStyle name="見出し 1" xfId="20" builtinId="16"/>
+    <cellStyle name="見出し 2" xfId="21" builtinId="17"/>
+    <cellStyle name="計算" xfId="22" builtinId="22"/>
+    <cellStyle name="見出し 3" xfId="23" builtinId="18"/>
+    <cellStyle name="見出し 4" xfId="24" builtinId="19"/>
+    <cellStyle name="60% - アクセント 5" xfId="25" builtinId="48"/>
+    <cellStyle name="チェックセル" xfId="26" builtinId="23"/>
+    <cellStyle name="40% - アクセント 1" xfId="27" builtinId="31"/>
+    <cellStyle name="集計" xfId="28" builtinId="25"/>
+    <cellStyle name="悪い" xfId="29" builtinId="27"/>
+    <cellStyle name="どちらでもない" xfId="30" builtinId="28"/>
+    <cellStyle name="アクセント 1" xfId="31" builtinId="29"/>
+    <cellStyle name="20% - アクセント 1" xfId="32" builtinId="30"/>
+    <cellStyle name="20% - アクセント 5" xfId="33" builtinId="46"/>
+    <cellStyle name="60% - アクセント 1" xfId="34" builtinId="32"/>
+    <cellStyle name="20% - アクセント 2" xfId="35" builtinId="34"/>
+    <cellStyle name="40% - アクセント 2" xfId="36" builtinId="35"/>
+    <cellStyle name="20% - アクセント 6" xfId="37" builtinId="50"/>
+    <cellStyle name="60% - アクセント 2" xfId="38" builtinId="36"/>
+    <cellStyle name="アクセント 3" xfId="39" builtinId="37"/>
+    <cellStyle name="20% - アクセント 3" xfId="40" builtinId="38"/>
+    <cellStyle name="40% - アクセント 3" xfId="41" builtinId="39"/>
+    <cellStyle name="60% - アクセント 3" xfId="42" builtinId="40"/>
+    <cellStyle name="アクセント 4" xfId="43" builtinId="41"/>
+    <cellStyle name="40% - アクセント 4" xfId="44" builtinId="43"/>
+    <cellStyle name="60% - アクセント 4" xfId="45" builtinId="44"/>
+    <cellStyle name="アクセント 5" xfId="46" builtinId="45"/>
+    <cellStyle name="40% - アクセント 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - アクセント 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Actors"/>
       <sheetName val="Learning"/>
       <sheetName val="SkillTrigger"/>
       <sheetName val="TextData"/>
+      <sheetName val="TextDat"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -441,9 +1034,8 @@
           <cell r="A1" t="str">
             <v>Id</v>
           </cell>
-          <cell r="B1" t="str">
-            <v>Text</v>
-          </cell>
+        </row>
+        <row r="1">
           <cell r="C1" t="str">
             <v>SubName</v>
           </cell>
@@ -452,9 +1044,8 @@
           <cell r="A2">
             <v>1</v>
           </cell>
-          <cell r="B2" t="str">
-            <v>ミカ</v>
-          </cell>
+        </row>
+        <row r="2">
           <cell r="C2" t="str">
             <v>【煉獄棘姫】</v>
           </cell>
@@ -463,9 +1054,8 @@
           <cell r="A3">
             <v>2</v>
           </cell>
-          <cell r="B3" t="str">
-            <v>エリザベート</v>
-          </cell>
+        </row>
+        <row r="3">
           <cell r="C3" t="str">
             <v>【ChargeCommander】</v>
           </cell>
@@ -474,9 +1064,8 @@
           <cell r="A4">
             <v>3</v>
           </cell>
-          <cell r="B4" t="str">
-            <v>アリエス</v>
-          </cell>
+        </row>
+        <row r="4">
           <cell r="C4" t="str">
             <v>【怠惰な守護少女】</v>
           </cell>
@@ -485,9 +1074,8 @@
           <cell r="A5">
             <v>4</v>
           </cell>
-          <cell r="B5" t="str">
-            <v>シイナ</v>
-          </cell>
+        </row>
+        <row r="5">
           <cell r="C5" t="str">
             <v>【イノセント・リメディ】</v>
           </cell>
@@ -496,9 +1084,8 @@
           <cell r="A6">
             <v>5</v>
           </cell>
-          <cell r="B6" t="str">
-            <v>レダ</v>
-          </cell>
+        </row>
+        <row r="6">
           <cell r="C6" t="str">
             <v>【Self-sacrifice】</v>
           </cell>
@@ -507,9 +1094,8 @@
           <cell r="A7">
             <v>6</v>
           </cell>
-          <cell r="B7" t="str">
-            <v>リシェリ</v>
-          </cell>
+        </row>
+        <row r="7">
           <cell r="C7" t="str">
             <v>【Faked-Magician】</v>
           </cell>
@@ -518,9 +1104,8 @@
           <cell r="A8">
             <v>7</v>
           </cell>
-          <cell r="B8" t="str">
-            <v>ユニ</v>
-          </cell>
+        </row>
+        <row r="8">
           <cell r="C8" t="str">
             <v>【奇跡の乙女】</v>
           </cell>
@@ -529,9 +1114,8 @@
           <cell r="A9">
             <v>8</v>
           </cell>
-          <cell r="B9" t="str">
-            <v>マリーベル</v>
-          </cell>
+        </row>
+        <row r="9">
           <cell r="C9" t="str">
             <v>【唯心の在処】</v>
           </cell>
@@ -540,9 +1124,8 @@
           <cell r="A10">
             <v>9</v>
           </cell>
-          <cell r="B10" t="str">
-            <v>ナツキ</v>
-          </cell>
+        </row>
+        <row r="10">
           <cell r="C10" t="str">
             <v>【黄昏ニヒリスト】</v>
           </cell>
@@ -551,9 +1134,8 @@
           <cell r="A11">
             <v>10</v>
           </cell>
-          <cell r="B11" t="str">
-            <v>メリアドール</v>
-          </cell>
+        </row>
+        <row r="11">
           <cell r="C11" t="str">
             <v>【怨嗟の鎖】</v>
           </cell>
@@ -562,14 +1144,14 @@
           <cell r="A12">
             <v>11</v>
           </cell>
-          <cell r="B12" t="str">
-            <v>セリナ</v>
-          </cell>
+        </row>
+        <row r="12">
           <cell r="C12" t="str">
             <v>【氷雪の勿忘草】</v>
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="4" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -856,28 +1438,28 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:AH12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="3" max="3" width="11.6328125" customWidth="1"/>
+    <col min="3" max="3" width="11.6363636363636" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
-    <col min="5" max="5" width="7.54296875" customWidth="1"/>
+    <col min="5" max="5" width="7.54545454545455" customWidth="1"/>
     <col min="6" max="6" width="9" style="2"/>
-    <col min="7" max="7" width="6.1796875" customWidth="1"/>
-    <col min="8" max="8" width="6.81640625" customWidth="1"/>
-    <col min="9" max="9" width="6.453125" customWidth="1"/>
-    <col min="10" max="10" width="6.6328125" customWidth="1"/>
-    <col min="11" max="12" width="7.08984375" customWidth="1"/>
-    <col min="13" max="14" width="7.36328125" customWidth="1"/>
+    <col min="7" max="7" width="6.18181818181818" customWidth="1"/>
+    <col min="8" max="8" width="6.81818181818182" customWidth="1"/>
+    <col min="9" max="9" width="6.45454545454545" customWidth="1"/>
+    <col min="10" max="10" width="6.63636363636364" customWidth="1"/>
+    <col min="11" max="12" width="7.09090909090909" customWidth="1"/>
+    <col min="13" max="14" width="7.36363636363636" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:34">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -918,70 +1500,70 @@
         <v>11</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>94</v>
+        <v>12</v>
       </c>
       <c r="O1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="U1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="W1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="X1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Z1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AB1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AC1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AD1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AF1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AG1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AH1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34">
       <c r="A2">
         <v>1</v>
       </c>
@@ -989,7 +1571,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(B2,[1]TextData!A:A))</f>
+        <f>INDEX(TextData!B:B,MATCH(B2,TextData!A:A))</f>
         <v>ミカ</v>
       </c>
       <c r="D2" t="str">
@@ -1000,7 +1582,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -1087,7 +1669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:34">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1095,7 +1677,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(B3,[1]TextData!A:A))</f>
+        <f>INDEX(TextData!B:B,MATCH(B3,TextData!A:A))</f>
         <v>エリザベート</v>
       </c>
       <c r="D3" t="str">
@@ -1106,7 +1688,7 @@
         <v>2</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -1193,7 +1775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:34">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1201,7 +1783,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(B4,[1]TextData!A:A))</f>
+        <f>INDEX(TextData!B:B,MATCH(B4,TextData!A:A))</f>
         <v>アリエス</v>
       </c>
       <c r="D4" t="str">
@@ -1212,7 +1794,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -1299,7 +1881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1307,7 +1889,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(B5,[1]TextData!A:A))</f>
+        <f>INDEX(TextData!B:B,MATCH(B5,TextData!A:A))</f>
         <v>シイナ</v>
       </c>
       <c r="D5" t="str">
@@ -1318,7 +1900,7 @@
         <v>4</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1405,7 +1987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1413,7 +1995,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(B6,[1]TextData!A:A))</f>
+        <f>INDEX(TextData!B:B,MATCH(B6,TextData!A:A))</f>
         <v>レダ</v>
       </c>
       <c r="D6" t="str">
@@ -1424,7 +2006,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1511,7 +2093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1519,7 +2101,7 @@
         <v>6</v>
       </c>
       <c r="C7" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(B7,[1]TextData!A:A))</f>
+        <f>INDEX(TextData!B:B,MATCH(B7,TextData!A:A))</f>
         <v>リシェリ</v>
       </c>
       <c r="D7" t="str">
@@ -1530,7 +2112,7 @@
         <v>6</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1617,7 +2199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1625,7 +2207,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(B8,[1]TextData!A:A))</f>
+        <f>INDEX(TextData!B:B,MATCH(B8,TextData!A:A))</f>
         <v>ユニ</v>
       </c>
       <c r="D8" t="str">
@@ -1636,7 +2218,7 @@
         <v>7</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1723,7 +2305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1731,7 +2313,7 @@
         <v>8</v>
       </c>
       <c r="C9" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(B9,[1]TextData!A:A))</f>
+        <f>INDEX(TextData!B:B,MATCH(B9,TextData!A:A))</f>
         <v>マリーベル</v>
       </c>
       <c r="D9" t="str">
@@ -1742,7 +2324,7 @@
         <v>8</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1829,7 +2411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1837,7 +2419,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(B10,[1]TextData!A:A))</f>
+        <f>INDEX(TextData!B:B,MATCH(B10,TextData!A:A))</f>
         <v>ナツキ</v>
       </c>
       <c r="D10" t="str">
@@ -1848,7 +2430,7 @@
         <v>9</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1935,7 +2517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1943,7 +2525,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(B11,[1]TextData!A:A))</f>
+        <f>INDEX(TextData!B:B,MATCH(B11,TextData!A:A))</f>
         <v>メリアドール</v>
       </c>
       <c r="D11" t="str">
@@ -1954,7 +2536,7 @@
         <v>10</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -2041,7 +2623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:34">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2049,7 +2631,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(B12,[1]TextData!A:A))</f>
+        <f>INDEX(TextData!B:B,MATCH(B12,TextData!A:A))</f>
         <v>セリナ</v>
       </c>
       <c r="D12" t="str">
@@ -2060,7 +2642,7 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -2148,43 +2730,44 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C45"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
-    <col min="2" max="2" width="44.26953125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="44.2727272727273" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2195,7 +2778,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -2206,7 +2789,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -2217,15 +2800,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2">
       <c r="A6">
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>2</v>
       </c>
@@ -2236,7 +2819,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>2</v>
       </c>
@@ -2247,7 +2830,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -2258,15 +2841,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2">
       <c r="A10">
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11">
         <v>3</v>
       </c>
@@ -2277,7 +2860,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3">
       <c r="A12">
         <v>3</v>
       </c>
@@ -2288,7 +2871,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3">
       <c r="A13">
         <v>3</v>
       </c>
@@ -2299,15 +2882,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2">
       <c r="A14">
         <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15">
         <v>4</v>
       </c>
@@ -2318,7 +2901,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3">
       <c r="A16">
         <v>4</v>
       </c>
@@ -2329,7 +2912,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3">
       <c r="A17">
         <v>4</v>
       </c>
@@ -2340,15 +2923,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2">
       <c r="A18">
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19">
         <v>5</v>
       </c>
@@ -2359,7 +2942,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3">
       <c r="A20">
         <v>5</v>
       </c>
@@ -2370,7 +2953,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3">
       <c r="A21">
         <v>5</v>
       </c>
@@ -2381,15 +2964,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2">
       <c r="A22">
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23">
         <v>6</v>
       </c>
@@ -2400,7 +2983,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3">
       <c r="A24">
         <v>6</v>
       </c>
@@ -2411,7 +2994,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3">
       <c r="A25">
         <v>6</v>
       </c>
@@ -2422,15 +3005,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2">
       <c r="A26">
         <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27">
         <v>7</v>
       </c>
@@ -2441,7 +3024,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3">
       <c r="A28">
         <v>7</v>
       </c>
@@ -2452,7 +3035,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3">
       <c r="A29">
         <v>7</v>
       </c>
@@ -2463,15 +3046,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2">
       <c r="A30">
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
       <c r="A31">
         <v>8</v>
       </c>
@@ -2482,7 +3065,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3">
       <c r="A32">
         <v>8</v>
       </c>
@@ -2493,7 +3076,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3">
       <c r="A33">
         <v>8</v>
       </c>
@@ -2504,15 +3087,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2">
       <c r="A34">
         <v>9</v>
       </c>
       <c r="B34" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35">
         <v>9</v>
       </c>
@@ -2523,7 +3106,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3">
       <c r="A36">
         <v>9</v>
       </c>
@@ -2534,7 +3117,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3">
       <c r="A37">
         <v>9</v>
       </c>
@@ -2545,15 +3128,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2">
       <c r="A38">
         <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39">
         <v>10</v>
       </c>
@@ -2564,7 +3147,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3">
       <c r="A40">
         <v>10</v>
       </c>
@@ -2575,7 +3158,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3">
       <c r="A41">
         <v>10</v>
       </c>
@@ -2586,15 +3169,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2">
       <c r="A42">
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43">
         <v>11</v>
       </c>
@@ -2605,7 +3188,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3">
       <c r="A44">
         <v>11</v>
       </c>
@@ -2616,7 +3199,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3">
       <c r="A45">
         <v>11</v>
       </c>
@@ -2628,34 +3211,35 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D112"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="3"/>
   <cols>
-    <col min="3" max="4" width="12.90625" customWidth="1"/>
+    <col min="3" max="4" width="12.9090909090909" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C1" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2669,7 +3253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2683,7 +3267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>1</v>
       </c>
@@ -2697,7 +3281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5">
         <v>1</v>
       </c>
@@ -2711,7 +3295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="A6">
         <v>1</v>
       </c>
@@ -2725,7 +3309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4">
       <c r="A7">
         <v>1</v>
       </c>
@@ -2739,7 +3323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4">
       <c r="A8">
         <v>1</v>
       </c>
@@ -2753,7 +3337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4">
       <c r="A9">
         <v>1</v>
       </c>
@@ -2767,7 +3351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4">
       <c r="A10">
         <v>1</v>
       </c>
@@ -2781,7 +3365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4">
       <c r="A11">
         <v>1</v>
       </c>
@@ -2795,7 +3379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4">
       <c r="A12">
         <v>2</v>
       </c>
@@ -2809,7 +3393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4">
       <c r="A13">
         <v>2</v>
       </c>
@@ -2823,7 +3407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4">
       <c r="A14">
         <v>2</v>
       </c>
@@ -2837,7 +3421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4">
       <c r="A15">
         <v>2</v>
       </c>
@@ -2851,7 +3435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4">
       <c r="A16">
         <v>2</v>
       </c>
@@ -2865,7 +3449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4">
       <c r="A17">
         <v>2</v>
       </c>
@@ -2879,7 +3463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4">
       <c r="A18">
         <v>2</v>
       </c>
@@ -2893,7 +3477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4">
       <c r="A19">
         <v>2</v>
       </c>
@@ -2907,7 +3491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4">
       <c r="A20">
         <v>2</v>
       </c>
@@ -2921,7 +3505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4">
       <c r="A21">
         <v>2</v>
       </c>
@@ -2935,7 +3519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4">
       <c r="A22">
         <v>3</v>
       </c>
@@ -2949,7 +3533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4">
       <c r="A23">
         <v>3</v>
       </c>
@@ -2963,7 +3547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4">
       <c r="A24">
         <v>3</v>
       </c>
@@ -2977,7 +3561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4">
       <c r="A25">
         <v>3</v>
       </c>
@@ -2991,7 +3575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4">
       <c r="A26">
         <v>3</v>
       </c>
@@ -3005,7 +3589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4">
       <c r="A27">
         <v>3</v>
       </c>
@@ -3019,7 +3603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4">
       <c r="A28">
         <v>3</v>
       </c>
@@ -3033,7 +3617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4">
       <c r="A29">
         <v>3</v>
       </c>
@@ -3047,7 +3631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4">
       <c r="A30">
         <v>3</v>
       </c>
@@ -3061,7 +3645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4">
       <c r="A31">
         <v>3</v>
       </c>
@@ -3075,7 +3659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4">
       <c r="A32">
         <v>4</v>
       </c>
@@ -3089,7 +3673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4">
       <c r="A33">
         <v>4</v>
       </c>
@@ -3103,7 +3687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4">
       <c r="A34">
         <v>4</v>
       </c>
@@ -3117,7 +3701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4">
       <c r="A35">
         <v>4</v>
       </c>
@@ -3131,7 +3715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4">
       <c r="A36">
         <v>4</v>
       </c>
@@ -3145,7 +3729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4">
       <c r="A37">
         <v>4</v>
       </c>
@@ -3159,7 +3743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4">
       <c r="A38">
         <v>4</v>
       </c>
@@ -3173,7 +3757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4">
       <c r="A39">
         <v>4</v>
       </c>
@@ -3187,7 +3771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4">
       <c r="A40">
         <v>4</v>
       </c>
@@ -3201,7 +3785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4">
       <c r="A41">
         <v>4</v>
       </c>
@@ -3215,7 +3799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4">
       <c r="A42">
         <v>5</v>
       </c>
@@ -3229,7 +3813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4">
       <c r="A43">
         <v>5</v>
       </c>
@@ -3243,7 +3827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4">
       <c r="A44">
         <v>5</v>
       </c>
@@ -3257,7 +3841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4">
       <c r="A45">
         <v>5</v>
       </c>
@@ -3271,7 +3855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4">
       <c r="A46">
         <v>5</v>
       </c>
@@ -3285,7 +3869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4">
       <c r="A47">
         <v>5</v>
       </c>
@@ -3299,7 +3883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4">
       <c r="A48">
         <v>5</v>
       </c>
@@ -3313,7 +3897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4">
       <c r="A49">
         <v>5</v>
       </c>
@@ -3327,7 +3911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4">
       <c r="A50">
         <v>5</v>
       </c>
@@ -3341,7 +3925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4">
       <c r="A51">
         <v>5</v>
       </c>
@@ -3355,7 +3939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4">
       <c r="A52">
         <v>6</v>
       </c>
@@ -3369,7 +3953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4">
       <c r="A53">
         <v>6</v>
       </c>
@@ -3383,7 +3967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4">
       <c r="A54">
         <v>6</v>
       </c>
@@ -3397,7 +3981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4">
       <c r="A55">
         <v>6</v>
       </c>
@@ -3411,7 +3995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4">
       <c r="A56">
         <v>6</v>
       </c>
@@ -3425,7 +4009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4">
       <c r="A57">
         <v>6</v>
       </c>
@@ -3439,7 +4023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4">
       <c r="A58">
         <v>6</v>
       </c>
@@ -3453,7 +4037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4">
       <c r="A59">
         <v>6</v>
       </c>
@@ -3467,7 +4051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4">
       <c r="A60">
         <v>6</v>
       </c>
@@ -3481,7 +4065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4">
       <c r="A61">
         <v>6</v>
       </c>
@@ -3495,7 +4079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4">
       <c r="A62">
         <v>7</v>
       </c>
@@ -3509,7 +4093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4">
       <c r="A63">
         <v>7</v>
       </c>
@@ -3523,7 +4107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4">
       <c r="A64">
         <v>7</v>
       </c>
@@ -3537,7 +4121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4">
       <c r="A65">
         <v>7</v>
       </c>
@@ -3551,7 +4135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4">
       <c r="A66">
         <v>7</v>
       </c>
@@ -3565,7 +4149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4">
       <c r="A67">
         <v>7</v>
       </c>
@@ -3579,7 +4163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4">
       <c r="A68">
         <v>7</v>
       </c>
@@ -3593,7 +4177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4">
       <c r="A69">
         <v>7</v>
       </c>
@@ -3607,7 +4191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4">
       <c r="A70">
         <v>7</v>
       </c>
@@ -3621,7 +4205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4">
       <c r="A71">
         <v>7</v>
       </c>
@@ -3635,7 +4219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4">
       <c r="A72">
         <v>8</v>
       </c>
@@ -3649,7 +4233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4">
       <c r="A73">
         <v>8</v>
       </c>
@@ -3663,7 +4247,7 @@
         <v>9120</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4">
       <c r="A74">
         <v>8</v>
       </c>
@@ -3677,7 +4261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4">
       <c r="A75">
         <v>8</v>
       </c>
@@ -3691,7 +4275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4">
       <c r="A76">
         <v>8</v>
       </c>
@@ -3705,7 +4289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4">
       <c r="A77">
         <v>8</v>
       </c>
@@ -3719,7 +4303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4">
       <c r="A78">
         <v>8</v>
       </c>
@@ -3733,7 +4317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4">
       <c r="A79">
         <v>8</v>
       </c>
@@ -3747,7 +4331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4">
       <c r="A80">
         <v>8</v>
       </c>
@@ -3761,7 +4345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4">
       <c r="A81">
         <v>8</v>
       </c>
@@ -3775,7 +4359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4">
       <c r="A82">
         <v>9</v>
       </c>
@@ -3789,7 +4373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4">
       <c r="A83">
         <v>9</v>
       </c>
@@ -3803,7 +4387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4">
       <c r="A84">
         <v>9</v>
       </c>
@@ -3817,7 +4401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4">
       <c r="A85">
         <v>9</v>
       </c>
@@ -3831,7 +4415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4">
       <c r="A86">
         <v>9</v>
       </c>
@@ -3845,7 +4429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4">
       <c r="A87">
         <v>9</v>
       </c>
@@ -3859,7 +4443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4">
       <c r="A88">
         <v>9</v>
       </c>
@@ -3873,7 +4457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4">
       <c r="A89">
         <v>9</v>
       </c>
@@ -3887,7 +4471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4">
       <c r="A90">
         <v>9</v>
       </c>
@@ -3901,7 +4485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4">
       <c r="A91">
         <v>9</v>
       </c>
@@ -3915,7 +4499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4">
       <c r="A92">
         <v>10</v>
       </c>
@@ -3929,7 +4513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4">
       <c r="A93">
         <v>10</v>
       </c>
@@ -3943,7 +4527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4">
       <c r="A94">
         <v>10</v>
       </c>
@@ -3957,7 +4541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4">
       <c r="A95">
         <v>10</v>
       </c>
@@ -3971,7 +4555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4">
       <c r="A96">
         <v>10</v>
       </c>
@@ -3985,7 +4569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:4">
       <c r="A97">
         <v>10</v>
       </c>
@@ -3999,7 +4583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:4">
       <c r="A98">
         <v>10</v>
       </c>
@@ -4013,7 +4597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:4">
       <c r="A99">
         <v>10</v>
       </c>
@@ -4027,7 +4611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:4">
       <c r="A100">
         <v>10</v>
       </c>
@@ -4041,7 +4625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:4">
       <c r="A101">
         <v>10</v>
       </c>
@@ -4055,7 +4639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:4">
       <c r="A102">
         <v>11</v>
       </c>
@@ -4069,7 +4653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:4">
       <c r="A103">
         <v>11</v>
       </c>
@@ -4083,7 +4667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:4">
       <c r="A104">
         <v>11</v>
       </c>
@@ -4097,7 +4681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:4">
       <c r="A105">
         <v>11</v>
       </c>
@@ -4111,7 +4695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:4">
       <c r="A106">
         <v>11</v>
       </c>
@@ -4125,7 +4709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:4">
       <c r="A107">
         <v>11</v>
       </c>
@@ -4139,7 +4723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:4">
       <c r="A108">
         <v>11</v>
       </c>
@@ -4153,7 +4737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:4">
       <c r="A109">
         <v>11</v>
       </c>
@@ -4167,7 +4751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:4">
       <c r="A110">
         <v>11</v>
       </c>
@@ -4181,7 +4765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:4">
       <c r="A111">
         <v>11</v>
       </c>
@@ -4195,7 +4779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:4">
       <c r="A112">
         <v>11</v>
       </c>
@@ -4210,91 +4794,92 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="3"/>
   <cols>
-    <col min="3" max="3" width="20.54296875" customWidth="1"/>
-    <col min="4" max="4" width="45.1796875" customWidth="1"/>
+    <col min="3" max="3" width="20.5454545454545" customWidth="1"/>
+    <col min="4" max="4" width="45.1818181818182" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C1" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="39" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" ht="39" spans="1:4">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="39" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" ht="39" spans="1:4">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="39" x14ac:dyDescent="0.2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" ht="39" spans="1:4">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="39" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" ht="39" spans="1:4">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="52" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" ht="52" spans="1:4">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4305,95 +4890,95 @@
         <v>76</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="39" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" ht="39" spans="1:4">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="52" x14ac:dyDescent="0.2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" ht="52" spans="1:4">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="52" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" ht="52" spans="1:4">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="39" x14ac:dyDescent="0.2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" ht="39" spans="1:4">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="39" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11" ht="39" spans="1:4">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="52" x14ac:dyDescent="0.2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" ht="52" spans="1:4">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="7820"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="98">
   <si>
     <t>Id</t>
   </si>
@@ -61,6 +61,9 @@
     <t>InitMov</t>
   </si>
   <si>
+    <t>InitCost</t>
+  </si>
+  <si>
     <t>GrowthHp</t>
   </si>
   <si>
@@ -77,6 +80,9 @@
   </si>
   <si>
     <t>GrowthMov</t>
+  </si>
+  <si>
+    <t>GrowthCost</t>
   </si>
   <si>
     <t>Element1</t>
@@ -326,10 +332,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -348,7 +354,37 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -361,10 +397,41 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -376,38 +443,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -423,31 +461,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -455,37 +476,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -500,7 +506,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,13 +560,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +590,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -560,37 +644,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -602,85 +680,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -691,47 +697,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -754,7 +719,55 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -776,18 +789,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -799,145 +805,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1444,7 +1450,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AH12"/>
+  <dimension ref="A1:AJ12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="3" max="3" width="11.6363636363636" customWidth="1"/>
@@ -1456,10 +1462,10 @@
     <col min="9" max="9" width="6.45454545454545" customWidth="1"/>
     <col min="10" max="10" width="6.63636363636364" customWidth="1"/>
     <col min="11" max="12" width="7.09090909090909" customWidth="1"/>
-    <col min="13" max="14" width="7.36363636363636" customWidth="1"/>
+    <col min="13" max="15" width="7.36363636363636" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:36">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1502,7 +1508,7 @@
       <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="3" t="s">
         <v>13</v>
       </c>
       <c r="P1" t="s">
@@ -1517,13 +1523,13 @@
       <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="3" t="s">
         <v>20</v>
       </c>
       <c r="W1" t="s">
@@ -1562,8 +1568,14 @@
       <c r="AH1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2" spans="1:34">
+      <c r="AI1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1582,7 +1594,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -1594,7 +1606,7 @@
         <v>39</v>
       </c>
       <c r="J2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K2">
         <v>30</v>
@@ -1609,67 +1621,73 @@
         <v>3</v>
       </c>
       <c r="O2">
+        <v>10</v>
+      </c>
+      <c r="P2">
         <v>55</v>
       </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
       <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
         <v>60</v>
       </c>
-      <c r="R2">
+      <c r="S2">
         <v>30</v>
       </c>
-      <c r="S2">
+      <c r="T2">
         <v>35</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>1</v>
+      </c>
+      <c r="X2">
         <v>2</v>
-      </c>
-      <c r="W2">
-        <v>6</v>
-      </c>
-      <c r="X2">
-        <v>3</v>
       </c>
       <c r="Y2">
         <v>6</v>
       </c>
       <c r="Z2">
-        <v>-10</v>
+        <v>3</v>
       </c>
       <c r="AA2">
-        <v>-54</v>
+        <v>6</v>
       </c>
       <c r="AB2">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF2">
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:34">
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:36">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1688,7 +1706,7 @@
         <v>2</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -1700,7 +1718,7 @@
         <v>29</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K3">
         <v>21</v>
@@ -1715,67 +1733,73 @@
         <v>4</v>
       </c>
       <c r="O3">
+        <v>10</v>
+      </c>
+      <c r="P3">
         <v>60</v>
       </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
       <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
         <v>40</v>
       </c>
-      <c r="R3">
+      <c r="S3">
         <v>25</v>
       </c>
-      <c r="S3">
+      <c r="T3">
         <v>70</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
         <v>2</v>
       </c>
-      <c r="V3">
-        <v>1</v>
-      </c>
-      <c r="W3">
+      <c r="X3">
+        <v>1</v>
+      </c>
+      <c r="Y3">
         <v>5</v>
       </c>
-      <c r="X3">
+      <c r="Z3">
         <v>7</v>
       </c>
-      <c r="Y3">
+      <c r="AA3">
         <v>3</v>
       </c>
-      <c r="Z3">
-        <v>-20</v>
-      </c>
-      <c r="AA3">
-        <v>-52</v>
-      </c>
       <c r="AB3">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="AC3">
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF3">
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:34">
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1794,7 +1818,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -1806,7 +1830,7 @@
         <v>35</v>
       </c>
       <c r="J4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K4">
         <v>17</v>
@@ -1821,67 +1845,73 @@
         <v>3</v>
       </c>
       <c r="O4">
+        <v>10</v>
+      </c>
+      <c r="P4">
         <v>85</v>
       </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
       <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
         <v>25</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <v>50</v>
       </c>
-      <c r="S4">
+      <c r="T4">
         <v>25</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
         <v>3</v>
       </c>
-      <c r="V4">
+      <c r="X4">
         <v>6</v>
       </c>
-      <c r="W4">
-        <v>1</v>
-      </c>
-      <c r="X4">
+      <c r="Y4">
+        <v>1</v>
+      </c>
+      <c r="Z4">
         <v>2</v>
       </c>
-      <c r="Y4">
+      <c r="AA4">
         <v>6</v>
       </c>
-      <c r="Z4">
+      <c r="AB4">
         <v>-10</v>
       </c>
-      <c r="AA4">
+      <c r="AC4">
         <v>-64</v>
       </c>
-      <c r="AB4">
+      <c r="AD4">
         <v>0.82</v>
       </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
       <c r="AE4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF4">
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:34">
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1900,7 +1930,7 @@
         <v>4</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1912,7 +1942,7 @@
         <v>32</v>
       </c>
       <c r="J5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K5">
         <v>15</v>
@@ -1927,67 +1957,73 @@
         <v>3</v>
       </c>
       <c r="O5">
+        <v>10</v>
+      </c>
+      <c r="P5">
         <v>85</v>
       </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
       <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
         <v>35</v>
       </c>
-      <c r="R5">
+      <c r="S5">
         <v>15</v>
       </c>
-      <c r="S5">
+      <c r="T5">
         <v>30</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
         <v>4</v>
       </c>
-      <c r="V5">
+      <c r="X5">
         <v>3</v>
       </c>
-      <c r="W5">
+      <c r="Y5">
         <v>3</v>
       </c>
-      <c r="X5">
-        <v>1</v>
-      </c>
-      <c r="Y5">
+      <c r="Z5">
+        <v>1</v>
+      </c>
+      <c r="AA5">
         <v>7</v>
       </c>
-      <c r="Z5">
+      <c r="AB5">
         <v>-4</v>
       </c>
-      <c r="AA5">
+      <c r="AC5">
         <v>-68</v>
       </c>
-      <c r="AB5">
+      <c r="AD5">
         <v>0.8</v>
       </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
       <c r="AE5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF5">
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:34">
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2006,7 +2042,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -2018,7 +2054,7 @@
         <v>29</v>
       </c>
       <c r="J6">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K6">
         <v>12</v>
@@ -2033,67 +2069,73 @@
         <v>3</v>
       </c>
       <c r="O6">
+        <v>10</v>
+      </c>
+      <c r="P6">
         <v>70</v>
       </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
       <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
         <v>30</v>
       </c>
-      <c r="R6">
+      <c r="S6">
         <v>40</v>
       </c>
-      <c r="S6">
+      <c r="T6">
         <v>45</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
         <v>4</v>
       </c>
-      <c r="V6">
+      <c r="X6">
         <v>6</v>
       </c>
-      <c r="W6">
+      <c r="Y6">
         <v>2</v>
       </c>
-      <c r="X6">
+      <c r="Z6">
         <v>5</v>
       </c>
-      <c r="Y6">
-        <v>1</v>
-      </c>
-      <c r="Z6">
+      <c r="AA6">
+        <v>1</v>
+      </c>
+      <c r="AB6">
         <v>-8</v>
       </c>
-      <c r="AA6">
+      <c r="AC6">
         <v>-44</v>
       </c>
-      <c r="AB6">
+      <c r="AD6">
         <v>0.82</v>
       </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
       <c r="AE6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF6">
         <v>0</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:34">
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:36">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2112,7 +2154,7 @@
         <v>6</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -2124,7 +2166,7 @@
         <v>30</v>
       </c>
       <c r="J7">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K7">
         <v>20</v>
@@ -2139,13 +2181,13 @@
         <v>3</v>
       </c>
       <c r="O7">
+        <v>10</v>
+      </c>
+      <c r="P7">
         <v>40</v>
       </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
       <c r="Q7">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R7">
         <v>50</v>
@@ -2154,52 +2196,58 @@
         <v>50</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="U7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X7">
         <v>6</v>
       </c>
       <c r="Y7">
+        <v>2</v>
+      </c>
+      <c r="Z7">
+        <v>6</v>
+      </c>
+      <c r="AA7">
         <v>3</v>
       </c>
-      <c r="Z7">
+      <c r="AB7">
         <v>48</v>
       </c>
-      <c r="AA7">
+      <c r="AC7">
         <v>-68</v>
       </c>
-      <c r="AB7">
+      <c r="AD7">
         <v>0.76</v>
       </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
       <c r="AE7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF7">
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:34">
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:36">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2218,7 +2266,7 @@
         <v>7</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -2230,7 +2278,7 @@
         <v>40</v>
       </c>
       <c r="J8">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K8">
         <v>22</v>
@@ -2245,67 +2293,73 @@
         <v>4</v>
       </c>
       <c r="O8">
+        <v>10</v>
+      </c>
+      <c r="P8">
         <v>65</v>
       </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
       <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
         <v>45</v>
       </c>
-      <c r="R8">
+      <c r="S8">
         <v>40</v>
       </c>
-      <c r="S8">
+      <c r="T8">
         <v>30</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W8">
         <v>4</v>
       </c>
       <c r="X8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y8">
         <v>4</v>
       </c>
       <c r="Z8">
+        <v>3</v>
+      </c>
+      <c r="AA8">
+        <v>4</v>
+      </c>
+      <c r="AB8">
         <v>-20</v>
       </c>
-      <c r="AA8">
+      <c r="AC8">
         <v>-60</v>
       </c>
-      <c r="AB8">
+      <c r="AD8">
         <v>0.79</v>
       </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
       <c r="AE8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF8">
         <v>0</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:34">
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2324,7 +2378,7 @@
         <v>8</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -2336,7 +2390,7 @@
         <v>37</v>
       </c>
       <c r="J9">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K9">
         <v>15</v>
@@ -2351,67 +2405,73 @@
         <v>3</v>
       </c>
       <c r="O9">
+        <v>10</v>
+      </c>
+      <c r="P9">
         <v>80</v>
       </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
       <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
         <v>40</v>
       </c>
-      <c r="R9">
+      <c r="S9">
         <v>60</v>
       </c>
-      <c r="S9">
+      <c r="T9">
         <v>35</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
       <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
         <v>6</v>
       </c>
-      <c r="V9">
+      <c r="X9">
         <v>2</v>
       </c>
-      <c r="W9">
-        <v>1</v>
-      </c>
-      <c r="X9">
+      <c r="Y9">
+        <v>1</v>
+      </c>
+      <c r="Z9">
         <v>5</v>
       </c>
-      <c r="Y9">
+      <c r="AA9">
         <v>4</v>
       </c>
-      <c r="Z9">
+      <c r="AB9">
         <v>-52</v>
       </c>
-      <c r="AA9">
+      <c r="AC9">
         <v>-52</v>
       </c>
-      <c r="AB9">
+      <c r="AD9">
         <v>0.8</v>
       </c>
-      <c r="AC9">
-        <v>0</v>
-      </c>
-      <c r="AD9">
-        <v>0</v>
-      </c>
       <c r="AE9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF9">
         <v>0</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:34">
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2430,7 +2490,7 @@
         <v>9</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -2442,7 +2502,7 @@
         <v>34</v>
       </c>
       <c r="J10">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K10">
         <v>25</v>
@@ -2457,67 +2517,73 @@
         <v>3</v>
       </c>
       <c r="O10">
+        <v>10</v>
+      </c>
+      <c r="P10">
         <v>25</v>
       </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
       <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
         <v>65</v>
       </c>
-      <c r="R10">
+      <c r="S10">
         <v>30</v>
       </c>
-      <c r="S10">
+      <c r="T10">
         <v>50</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
       <c r="U10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>1</v>
+      </c>
+      <c r="X10">
         <v>4</v>
       </c>
-      <c r="W10">
+      <c r="Y10">
         <v>4</v>
       </c>
-      <c r="X10">
+      <c r="Z10">
         <v>7</v>
       </c>
-      <c r="Y10">
+      <c r="AA10">
         <v>2</v>
       </c>
-      <c r="Z10">
+      <c r="AB10">
         <v>-16</v>
       </c>
-      <c r="AA10">
+      <c r="AC10">
         <v>-52</v>
       </c>
-      <c r="AB10">
+      <c r="AD10">
         <v>0.75</v>
       </c>
-      <c r="AC10">
-        <v>0</v>
-      </c>
-      <c r="AD10">
-        <v>0</v>
-      </c>
       <c r="AE10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF10">
         <v>0</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:34">
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:36">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2536,7 +2602,7 @@
         <v>10</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -2548,7 +2614,7 @@
         <v>30</v>
       </c>
       <c r="J11">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K11">
         <v>17</v>
@@ -2563,67 +2629,73 @@
         <v>4</v>
       </c>
       <c r="O11">
+        <v>10</v>
+      </c>
+      <c r="P11">
         <v>45</v>
       </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
       <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
         <v>30</v>
       </c>
-      <c r="R11">
+      <c r="S11">
         <v>20</v>
       </c>
-      <c r="S11">
+      <c r="T11">
         <v>75</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
       <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
         <v>4</v>
       </c>
-      <c r="V11">
-        <v>1</v>
-      </c>
-      <c r="W11">
+      <c r="X11">
+        <v>1</v>
+      </c>
+      <c r="Y11">
         <v>6</v>
       </c>
-      <c r="X11">
+      <c r="Z11">
         <v>5</v>
       </c>
-      <c r="Y11">
+      <c r="AA11">
         <v>2</v>
       </c>
-      <c r="Z11">
+      <c r="AB11">
         <v>12</v>
       </c>
-      <c r="AA11">
+      <c r="AC11">
         <v>-64</v>
       </c>
-      <c r="AB11">
+      <c r="AD11">
         <v>0.77</v>
       </c>
-      <c r="AC11">
-        <v>0</v>
-      </c>
-      <c r="AD11">
-        <v>0</v>
-      </c>
       <c r="AE11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF11">
         <v>0</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:34">
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:36">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2642,7 +2714,7 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -2654,7 +2726,7 @@
         <v>33</v>
       </c>
       <c r="J12">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K12">
         <v>21</v>
@@ -2669,63 +2741,69 @@
         <v>3</v>
       </c>
       <c r="O12">
+        <v>10</v>
+      </c>
+      <c r="P12">
         <v>65</v>
       </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
       <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
         <v>40</v>
       </c>
-      <c r="R12">
+      <c r="S12">
         <v>25</v>
       </c>
-      <c r="S12">
+      <c r="T12">
         <v>30</v>
       </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
       <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
         <v>6</v>
       </c>
-      <c r="V12">
+      <c r="X12">
         <v>6</v>
       </c>
-      <c r="W12">
-        <v>1</v>
-      </c>
-      <c r="X12">
+      <c r="Y12">
+        <v>1</v>
+      </c>
+      <c r="Z12">
         <v>3</v>
       </c>
-      <c r="Y12">
+      <c r="AA12">
         <v>2</v>
       </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-      <c r="AA12">
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
         <v>-54</v>
       </c>
-      <c r="AB12">
+      <c r="AD12">
         <v>0.87</v>
       </c>
-      <c r="AC12">
-        <v>0</v>
-      </c>
-      <c r="AD12">
-        <v>0</v>
-      </c>
       <c r="AE12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF12">
         <v>0</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
         <v>0</v>
       </c>
     </row>
@@ -2747,13 +2825,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2761,7 +2839,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -2805,7 +2883,7 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2846,7 +2924,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2887,7 +2965,7 @@
         <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2928,7 +3006,7 @@
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2969,7 +3047,7 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -3010,7 +3088,7 @@
         <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -3051,7 +3129,7 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -3092,7 +3170,7 @@
         <v>9</v>
       </c>
       <c r="B34" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -3133,7 +3211,7 @@
         <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -3174,7 +3252,7 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -3227,16 +3305,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -4814,13 +4892,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" ht="39" spans="1:4">
@@ -4828,13 +4906,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" ht="39" spans="1:4">
@@ -4842,13 +4920,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" ht="39" spans="1:4">
@@ -4856,13 +4934,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" ht="39" spans="1:4">
@@ -4870,13 +4948,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" ht="52" spans="1:4">
@@ -4884,13 +4962,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" ht="39" spans="1:4">
@@ -4898,13 +4976,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" ht="52" spans="1:4">
@@ -4912,13 +4990,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" ht="52" spans="1:4">
@@ -4926,13 +5004,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" ht="39" spans="1:4">
@@ -4940,13 +5018,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" ht="39" spans="1:4">
@@ -4954,13 +5032,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" ht="52" spans="1:4">
@@ -4968,13 +5046,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -332,10 +332,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -353,10 +353,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -367,11 +368,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -382,16 +382,25 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -406,15 +415,22 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -444,14 +460,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -461,14 +469,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -482,16 +483,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -512,19 +512,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +536,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -554,67 +578,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -632,13 +596,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -650,31 +662,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -686,7 +686,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -719,16 +719,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -757,17 +763,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -786,17 +797,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -808,142 +808,142 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1890,7 +1890,7 @@
         <v>-64</v>
       </c>
       <c r="AD4">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AE4">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         <v>-68</v>
       </c>
       <c r="AD5">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AE5">
         <v>0</v>
@@ -2114,7 +2114,7 @@
         <v>-44</v>
       </c>
       <c r="AD6">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AE6">
         <v>0</v>
@@ -2226,7 +2226,7 @@
         <v>-68</v>
       </c>
       <c r="AD7">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="AE7">
         <v>0</v>
@@ -2338,7 +2338,7 @@
         <v>-60</v>
       </c>
       <c r="AD8">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="AE8">
         <v>0</v>
@@ -2450,7 +2450,7 @@
         <v>-52</v>
       </c>
       <c r="AD9">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AE9">
         <v>0</v>
@@ -2562,7 +2562,7 @@
         <v>-52</v>
       </c>
       <c r="AD10">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AE10">
         <v>0</v>
@@ -2674,7 +2674,7 @@
         <v>-64</v>
       </c>
       <c r="AD11">
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="AE11">
         <v>0</v>
@@ -2786,7 +2786,7 @@
         <v>-54</v>
       </c>
       <c r="AD12">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AE12">
         <v>0</v>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -332,10 +332,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -353,16 +353,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -376,17 +368,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -414,9 +412,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -431,13 +436,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -468,8 +466,16 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -477,21 +483,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -506,7 +506,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,7 +542,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,31 +614,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,49 +632,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -626,25 +674,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -656,37 +686,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -715,15 +715,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -735,6 +726,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -756,9 +756,20 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -768,17 +779,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -805,46 +805,46 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -853,97 +853,97 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1678,7 +1678,7 @@
         <v>1</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI2">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>1</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI3">
         <v>0</v>
@@ -1902,7 +1902,7 @@
         <v>1</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI4">
         <v>0</v>
@@ -2014,7 +2014,7 @@
         <v>1</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI5">
         <v>0</v>
@@ -2126,7 +2126,7 @@
         <v>1</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI6">
         <v>0</v>
@@ -2238,7 +2238,7 @@
         <v>1</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI7">
         <v>0</v>
@@ -2350,7 +2350,7 @@
         <v>1</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI8">
         <v>0</v>
@@ -2462,7 +2462,7 @@
         <v>1</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI9">
         <v>0</v>
@@ -2574,7 +2574,7 @@
         <v>1</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI10">
         <v>0</v>
@@ -2686,7 +2686,7 @@
         <v>1</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI11">
         <v>0</v>
@@ -2798,7 +2798,7 @@
         <v>1</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI12">
         <v>0</v>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -333,8 +333,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -353,8 +353,54 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -368,29 +414,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -404,6 +436,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -413,55 +453,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -473,9 +467,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -491,7 +491,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -506,43 +506,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -554,37 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -602,19 +560,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -626,19 +578,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -656,19 +638,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -686,7 +668,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -697,6 +697,26 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -730,6 +750,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -756,47 +791,12 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -805,145 +805,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1621,7 +1621,7 @@
         <v>3</v>
       </c>
       <c r="O2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P2">
         <v>55</v>
@@ -1733,7 +1733,7 @@
         <v>4</v>
       </c>
       <c r="O3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P3">
         <v>60</v>
@@ -1845,7 +1845,7 @@
         <v>3</v>
       </c>
       <c r="O4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P4">
         <v>85</v>
@@ -1957,7 +1957,7 @@
         <v>3</v>
       </c>
       <c r="O5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P5">
         <v>85</v>
@@ -2069,7 +2069,7 @@
         <v>3</v>
       </c>
       <c r="O6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P6">
         <v>70</v>
@@ -2181,7 +2181,7 @@
         <v>3</v>
       </c>
       <c r="O7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P7">
         <v>40</v>
@@ -2293,7 +2293,7 @@
         <v>4</v>
       </c>
       <c r="O8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P8">
         <v>65</v>
@@ -2405,7 +2405,7 @@
         <v>3</v>
       </c>
       <c r="O9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P9">
         <v>80</v>
@@ -2517,7 +2517,7 @@
         <v>3</v>
       </c>
       <c r="O10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P10">
         <v>25</v>
@@ -2629,7 +2629,7 @@
         <v>4</v>
       </c>
       <c r="O11">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P11">
         <v>45</v>
@@ -2741,7 +2741,7 @@
         <v>3</v>
       </c>
       <c r="O12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P12">
         <v>65</v>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -172,7 +172,7 @@
     <t>11,21,31,1010,1060,100110,100120</t>
   </si>
   <si>
-    <t>11,21,31,2010,2070,100210,100220</t>
+    <t>11,21,31,2010,12010,100210,100220</t>
   </si>
   <si>
     <t>11,21,31,3010,3020,100310,100320</t>
@@ -332,10 +332,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -355,24 +355,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -384,9 +377,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -394,13 +401,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -420,24 +420,32 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -452,23 +460,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -483,15 +477,21 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -506,13 +506,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,25 +584,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -560,7 +632,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,7 +644,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -584,7 +662,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -596,97 +680,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -697,6 +697,69 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -720,36 +783,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -764,39 +797,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -805,145 +805,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1603,7 +1603,7 @@
         <v>99</v>
       </c>
       <c r="I2">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="J2">
         <v>4</v>
@@ -1624,7 +1624,7 @@
         <v>6</v>
       </c>
       <c r="P2">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -1715,7 +1715,7 @@
         <v>99</v>
       </c>
       <c r="I3">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J3">
         <v>5</v>
@@ -1736,7 +1736,7 @@
         <v>6</v>
       </c>
       <c r="P3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="Q3">
         <v>0</v>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -334,8 +334,8 @@
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -353,59 +353,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -420,9 +367,99 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -438,38 +475,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -478,20 +492,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -506,13 +506,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,91 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -626,7 +560,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -638,31 +656,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -674,19 +686,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -700,11 +700,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -724,6 +730,24 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -739,26 +763,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -769,15 +778,6 @@
         <color theme="4"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -805,145 +805,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1642,7 +1642,7 @@
         <v>0</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W2">
         <v>1</v>
@@ -1754,7 +1754,7 @@
         <v>0</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W3">
         <v>2</v>
@@ -1866,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W4">
         <v>3</v>
@@ -1978,7 +1978,7 @@
         <v>0</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W5">
         <v>4</v>
@@ -2090,7 +2090,7 @@
         <v>0</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W6">
         <v>4</v>
@@ -2202,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W7">
         <v>1</v>
@@ -2314,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W8">
         <v>4</v>
@@ -2426,7 +2426,7 @@
         <v>0</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W9">
         <v>6</v>
@@ -2538,7 +2538,7 @@
         <v>0</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W10">
         <v>1</v>
@@ -2650,7 +2650,7 @@
         <v>0</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W11">
         <v>4</v>
@@ -2762,7 +2762,7 @@
         <v>0</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W12">
         <v>6</v>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -332,9 +332,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -354,14 +354,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -371,6 +371,14 @@
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -390,8 +398,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -404,14 +413,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -421,7 +422,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -451,8 +452,32 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -465,33 +490,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -506,13 +506,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,37 +530,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -566,19 +566,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -596,7 +584,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -608,13 +596,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -626,19 +626,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -650,43 +656,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -730,24 +730,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -766,19 +748,26 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -797,6 +786,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -805,16 +805,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -823,127 +823,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1624,7 +1624,7 @@
         <v>6</v>
       </c>
       <c r="P2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="Q2">
         <v>0</v>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -175,7 +175,7 @@
     <t>11,21,31,2010,12010,100210,100220</t>
   </si>
   <si>
-    <t>11,21,31,3010,3020,100310,100320</t>
+    <t>11,21,31,3010,3030,100310,100320</t>
   </si>
   <si>
     <t>11,21,31,4010,4030,100410,100420</t>
@@ -332,9 +332,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -360,15 +360,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -382,9 +391,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -398,14 +437,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -414,15 +445,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -443,33 +474,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -477,21 +483,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -506,7 +506,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,13 +548,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,19 +656,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -560,73 +668,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -638,55 +680,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -700,74 +700,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -797,6 +734,69 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -805,16 +805,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -823,127 +823,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1827,7 +1827,7 @@
         <v>99</v>
       </c>
       <c r="I4">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -1839,7 +1839,7 @@
         <v>17</v>
       </c>
       <c r="M4">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="N4">
         <v>3</v>
@@ -1848,19 +1848,19 @@
         <v>6</v>
       </c>
       <c r="P4">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="Q4">
         <v>0</v>
       </c>
       <c r="R4">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="S4">
         <v>50</v>
       </c>
       <c r="T4">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="U4">
         <v>0</v>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -333,9 +333,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -360,11 +360,63 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -383,24 +435,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -414,68 +459,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -490,8 +475,23 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -506,7 +506,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,7 +590,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,157 +680,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -697,41 +697,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -769,16 +734,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -797,6 +753,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -805,7 +805,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -814,7 +814,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -823,127 +823,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1884,10 +1884,10 @@
         <v>6</v>
       </c>
       <c r="AB4">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="AC4">
-        <v>-64</v>
+        <v>0</v>
       </c>
       <c r="AD4">
         <v>1</v>
@@ -1996,10 +1996,10 @@
         <v>7</v>
       </c>
       <c r="AB5">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AC5">
-        <v>-68</v>
+        <v>0</v>
       </c>
       <c r="AD5">
         <v>1</v>
@@ -2108,10 +2108,10 @@
         <v>1</v>
       </c>
       <c r="AB6">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="AC6">
-        <v>-44</v>
+        <v>0</v>
       </c>
       <c r="AD6">
         <v>1</v>
@@ -2220,10 +2220,10 @@
         <v>3</v>
       </c>
       <c r="AB7">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AC7">
-        <v>-68</v>
+        <v>0</v>
       </c>
       <c r="AD7">
         <v>1</v>
@@ -2332,10 +2332,10 @@
         <v>4</v>
       </c>
       <c r="AB8">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AC8">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="AD8">
         <v>1</v>
@@ -2444,10 +2444,10 @@
         <v>4</v>
       </c>
       <c r="AB9">
-        <v>-52</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>-52</v>
+        <v>0</v>
       </c>
       <c r="AD9">
         <v>1</v>
@@ -2556,10 +2556,10 @@
         <v>2</v>
       </c>
       <c r="AB10">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>-52</v>
+        <v>0</v>
       </c>
       <c r="AD10">
         <v>1</v>
@@ -2668,10 +2668,10 @@
         <v>2</v>
       </c>
       <c r="AB11">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>-64</v>
+        <v>0</v>
       </c>
       <c r="AD11">
         <v>1</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="AC12">
-        <v>-54</v>
+        <v>0</v>
       </c>
       <c r="AD12">
         <v>1</v>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -332,9 +332,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
@@ -360,8 +360,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -369,14 +407,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -389,8 +420,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -405,10 +444,33 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -434,68 +496,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -506,7 +506,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,61 +644,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -584,109 +680,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -697,6 +697,24 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -711,6 +729,17 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -768,35 +797,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -805,145 +805,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1715,16 +1715,16 @@
         <v>99</v>
       </c>
       <c r="I3">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J3">
         <v>5</v>
       </c>
       <c r="K3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3">
         <v>28</v>
@@ -1939,7 +1939,7 @@
         <v>99</v>
       </c>
       <c r="I5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -1948,10 +1948,10 @@
         <v>15</v>
       </c>
       <c r="L5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N5">
         <v>3</v>
@@ -1960,7 +1960,7 @@
         <v>6</v>
       </c>
       <c r="P5">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1969,10 +1969,10 @@
         <v>35</v>
       </c>
       <c r="S5">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="T5">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="U5">
         <v>0</v>
@@ -2051,19 +2051,19 @@
         <v>99</v>
       </c>
       <c r="I6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J6">
         <v>4</v>
       </c>
       <c r="K6">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="L6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="N6">
         <v>3</v>
@@ -2078,10 +2078,10 @@
         <v>0</v>
       </c>
       <c r="R6">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="S6">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="T6">
         <v>45</v>
@@ -2169,10 +2169,10 @@
         <v>4</v>
       </c>
       <c r="K7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L7">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="M7">
         <v>20</v>
@@ -2184,7 +2184,7 @@
         <v>6</v>
       </c>
       <c r="P7">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -2275,16 +2275,16 @@
         <v>99</v>
       </c>
       <c r="I8">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="J8">
         <v>4</v>
       </c>
       <c r="K8">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L8">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="M8">
         <v>16</v>
@@ -2296,19 +2296,19 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="Q8">
         <v>0</v>
       </c>
       <c r="R8">
+        <v>50</v>
+      </c>
+      <c r="S8">
         <v>45</v>
       </c>
-      <c r="S8">
-        <v>40</v>
-      </c>
       <c r="T8">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="U8">
         <v>0</v>
@@ -2387,19 +2387,19 @@
         <v>99</v>
       </c>
       <c r="I9">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J9">
         <v>4</v>
       </c>
       <c r="K9">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L9">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M9">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N9">
         <v>3</v>
@@ -2408,16 +2408,16 @@
         <v>6</v>
       </c>
       <c r="P9">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="Q9">
         <v>0</v>
       </c>
       <c r="R9">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="S9">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="T9">
         <v>35</v>
@@ -2499,7 +2499,7 @@
         <v>99</v>
       </c>
       <c r="I10">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="J10">
         <v>4</v>
@@ -2508,10 +2508,10 @@
         <v>25</v>
       </c>
       <c r="L10">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M10">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N10">
         <v>3</v>
@@ -2520,13 +2520,13 @@
         <v>6</v>
       </c>
       <c r="P10">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="Q10">
         <v>0</v>
       </c>
       <c r="R10">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="S10">
         <v>30</v>
@@ -2611,7 +2611,7 @@
         <v>99</v>
       </c>
       <c r="I11">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J11">
         <v>4</v>
@@ -2632,19 +2632,19 @@
         <v>6</v>
       </c>
       <c r="P11">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="Q11">
         <v>0</v>
       </c>
       <c r="R11">
+        <v>35</v>
+      </c>
+      <c r="S11">
         <v>30</v>
       </c>
-      <c r="S11">
-        <v>20</v>
-      </c>
       <c r="T11">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="U11">
         <v>0</v>
@@ -2723,19 +2723,19 @@
         <v>99</v>
       </c>
       <c r="I12">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J12">
         <v>4</v>
       </c>
       <c r="K12">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L12">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M12">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N12">
         <v>3</v>
@@ -2753,10 +2753,10 @@
         <v>40</v>
       </c>
       <c r="S12">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="T12">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="U12">
         <v>0</v>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820"/>
+    <workbookView windowWidth="19200" windowHeight="7820" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -217,7 +217,7 @@
     <t>Feature</t>
   </si>
   <si>
-    <t>ミカ</t>
+    <t>ロジーナ</t>
   </si>
   <si>
     <t>【煉獄棘姫】</t>
@@ -333,9 +333,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -353,24 +353,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -383,23 +383,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -413,8 +413,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -429,7 +430,36 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -444,23 +474,8 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -468,30 +483,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -506,7 +506,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,19 +674,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,145 +686,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -697,24 +697,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -733,13 +715,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -768,6 +754,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -783,17 +789,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -805,16 +805,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -823,127 +823,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="C2" t="str">
         <f>INDEX(TextData!B:B,MATCH(B2,TextData!A:A))</f>
-        <v>ミカ</v>
+        <v>ロジーナ</v>
       </c>
       <c r="D2" t="str">
         <f>INDEX([1]TextData!C:C,MATCH(B2,[1]TextData!A:A))</f>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820" activeTab="3"/>
+    <workbookView windowWidth="19200" windowHeight="7820"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -332,10 +332,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -353,9 +353,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -370,7 +377,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -383,23 +390,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -408,14 +408,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -444,7 +436,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -452,14 +452,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -475,7 +476,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -483,15 +484,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -506,7 +506,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,7 +530,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,13 +632,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,49 +668,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -602,91 +686,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -697,36 +697,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -754,13 +724,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -770,6 +744,21 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -797,6 +786,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -805,145 +805,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1624,19 +1624,19 @@
         <v>6</v>
       </c>
       <c r="P2">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="Q2">
         <v>0</v>
       </c>
       <c r="R2">
+        <v>90</v>
+      </c>
+      <c r="S2">
         <v>60</v>
       </c>
-      <c r="S2">
-        <v>30</v>
-      </c>
       <c r="T2">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="U2">
         <v>0</v>
@@ -1736,19 +1736,19 @@
         <v>6</v>
       </c>
       <c r="P3">
-        <v>65</v>
+        <v>115</v>
       </c>
       <c r="Q3">
         <v>0</v>
       </c>
       <c r="R3">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="S3">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="T3">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="U3">
         <v>0</v>
@@ -1848,19 +1848,19 @@
         <v>6</v>
       </c>
       <c r="P4">
+        <v>130</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>60</v>
+      </c>
+      <c r="S4">
         <v>80</v>
       </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>30</v>
-      </c>
-      <c r="S4">
-        <v>50</v>
-      </c>
       <c r="T4">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="U4">
         <v>0</v>
@@ -1960,19 +1960,19 @@
         <v>6</v>
       </c>
       <c r="P5">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="Q5">
         <v>0</v>
       </c>
       <c r="R5">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="S5">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="T5">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="U5">
         <v>0</v>
@@ -2072,19 +2072,19 @@
         <v>6</v>
       </c>
       <c r="P6">
+        <v>120</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
         <v>70</v>
       </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>40</v>
-      </c>
       <c r="S6">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="T6">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="U6">
         <v>0</v>
@@ -2184,19 +2184,19 @@
         <v>6</v>
       </c>
       <c r="P7">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q7">
         <v>0</v>
       </c>
       <c r="R7">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="S7">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="T7">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U7">
         <v>0</v>
@@ -2296,19 +2296,19 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="Q8">
         <v>0</v>
       </c>
       <c r="R8">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="S8">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="T8">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="U8">
         <v>0</v>
@@ -2408,19 +2408,19 @@
         <v>6</v>
       </c>
       <c r="P9">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="Q9">
         <v>0</v>
       </c>
       <c r="R9">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="S9">
+        <v>95</v>
+      </c>
+      <c r="T9">
         <v>65</v>
-      </c>
-      <c r="T9">
-        <v>35</v>
       </c>
       <c r="U9">
         <v>0</v>
@@ -2520,19 +2520,19 @@
         <v>6</v>
       </c>
       <c r="P10">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="Q10">
         <v>0</v>
       </c>
       <c r="R10">
+        <v>110</v>
+      </c>
+      <c r="S10">
+        <v>60</v>
+      </c>
+      <c r="T10">
         <v>80</v>
-      </c>
-      <c r="S10">
-        <v>30</v>
-      </c>
-      <c r="T10">
-        <v>50</v>
       </c>
       <c r="U10">
         <v>0</v>
@@ -2632,19 +2632,19 @@
         <v>6</v>
       </c>
       <c r="P11">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q11">
         <v>0</v>
       </c>
       <c r="R11">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="S11">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="T11">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="U11">
         <v>0</v>
@@ -2744,19 +2744,19 @@
         <v>6</v>
       </c>
       <c r="P12">
+        <v>115</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>70</v>
+      </c>
+      <c r="S12">
         <v>65</v>
       </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <v>40</v>
-      </c>
-      <c r="S12">
-        <v>35</v>
-      </c>
       <c r="T12">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U12">
         <v>0</v>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -332,10 +332,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -353,26 +353,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -390,16 +374,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -410,14 +402,6 @@
       <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -442,6 +426,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -452,17 +444,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -484,14 +476,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -506,7 +506,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,7 +518,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,25 +542,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -560,7 +560,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -584,7 +590,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -596,31 +608,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -632,19 +656,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -662,31 +680,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -717,8 +717,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -748,21 +750,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -782,18 +769,31 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -805,145 +805,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1621,7 +1621,7 @@
         <v>3</v>
       </c>
       <c r="O2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P2">
         <v>135</v>
@@ -1733,7 +1733,7 @@
         <v>4</v>
       </c>
       <c r="O3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P3">
         <v>115</v>
@@ -1845,7 +1845,7 @@
         <v>3</v>
       </c>
       <c r="O4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P4">
         <v>130</v>
@@ -1957,7 +1957,7 @@
         <v>3</v>
       </c>
       <c r="O5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P5">
         <v>140</v>
@@ -2069,7 +2069,7 @@
         <v>3</v>
       </c>
       <c r="O6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P6">
         <v>120</v>
@@ -2181,7 +2181,7 @@
         <v>3</v>
       </c>
       <c r="O7">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P7">
         <v>100</v>
@@ -2293,7 +2293,7 @@
         <v>4</v>
       </c>
       <c r="O8">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P8">
         <v>120</v>
@@ -2405,7 +2405,7 @@
         <v>3</v>
       </c>
       <c r="O9">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P9">
         <v>120</v>
@@ -2517,7 +2517,7 @@
         <v>3</v>
       </c>
       <c r="O10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P10">
         <v>90</v>
@@ -2629,7 +2629,7 @@
         <v>4</v>
       </c>
       <c r="O11">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -2741,7 +2741,7 @@
         <v>3</v>
       </c>
       <c r="O12">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P12">
         <v>115</v>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -332,10 +332,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -353,8 +353,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,6 +398,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -382,16 +420,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -412,46 +443,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -459,7 +460,7 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -476,22 +477,21 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -506,7 +506,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,7 +524,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,7 +548,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +608,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -554,85 +662,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -644,43 +680,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -701,27 +701,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -741,26 +730,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -768,8 +748,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -797,6 +777,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -805,145 +805,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1884,13 +1884,13 @@
         <v>6</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC4">
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE4">
         <v>0</v>
@@ -1996,13 +1996,13 @@
         <v>7</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AD5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE5">
         <v>0</v>
@@ -2111,7 +2111,7 @@
         <v>0</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="AD6">
         <v>1</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AD7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE7">
         <v>0</v>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -12,15 +12,12 @@
     <sheet name="SkillTrigger" sheetId="4" r:id="rId3"/>
     <sheet name="TextData" sheetId="2" r:id="rId4"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId5"/>
-  </externalReferences>
   <calcPr calcId="144525" concurrentCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="105">
   <si>
     <t>Id</t>
   </si>
@@ -31,7 +28,7 @@
     <t>_</t>
   </si>
   <si>
-    <t>ClassId</t>
+    <t>Rank</t>
   </si>
   <si>
     <t>ImagePath</t>
@@ -160,6 +157,12 @@
     <t>0011</t>
   </si>
   <si>
+    <t>0101</t>
+  </si>
+  <si>
+    <t>0102</t>
+  </si>
+  <si>
     <t>ActorId</t>
   </si>
   <si>
@@ -200,6 +203,9 @@
   </si>
   <si>
     <t>11,21,31,3010,3050,101110,101120</t>
+  </si>
+  <si>
+    <t>11,21,31,3010,3080,100310,100320</t>
   </si>
   <si>
     <t>TriggerType1</t>
@@ -325,6 +331,18 @@
   <si>
     <t>凍結攻撃を主体とするアタッカー。
 「ディープフリーズ」で攻撃時に一定量のダメージを受ける「凍結」状態にし、凍結効果をさらにアップすることで自滅に追い込むことができる。</t>
+  </si>
+  <si>
+    <t>シグルド</t>
+  </si>
+  <si>
+    <t>【竜殺し】</t>
+  </si>
+  <si>
+    <t>ブリュンヒルデ</t>
+  </si>
+  <si>
+    <t>【悲劇の戦乙女】</t>
   </si>
 </sst>
 </file>
@@ -332,10 +350,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -353,46 +371,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -406,7 +386,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -415,14 +395,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -443,6 +415,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -451,8 +430,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -460,7 +477,7 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -477,21 +494,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -506,7 +524,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,13 +596,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,157 +704,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -697,36 +715,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -745,20 +733,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -781,8 +766,41 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -805,145 +823,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1019,148 +1037,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Actors"/>
-      <sheetName val="Learning"/>
-      <sheetName val="SkillTrigger"/>
-      <sheetName val="TextData"/>
-      <sheetName val="TextDat"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3">
-        <row r="1">
-          <cell r="A1" t="str">
-            <v>Id</v>
-          </cell>
-        </row>
-        <row r="1">
-          <cell r="C1" t="str">
-            <v>SubName</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="A2">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="C2" t="str">
-            <v>【煉獄棘姫】</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="C3" t="str">
-            <v>【ChargeCommander】</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="C4" t="str">
-            <v>【怠惰な守護少女】</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="C5" t="str">
-            <v>【イノセント・リメディ】</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="C6" t="str">
-            <v>【Self-sacrifice】</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7">
-            <v>6</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="C7" t="str">
-            <v>【Faked-Magician】</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8">
-            <v>7</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="C8" t="str">
-            <v>【奇跡の乙女】</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9">
-            <v>8</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="C9" t="str">
-            <v>【唯心の在処】</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10">
-            <v>9</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="C10" t="str">
-            <v>【黄昏ニヒリスト】</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11">
-            <v>10</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="C11" t="str">
-            <v>【怨嗟の鎖】</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12">
-            <v>11</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="C12" t="str">
-            <v>【氷雪の勿忘草】</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="4" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1450,7 +1326,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AJ12"/>
+  <dimension ref="A1:AJ14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="3" max="3" width="11.6363636363636" customWidth="1"/>
@@ -1587,11 +1463,11 @@
         <v>ロジーナ</v>
       </c>
       <c r="D2" t="str">
-        <f>INDEX([1]TextData!C:C,MATCH(B2,[1]TextData!A:A))</f>
+        <f>INDEX(TextData!C:C,MATCH(B2,TextData!A:A))</f>
         <v>【煉獄棘姫】</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>35</v>
@@ -1699,11 +1575,11 @@
         <v>エリザベート</v>
       </c>
       <c r="D3" t="str">
-        <f>INDEX([1]TextData!C:C,MATCH(B3,[1]TextData!A:A))</f>
+        <f>INDEX(TextData!C:C,MATCH(B3,TextData!A:A))</f>
         <v>【ChargeCommander】</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>36</v>
@@ -1811,11 +1687,11 @@
         <v>アリエス</v>
       </c>
       <c r="D4" t="str">
-        <f>INDEX([1]TextData!C:C,MATCH(B4,[1]TextData!A:A))</f>
+        <f>INDEX(TextData!C:C,MATCH(B4,TextData!A:A))</f>
         <v>【怠惰な守護少女】</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>37</v>
@@ -1923,11 +1799,11 @@
         <v>シイナ</v>
       </c>
       <c r="D5" t="str">
-        <f>INDEX([1]TextData!C:C,MATCH(B5,[1]TextData!A:A))</f>
+        <f>INDEX(TextData!C:C,MATCH(B5,TextData!A:A))</f>
         <v>【イノセント・リメディ】</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>38</v>
@@ -2035,11 +1911,11 @@
         <v>レダ</v>
       </c>
       <c r="D6" t="str">
-        <f>INDEX([1]TextData!C:C,MATCH(B6,[1]TextData!A:A))</f>
+        <f>INDEX(TextData!C:C,MATCH(B6,TextData!A:A))</f>
         <v>【Self-sacrifice】</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>39</v>
@@ -2147,11 +2023,11 @@
         <v>リシェリ</v>
       </c>
       <c r="D7" t="str">
-        <f>INDEX([1]TextData!C:C,MATCH(B7,[1]TextData!A:A))</f>
+        <f>INDEX(TextData!C:C,MATCH(B7,TextData!A:A))</f>
         <v>【Faked-Magician】</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>40</v>
@@ -2259,11 +2135,11 @@
         <v>ユニ</v>
       </c>
       <c r="D8" t="str">
-        <f>INDEX([1]TextData!C:C,MATCH(B8,[1]TextData!A:A))</f>
+        <f>INDEX(TextData!C:C,MATCH(B8,TextData!A:A))</f>
         <v>【奇跡の乙女】</v>
       </c>
       <c r="E8">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>41</v>
@@ -2371,11 +2247,11 @@
         <v>マリーベル</v>
       </c>
       <c r="D9" t="str">
-        <f>INDEX([1]TextData!C:C,MATCH(B9,[1]TextData!A:A))</f>
+        <f>INDEX(TextData!C:C,MATCH(B9,TextData!A:A))</f>
         <v>【唯心の在処】</v>
       </c>
       <c r="E9">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>42</v>
@@ -2483,11 +2359,11 @@
         <v>ナツキ</v>
       </c>
       <c r="D10" t="str">
-        <f>INDEX([1]TextData!C:C,MATCH(B10,[1]TextData!A:A))</f>
+        <f>INDEX(TextData!C:C,MATCH(B10,TextData!A:A))</f>
         <v>【黄昏ニヒリスト】</v>
       </c>
       <c r="E10">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>43</v>
@@ -2595,11 +2471,11 @@
         <v>メリアドール</v>
       </c>
       <c r="D11" t="str">
-        <f>INDEX([1]TextData!C:C,MATCH(B11,[1]TextData!A:A))</f>
+        <f>INDEX(TextData!C:C,MATCH(B11,TextData!A:A))</f>
         <v>【怨嗟の鎖】</v>
       </c>
       <c r="E11">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>44</v>
@@ -2707,11 +2583,11 @@
         <v>セリナ</v>
       </c>
       <c r="D12" t="str">
-        <f>INDEX([1]TextData!C:C,MATCH(B12,[1]TextData!A:A))</f>
+        <f>INDEX(TextData!C:C,MATCH(B12,TextData!A:A))</f>
         <v>【氷雪の勿忘草】</v>
       </c>
       <c r="E12">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>45</v>
@@ -2804,6 +2680,230 @@
         <v>0</v>
       </c>
       <c r="AJ12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:36">
+      <c r="A13">
+        <v>101</v>
+      </c>
+      <c r="B13">
+        <v>101</v>
+      </c>
+      <c r="C13" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B13,TextData!A:A))</f>
+        <v>シグルド</v>
+      </c>
+      <c r="D13" t="str">
+        <f>INDEX(TextData!C:C,MATCH(B13,TextData!A:A))</f>
+        <v>【竜殺し】</v>
+      </c>
+      <c r="E13">
+        <v>10</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>99</v>
+      </c>
+      <c r="I13">
+        <v>38</v>
+      </c>
+      <c r="J13">
+        <v>4</v>
+      </c>
+      <c r="K13">
+        <v>24</v>
+      </c>
+      <c r="L13">
+        <v>15</v>
+      </c>
+      <c r="M13">
+        <v>15</v>
+      </c>
+      <c r="N13">
+        <v>3</v>
+      </c>
+      <c r="O13">
+        <v>2</v>
+      </c>
+      <c r="P13">
+        <v>145</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>70</v>
+      </c>
+      <c r="S13">
+        <v>65</v>
+      </c>
+      <c r="T13">
+        <v>60</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>50</v>
+      </c>
+      <c r="W13">
+        <v>4</v>
+      </c>
+      <c r="X13">
+        <v>5</v>
+      </c>
+      <c r="Y13">
+        <v>1</v>
+      </c>
+      <c r="Z13">
+        <v>2</v>
+      </c>
+      <c r="AA13">
+        <v>7</v>
+      </c>
+      <c r="AB13">
+        <v>40</v>
+      </c>
+      <c r="AC13">
+        <v>-40</v>
+      </c>
+      <c r="AD13">
+        <v>1</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>1</v>
+      </c>
+      <c r="AH13">
+        <v>2</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36">
+      <c r="A14">
+        <v>102</v>
+      </c>
+      <c r="B14">
+        <v>102</v>
+      </c>
+      <c r="C14" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B14,TextData!A:A))</f>
+        <v>ブリュンヒルデ</v>
+      </c>
+      <c r="D14" t="str">
+        <f>INDEX(TextData!C:C,MATCH(B14,TextData!A:A))</f>
+        <v>【悲劇の戦乙女】</v>
+      </c>
+      <c r="E14">
+        <v>10</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>99</v>
+      </c>
+      <c r="I14">
+        <v>34</v>
+      </c>
+      <c r="J14">
+        <v>4</v>
+      </c>
+      <c r="K14">
+        <v>32</v>
+      </c>
+      <c r="L14">
+        <v>6</v>
+      </c>
+      <c r="M14">
+        <v>25</v>
+      </c>
+      <c r="N14">
+        <v>4</v>
+      </c>
+      <c r="O14">
+        <v>2</v>
+      </c>
+      <c r="P14">
+        <v>120</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>90</v>
+      </c>
+      <c r="S14">
+        <v>50</v>
+      </c>
+      <c r="T14">
+        <v>120</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>50</v>
+      </c>
+      <c r="W14">
+        <v>3</v>
+      </c>
+      <c r="X14">
+        <v>3</v>
+      </c>
+      <c r="Y14">
+        <v>5</v>
+      </c>
+      <c r="Z14">
+        <v>4</v>
+      </c>
+      <c r="AA14">
+        <v>1</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>1</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>1</v>
+      </c>
+      <c r="AH14">
+        <v>4</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
         <v>0</v>
       </c>
     </row>
@@ -2817,7 +2917,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="44.2727272727273" style="2" customWidth="1"/>
@@ -2825,13 +2925,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2839,7 +2939,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -2883,7 +2983,7 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2924,7 +3024,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2965,7 +3065,7 @@
         <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -3006,7 +3106,7 @@
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3047,7 +3147,7 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -3088,7 +3188,7 @@
         <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -3129,7 +3229,7 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -3170,7 +3270,7 @@
         <v>9</v>
       </c>
       <c r="B34" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -3211,7 +3311,7 @@
         <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -3252,7 +3352,7 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -3285,6 +3385,88 @@
         <v>3080</v>
       </c>
       <c r="C45">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>101</v>
+      </c>
+      <c r="B46" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47">
+        <v>101</v>
+      </c>
+      <c r="B47">
+        <v>13080</v>
+      </c>
+      <c r="C47">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48">
+        <v>101</v>
+      </c>
+      <c r="B48">
+        <v>403010</v>
+      </c>
+      <c r="C48">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49">
+        <v>101</v>
+      </c>
+      <c r="B49">
+        <v>3040</v>
+      </c>
+      <c r="C49">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>102</v>
+      </c>
+      <c r="B50" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51">
+        <v>102</v>
+      </c>
+      <c r="B51">
+        <v>13090</v>
+      </c>
+      <c r="C51">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52">
+        <v>102</v>
+      </c>
+      <c r="B52">
+        <v>403050</v>
+      </c>
+      <c r="C52">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53">
+        <v>102</v>
+      </c>
+      <c r="B53">
+        <v>3080</v>
+      </c>
+      <c r="C53">
         <v>41</v>
       </c>
     </row>
@@ -3297,7 +3479,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D112"/>
+  <dimension ref="A1:D132"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="3"/>
   <cols>
     <col min="3" max="4" width="12.9090909090909" customWidth="1"/>
@@ -3305,16 +3487,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -4868,6 +5050,286 @@
         <v>0</v>
       </c>
       <c r="D112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113">
+        <v>101</v>
+      </c>
+      <c r="B113">
+        <v>3080</v>
+      </c>
+      <c r="C113">
+        <v>0</v>
+      </c>
+      <c r="D113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114">
+        <v>101</v>
+      </c>
+      <c r="B114">
+        <v>100320</v>
+      </c>
+      <c r="C114">
+        <v>0</v>
+      </c>
+      <c r="D114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115">
+        <v>101</v>
+      </c>
+      <c r="B115">
+        <v>3010</v>
+      </c>
+      <c r="C115">
+        <v>0</v>
+      </c>
+      <c r="D115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116">
+        <v>101</v>
+      </c>
+      <c r="B116">
+        <v>100310</v>
+      </c>
+      <c r="C116">
+        <v>0</v>
+      </c>
+      <c r="D116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117">
+        <v>101</v>
+      </c>
+      <c r="B117">
+        <v>0</v>
+      </c>
+      <c r="C117">
+        <v>0</v>
+      </c>
+      <c r="D117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118">
+        <v>101</v>
+      </c>
+      <c r="B118">
+        <v>0</v>
+      </c>
+      <c r="C118">
+        <v>0</v>
+      </c>
+      <c r="D118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119">
+        <v>101</v>
+      </c>
+      <c r="B119">
+        <v>0</v>
+      </c>
+      <c r="C119">
+        <v>0</v>
+      </c>
+      <c r="D119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120">
+        <v>101</v>
+      </c>
+      <c r="B120">
+        <v>0</v>
+      </c>
+      <c r="C120">
+        <v>0</v>
+      </c>
+      <c r="D120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121">
+        <v>101</v>
+      </c>
+      <c r="B121">
+        <v>0</v>
+      </c>
+      <c r="C121">
+        <v>0</v>
+      </c>
+      <c r="D121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122">
+        <v>101</v>
+      </c>
+      <c r="B122">
+        <v>0</v>
+      </c>
+      <c r="C122">
+        <v>0</v>
+      </c>
+      <c r="D122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123">
+        <v>102</v>
+      </c>
+      <c r="B123">
+        <v>100520</v>
+      </c>
+      <c r="C123">
+        <v>0</v>
+      </c>
+      <c r="D123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124">
+        <v>102</v>
+      </c>
+      <c r="B124">
+        <v>5070</v>
+      </c>
+      <c r="C124">
+        <v>0</v>
+      </c>
+      <c r="D124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125">
+        <v>102</v>
+      </c>
+      <c r="B125">
+        <v>5010</v>
+      </c>
+      <c r="C125">
+        <v>0</v>
+      </c>
+      <c r="D125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126">
+        <v>102</v>
+      </c>
+      <c r="B126">
+        <v>100510</v>
+      </c>
+      <c r="C126">
+        <v>0</v>
+      </c>
+      <c r="D126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127">
+        <v>102</v>
+      </c>
+      <c r="B127">
+        <v>0</v>
+      </c>
+      <c r="C127">
+        <v>0</v>
+      </c>
+      <c r="D127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128">
+        <v>102</v>
+      </c>
+      <c r="B128">
+        <v>0</v>
+      </c>
+      <c r="C128">
+        <v>0</v>
+      </c>
+      <c r="D128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129">
+        <v>102</v>
+      </c>
+      <c r="B129">
+        <v>0</v>
+      </c>
+      <c r="C129">
+        <v>0</v>
+      </c>
+      <c r="D129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130">
+        <v>102</v>
+      </c>
+      <c r="B130">
+        <v>0</v>
+      </c>
+      <c r="C130">
+        <v>0</v>
+      </c>
+      <c r="D130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131">
+        <v>102</v>
+      </c>
+      <c r="B131">
+        <v>0</v>
+      </c>
+      <c r="C131">
+        <v>0</v>
+      </c>
+      <c r="D131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132">
+        <v>102</v>
+      </c>
+      <c r="B132">
+        <v>0</v>
+      </c>
+      <c r="C132">
+        <v>0</v>
+      </c>
+      <c r="D132">
         <v>0</v>
       </c>
     </row>
@@ -4880,7 +5342,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="3"/>
   <cols>
     <col min="3" max="3" width="20.5454545454545" customWidth="1"/>
@@ -4892,13 +5354,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" ht="39" spans="1:4">
@@ -4906,13 +5368,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" ht="39" spans="1:4">
@@ -4920,13 +5382,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" ht="39" spans="1:4">
@@ -4934,13 +5396,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" ht="39" spans="1:4">
@@ -4948,13 +5410,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" ht="52" spans="1:4">
@@ -4962,13 +5424,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" ht="39" spans="1:4">
@@ -4976,13 +5438,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" ht="52" spans="1:4">
@@ -4990,13 +5452,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" ht="52" spans="1:4">
@@ -5004,13 +5466,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" ht="39" spans="1:4">
@@ -5018,13 +5480,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" ht="39" spans="1:4">
@@ -5032,13 +5494,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" ht="52" spans="1:4">
@@ -5046,13 +5508,41 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" ht="39" spans="1:4">
+      <c r="A13">
+        <v>101</v>
+      </c>
+      <c r="B13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" t="s">
+        <v>102</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" ht="39" spans="1:4">
+      <c r="A14">
+        <v>102</v>
+      </c>
+      <c r="B14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14" t="s">
+        <v>104</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -351,9 +351,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -372,14 +372,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -400,6 +393,43 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -410,28 +440,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -453,31 +461,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -494,9 +479,25 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -507,9 +508,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -524,7 +524,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +644,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -560,49 +674,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -614,97 +704,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -715,6 +715,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -729,45 +738,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -796,11 +766,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -815,6 +791,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -823,145 +823,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1536,13 +1536,13 @@
         <v>6</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>-28</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
@@ -1648,13 +1648,13 @@
         <v>3</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AC3">
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
@@ -1760,13 +1760,13 @@
         <v>6</v>
       </c>
       <c r="AB4">
-        <v>12</v>
+        <v>-24</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="AD4">
-        <v>0.97</v>
+        <v>0.77</v>
       </c>
       <c r="AE4">
         <v>0</v>
@@ -1878,7 +1878,7 @@
         <v>16</v>
       </c>
       <c r="AD5">
-        <v>0.97</v>
+        <v>0.77</v>
       </c>
       <c r="AE5">
         <v>0</v>
@@ -2768,13 +2768,13 @@
         <v>7</v>
       </c>
       <c r="AB13">
-        <v>40</v>
+        <v>-20</v>
       </c>
       <c r="AC13">
-        <v>-40</v>
+        <v>-64</v>
       </c>
       <c r="AD13">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AE13">
         <v>0</v>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -205,7 +205,7 @@
     <t>11,21,31,3010,3050,101110,101120</t>
   </si>
   <si>
-    <t>11,21,31,3010,3080,100310,100320</t>
+    <t>11,21,31,3010,13100,100310,100320</t>
   </si>
   <si>
     <t>TriggerType1</t>
@@ -350,10 +350,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -372,28 +372,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -401,7 +379,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -416,7 +394,45 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -445,6 +461,28 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -462,16 +500,8 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -479,37 +509,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -524,7 +524,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,7 +554,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,19 +644,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,139 +704,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -721,8 +721,17 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -738,30 +747,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -795,8 +780,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -823,145 +823,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1536,7 +1536,7 @@
         <v>6</v>
       </c>
       <c r="AB2">
-        <v>-28</v>
+        <v>-12</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         <v>3</v>
       </c>
       <c r="AB3">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -1760,7 +1760,7 @@
         <v>6</v>
       </c>
       <c r="AB4">
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="AC4">
         <v>-16</v>
@@ -1990,7 +1990,7 @@
         <v>-24</v>
       </c>
       <c r="AD6">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AE6">
         <v>0</v>
@@ -2102,7 +2102,7 @@
         <v>16</v>
       </c>
       <c r="AD7">
-        <v>0.97</v>
+        <v>0.77</v>
       </c>
       <c r="AE7">
         <v>0</v>
@@ -2768,7 +2768,7 @@
         <v>7</v>
       </c>
       <c r="AB13">
-        <v>-20</v>
+        <v>-4</v>
       </c>
       <c r="AC13">
         <v>-64</v>
@@ -5058,7 +5058,7 @@
         <v>101</v>
       </c>
       <c r="B113">
-        <v>3080</v>
+        <v>3010</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -5086,7 +5086,7 @@
         <v>101</v>
       </c>
       <c r="B115">
-        <v>3010</v>
+        <v>13100</v>
       </c>
       <c r="C115">
         <v>0</v>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="2"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -172,40 +172,40 @@
     <t>Level</t>
   </si>
   <si>
-    <t>11,21,31,1010,1060,100110,100120</t>
-  </si>
-  <si>
-    <t>11,21,31,2010,12010,100210,100220</t>
-  </si>
-  <si>
-    <t>11,21,31,3010,3030,100310,100320</t>
-  </si>
-  <si>
-    <t>11,21,31,4010,4030,100410,100420</t>
+    <t>11,21,31,1010,100110,100120</t>
+  </si>
+  <si>
+    <t>11,21,31,2010,100210,100220</t>
+  </si>
+  <si>
+    <t>11,21,31,3010,100310,100320</t>
+  </si>
+  <si>
+    <t>11,21,31,4010,100410,100420</t>
+  </si>
+  <si>
+    <t>11,21,31,5010,100510,100520</t>
+  </si>
+  <si>
+    <t>11,21,31,1010,100610,100620</t>
+  </si>
+  <si>
+    <t>11,21,31,2010,100710,100720</t>
+  </si>
+  <si>
+    <t>11,21,31,3010,100810,100820</t>
+  </si>
+  <si>
+    <t>11,21,31,1010,100910,100920</t>
+  </si>
+  <si>
+    <t>11,21,31,2010,101010,101020</t>
+  </si>
+  <si>
+    <t>11,21,31,3010,101110,101120</t>
   </si>
   <si>
     <t>11,21,31,5010,5070,100510,100520</t>
-  </si>
-  <si>
-    <t>11,21,31,1010,1030,100610,100620</t>
-  </si>
-  <si>
-    <t>11,21,31,2010,2040,100710,100720</t>
-  </si>
-  <si>
-    <t>11,21,31,3010,3070,100810,100820</t>
-  </si>
-  <si>
-    <t>11,21,31,1010,1050,100910,100920</t>
-  </si>
-  <si>
-    <t>11,21,31,2010,2030,101010,101020</t>
-  </si>
-  <si>
-    <t>11,21,31,3010,3050,101110,101120</t>
-  </si>
-  <si>
-    <t>11,21,31,3010,13100,100310,100320</t>
   </si>
   <si>
     <t>TriggerType1</t>
@@ -350,10 +350,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -372,14 +372,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -394,6 +403,74 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -401,7 +478,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -416,15 +493,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -445,75 +514,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -524,7 +524,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,19 +614,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -560,13 +632,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,49 +674,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -632,61 +686,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -698,13 +698,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -718,20 +718,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -747,6 +759,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -768,10 +789,8 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -786,32 +805,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -823,145 +823,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="S2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="T2">
         <v>65</v>
@@ -1618,13 +1618,13 @@
         <v>0</v>
       </c>
       <c r="R3">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="S3">
         <v>55</v>
       </c>
       <c r="T3">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="U3">
         <v>0</v>
@@ -1836,7 +1836,7 @@
         <v>2</v>
       </c>
       <c r="P5">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="R6">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="S6">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="T6">
         <v>75</v>
@@ -2514,13 +2514,13 @@
         <v>0</v>
       </c>
       <c r="R11">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="S11">
         <v>60</v>
       </c>
       <c r="T11">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="U11">
         <v>0</v>
@@ -2720,10 +2720,10 @@
         <v>24</v>
       </c>
       <c r="L13">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M13">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N13">
         <v>3</v>
@@ -2732,16 +2732,16 @@
         <v>2</v>
       </c>
       <c r="P13">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="Q13">
         <v>0</v>
       </c>
       <c r="R13">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="S13">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="T13">
         <v>60</v>
@@ -2786,7 +2786,7 @@
         <v>1</v>
       </c>
       <c r="AH13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI13">
         <v>0</v>
@@ -2898,7 +2898,7 @@
         <v>1</v>
       </c>
       <c r="AH14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI14">
         <v>0</v>
@@ -2917,7 +2917,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="44.2727272727273" style="2" customWidth="1"/>
@@ -2950,10 +2950,10 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>11060</v>
+        <v>1060</v>
       </c>
       <c r="C3">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2961,10 +2961,10 @@
         <v>1</v>
       </c>
       <c r="B4">
-        <v>401060</v>
+        <v>11060</v>
       </c>
       <c r="C4">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2972,29 +2972,29 @@
         <v>1</v>
       </c>
       <c r="B5">
+        <v>401060</v>
+      </c>
+      <c r="C5">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
         <v>1020</v>
       </c>
-      <c r="C5">
+      <c r="C6">
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:2">
       <c r="A7">
         <v>2</v>
       </c>
-      <c r="B7">
-        <v>12080</v>
-      </c>
-      <c r="C7">
-        <v>11</v>
+      <c r="B7" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3002,10 +3002,10 @@
         <v>2</v>
       </c>
       <c r="B8">
-        <v>12040</v>
+        <v>12010</v>
       </c>
       <c r="C8">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -3013,40 +3013,40 @@
         <v>2</v>
       </c>
       <c r="B9">
-        <v>2060</v>
+        <v>12080</v>
       </c>
       <c r="C9">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>53</v>
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>12040</v>
+      </c>
+      <c r="C10">
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11">
-        <v>13080</v>
+        <v>2060</v>
       </c>
       <c r="C11">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12">
         <v>3</v>
       </c>
-      <c r="B12">
-        <v>403010</v>
-      </c>
-      <c r="C12">
-        <v>26</v>
+      <c r="B12" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3054,67 +3054,70 @@
         <v>3</v>
       </c>
       <c r="B13">
-        <v>3040</v>
+        <v>3030</v>
       </c>
       <c r="C13">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14">
-        <v>4</v>
-      </c>
-      <c r="B14" t="s">
-        <v>54</v>
+        <v>3</v>
+      </c>
+      <c r="B14">
+        <v>13080</v>
+      </c>
+      <c r="C14">
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B15">
-        <v>14080</v>
+        <v>403010</v>
       </c>
       <c r="C15">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B16">
-        <v>404030</v>
+        <v>3040</v>
       </c>
       <c r="C16">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17">
         <v>4</v>
       </c>
-      <c r="B17">
-        <v>4060</v>
-      </c>
-      <c r="C17">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+      <c r="B17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18">
-        <v>5</v>
-      </c>
-      <c r="B18" t="s">
-        <v>55</v>
+        <v>4</v>
+      </c>
+      <c r="B18">
+        <v>4030</v>
+      </c>
+      <c r="C18">
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B19">
-        <v>15090</v>
+        <v>14080</v>
       </c>
       <c r="C19">
         <v>11</v>
@@ -3122,10 +3125,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B20">
-        <v>405070</v>
+        <v>404030</v>
       </c>
       <c r="C20">
         <v>26</v>
@@ -3133,10 +3136,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B21">
-        <v>5040</v>
+        <v>4060</v>
       </c>
       <c r="C21">
         <v>41</v>
@@ -3144,182 +3147,185 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B23">
-        <v>11040</v>
+        <v>5070</v>
       </c>
       <c r="C23">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B24">
-        <v>401030</v>
+        <v>15090</v>
       </c>
       <c r="C24">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
+        <v>5</v>
+      </c>
+      <c r="B25">
+        <v>405070</v>
+      </c>
+      <c r="C25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26">
+        <v>5</v>
+      </c>
+      <c r="B26">
+        <v>5040</v>
+      </c>
+      <c r="C26">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
         <v>6</v>
       </c>
-      <c r="B25">
-        <v>1070</v>
-      </c>
-      <c r="C25">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26">
-        <v>7</v>
-      </c>
-      <c r="B26" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27">
-        <v>7</v>
-      </c>
-      <c r="B27">
-        <v>12090</v>
-      </c>
-      <c r="C27">
-        <v>11</v>
+      <c r="B27" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B28">
-        <v>412090</v>
+        <v>1030</v>
       </c>
       <c r="C28">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B29">
-        <v>2050</v>
+        <v>11040</v>
       </c>
       <c r="C29">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30">
-        <v>8</v>
-      </c>
-      <c r="B30" t="s">
-        <v>58</v>
+        <v>6</v>
+      </c>
+      <c r="B30">
+        <v>401030</v>
+      </c>
+      <c r="C30">
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B31">
-        <v>13060</v>
+        <v>1070</v>
       </c>
       <c r="C31">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32">
-        <v>8</v>
-      </c>
-      <c r="B32">
-        <v>403070</v>
-      </c>
-      <c r="C32">
-        <v>26</v>
+        <v>7</v>
+      </c>
+      <c r="B32" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B33">
-        <v>3060</v>
+        <v>2040</v>
       </c>
       <c r="C33">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34">
-        <v>9</v>
-      </c>
-      <c r="B34" t="s">
-        <v>59</v>
+        <v>7</v>
+      </c>
+      <c r="B34">
+        <v>12090</v>
+      </c>
+      <c r="C34">
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B35">
-        <v>11070</v>
+        <v>412090</v>
       </c>
       <c r="C35">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B36">
-        <v>401050</v>
+        <v>2050</v>
       </c>
       <c r="C36">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37">
-        <v>9</v>
-      </c>
-      <c r="B37">
-        <v>1080</v>
-      </c>
-      <c r="C37">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
+        <v>8</v>
+      </c>
+      <c r="B37" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38">
-        <v>10</v>
-      </c>
-      <c r="B38" t="s">
-        <v>60</v>
+        <v>8</v>
+      </c>
+      <c r="B38">
+        <v>3070</v>
+      </c>
+      <c r="C38">
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B39">
-        <v>12010</v>
+        <v>13060</v>
       </c>
       <c r="C39">
         <v>11</v>
@@ -3327,10 +3333,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B40">
-        <v>402030</v>
+        <v>403070</v>
       </c>
       <c r="C40">
         <v>26</v>
@@ -3338,10 +3344,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B41">
-        <v>2080</v>
+        <v>3060</v>
       </c>
       <c r="C41">
         <v>41</v>
@@ -3349,124 +3355,261 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B42" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B43">
-        <v>13090</v>
+        <v>1050</v>
       </c>
       <c r="C43">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
+        <v>9</v>
+      </c>
+      <c r="B44">
+        <v>11070</v>
+      </c>
+      <c r="C44">
         <v>11</v>
-      </c>
-      <c r="B44">
-        <v>403050</v>
-      </c>
-      <c r="C44">
-        <v>26</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B45">
-        <v>3080</v>
+        <v>401050</v>
       </c>
       <c r="C45">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46">
+        <v>9</v>
+      </c>
+      <c r="B46">
+        <v>1080</v>
+      </c>
+      <c r="C46">
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
-      <c r="A46">
-        <v>101</v>
-      </c>
-      <c r="B46" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:2">
       <c r="A47">
-        <v>101</v>
-      </c>
-      <c r="B47">
-        <v>13080</v>
-      </c>
-      <c r="C47">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="B47" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="B48">
-        <v>403010</v>
+        <v>2030</v>
       </c>
       <c r="C48">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="B49">
-        <v>3040</v>
+        <v>12010</v>
       </c>
       <c r="C49">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50">
-        <v>102</v>
-      </c>
-      <c r="B50" t="s">
-        <v>55</v>
+        <v>10</v>
+      </c>
+      <c r="B50">
+        <v>402030</v>
+      </c>
+      <c r="C50">
+        <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>102</v>
+        <v>10</v>
       </c>
       <c r="B51">
-        <v>13090</v>
+        <v>2080</v>
       </c>
       <c r="C51">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
         <v>11</v>
       </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52">
-        <v>102</v>
-      </c>
-      <c r="B52">
-        <v>403050</v>
-      </c>
-      <c r="C52">
-        <v>26</v>
+      <c r="B52" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
+        <v>11</v>
+      </c>
+      <c r="B53">
+        <v>3050</v>
+      </c>
+      <c r="C53">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54">
+        <v>11</v>
+      </c>
+      <c r="B54">
+        <v>13090</v>
+      </c>
+      <c r="C54">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55">
+        <v>11</v>
+      </c>
+      <c r="B55">
+        <v>403050</v>
+      </c>
+      <c r="C55">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56">
+        <v>11</v>
+      </c>
+      <c r="B56">
+        <v>3080</v>
+      </c>
+      <c r="C56">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>101</v>
+      </c>
+      <c r="B57" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58">
+        <v>101</v>
+      </c>
+      <c r="B58">
+        <v>13100</v>
+      </c>
+      <c r="C58">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59">
+        <v>101</v>
+      </c>
+      <c r="B59">
+        <v>13080</v>
+      </c>
+      <c r="C59">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60">
+        <v>101</v>
+      </c>
+      <c r="B60">
+        <v>403010</v>
+      </c>
+      <c r="C60">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61">
+        <v>101</v>
+      </c>
+      <c r="B61">
+        <v>3040</v>
+      </c>
+      <c r="C61">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62">
         <v>102</v>
       </c>
-      <c r="B53">
+      <c r="B62" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63">
+        <v>102</v>
+      </c>
+      <c r="B63">
+        <v>5070</v>
+      </c>
+      <c r="C63">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64">
+        <v>102</v>
+      </c>
+      <c r="B64">
+        <v>13090</v>
+      </c>
+      <c r="C64">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65">
+        <v>102</v>
+      </c>
+      <c r="B65">
+        <v>403050</v>
+      </c>
+      <c r="C65">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66">
+        <v>102</v>
+      </c>
+      <c r="B66">
         <v>3080</v>
       </c>
-      <c r="C53">
+      <c r="C66">
         <v>41</v>
       </c>
     </row>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -350,10 +350,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -378,17 +378,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -402,15 +393,32 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -425,15 +433,60 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -454,64 +507,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -524,25 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -554,7 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -566,43 +548,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -620,13 +566,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -638,7 +602,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -656,55 +674,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -715,36 +715,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -767,7 +737,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -789,8 +759,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -805,13 +777,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -823,145 +823,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1512,7 +1512,7 @@
         <v>65</v>
       </c>
       <c r="T2">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="U2">
         <v>0</v>
@@ -1624,7 +1624,7 @@
         <v>55</v>
       </c>
       <c r="T3">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="U3">
         <v>0</v>
@@ -1736,7 +1736,7 @@
         <v>80</v>
       </c>
       <c r="T4">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="U4">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>60</v>
       </c>
       <c r="T5">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="U5">
         <v>0</v>
@@ -1960,7 +1960,7 @@
         <v>80</v>
       </c>
       <c r="T6">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="U6">
         <v>0</v>
@@ -2072,7 +2072,7 @@
         <v>80</v>
       </c>
       <c r="T7">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="U7">
         <v>0</v>
@@ -2184,7 +2184,7 @@
         <v>75</v>
       </c>
       <c r="T8">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="U8">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>95</v>
       </c>
       <c r="T9">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="U9">
         <v>0</v>
@@ -2408,7 +2408,7 @@
         <v>60</v>
       </c>
       <c r="T10">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="U10">
         <v>0</v>
@@ -2520,7 +2520,7 @@
         <v>60</v>
       </c>
       <c r="T11">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="U11">
         <v>0</v>
@@ -2632,7 +2632,7 @@
         <v>65</v>
       </c>
       <c r="T12">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="U12">
         <v>0</v>
@@ -2717,7 +2717,7 @@
         <v>4</v>
       </c>
       <c r="K13">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L13">
         <v>19</v>
@@ -2744,7 +2744,7 @@
         <v>80</v>
       </c>
       <c r="T13">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U13">
         <v>0</v>
@@ -2856,7 +2856,7 @@
         <v>50</v>
       </c>
       <c r="T14">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="U14">
         <v>0</v>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -371,22 +371,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -400,17 +401,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -424,16 +416,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -446,15 +438,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -469,10 +462,10 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -481,6 +474,14 @@
       <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -507,9 +508,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -524,25 +524,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -566,13 +572,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -584,13 +584,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -602,19 +608,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -638,19 +632,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -662,25 +674,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -704,7 +698,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -715,6 +715,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -729,15 +738,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -757,13 +757,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -773,6 +777,17 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -800,21 +815,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -823,7 +823,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -832,7 +832,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -841,127 +841,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
         <v>15</v>
       </c>
       <c r="M2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N2">
         <v>3</v>
@@ -2723,7 +2723,7 @@
         <v>19</v>
       </c>
       <c r="M13">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N13">
         <v>3</v>
@@ -2953,7 +2953,7 @@
         <v>1060</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3005,7 +3005,7 @@
         <v>12010</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -3057,7 +3057,7 @@
         <v>3030</v>
       </c>
       <c r="C13">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3109,7 +3109,7 @@
         <v>4030</v>
       </c>
       <c r="C18">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3161,7 +3161,7 @@
         <v>5070</v>
       </c>
       <c r="C23">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -3213,7 +3213,7 @@
         <v>1030</v>
       </c>
       <c r="C28">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -3265,7 +3265,7 @@
         <v>2040</v>
       </c>
       <c r="C33">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -3317,7 +3317,7 @@
         <v>3070</v>
       </c>
       <c r="C38">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -3369,7 +3369,7 @@
         <v>1050</v>
       </c>
       <c r="C43">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -3421,7 +3421,7 @@
         <v>2030</v>
       </c>
       <c r="C48">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -3473,7 +3473,7 @@
         <v>3050</v>
       </c>
       <c r="C53">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -3525,7 +3525,7 @@
         <v>13100</v>
       </c>
       <c r="C58">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -3577,7 +3577,7 @@
         <v>5070</v>
       </c>
       <c r="C63">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:3">

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -350,9 +350,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -371,46 +371,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -425,69 +387,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -503,6 +410,99 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -530,13 +530,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,25 +638,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,43 +686,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -626,85 +698,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -715,15 +715,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -781,17 +772,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -811,7 +791,27 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -823,16 +823,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -841,127 +841,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -352,8 +352,8 @@
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -372,17 +372,32 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -394,7 +409,38 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -409,44 +455,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -460,27 +469,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -494,22 +494,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -524,7 +524,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,19 +626,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -566,55 +680,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -626,85 +704,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -715,36 +715,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -766,32 +736,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -815,6 +776,45 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -823,145 +823,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2917,7 +2917,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="44.2727272727273" style="2" customWidth="1"/>
@@ -3035,29 +3035,29 @@
         <v>2</v>
       </c>
       <c r="B11">
+        <v>12041</v>
+      </c>
+      <c r="C11">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12">
         <v>2060</v>
       </c>
-      <c r="C11">
+      <c r="C12">
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:2">
       <c r="A13">
         <v>3</v>
       </c>
-      <c r="B13">
-        <v>3030</v>
-      </c>
-      <c r="C13">
-        <v>5</v>
+      <c r="B13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3065,10 +3065,10 @@
         <v>3</v>
       </c>
       <c r="B14">
-        <v>13080</v>
+        <v>3030</v>
       </c>
       <c r="C14">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -3076,10 +3076,10 @@
         <v>3</v>
       </c>
       <c r="B15">
-        <v>403010</v>
+        <v>13080</v>
       </c>
       <c r="C15">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -3087,40 +3087,40 @@
         <v>3</v>
       </c>
       <c r="B16">
-        <v>3040</v>
+        <v>13081</v>
       </c>
       <c r="C16">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17">
-        <v>4</v>
-      </c>
-      <c r="B17" t="s">
-        <v>54</v>
+        <v>3</v>
+      </c>
+      <c r="B17">
+        <v>403010</v>
+      </c>
+      <c r="C17">
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B18">
-        <v>4030</v>
+        <v>3040</v>
       </c>
       <c r="C18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19">
         <v>4</v>
       </c>
-      <c r="B19">
-        <v>14080</v>
-      </c>
-      <c r="C19">
-        <v>11</v>
+      <c r="B19" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -3128,10 +3128,10 @@
         <v>4</v>
       </c>
       <c r="B20">
-        <v>404030</v>
+        <v>4030</v>
       </c>
       <c r="C20">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3139,51 +3139,51 @@
         <v>4</v>
       </c>
       <c r="B21">
-        <v>4060</v>
+        <v>14080</v>
       </c>
       <c r="C21">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22">
-        <v>5</v>
-      </c>
-      <c r="B22" t="s">
-        <v>55</v>
+        <v>4</v>
+      </c>
+      <c r="B22">
+        <v>14081</v>
+      </c>
+      <c r="C22">
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B23">
-        <v>5070</v>
+        <v>404030</v>
       </c>
       <c r="C23">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B24">
-        <v>15090</v>
+        <v>4060</v>
       </c>
       <c r="C24">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25">
         <v>5</v>
       </c>
-      <c r="B25">
-        <v>405070</v>
-      </c>
-      <c r="C25">
-        <v>26</v>
+      <c r="B25" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -3191,51 +3191,51 @@
         <v>5</v>
       </c>
       <c r="B26">
-        <v>5040</v>
+        <v>5070</v>
       </c>
       <c r="C26">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27">
-        <v>6</v>
-      </c>
-      <c r="B27" t="s">
-        <v>56</v>
+        <v>5</v>
+      </c>
+      <c r="B27">
+        <v>15090</v>
+      </c>
+      <c r="C27">
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B28">
-        <v>1030</v>
+        <v>405070</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B29">
-        <v>11040</v>
+        <v>5040</v>
       </c>
       <c r="C29">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30">
         <v>6</v>
       </c>
-      <c r="B30">
-        <v>401030</v>
-      </c>
-      <c r="C30">
-        <v>26</v>
+      <c r="B30" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -3243,51 +3243,51 @@
         <v>6</v>
       </c>
       <c r="B31">
-        <v>1070</v>
+        <v>1030</v>
       </c>
       <c r="C31">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32">
-        <v>7</v>
-      </c>
-      <c r="B32" t="s">
-        <v>57</v>
+        <v>6</v>
+      </c>
+      <c r="B32">
+        <v>11040</v>
+      </c>
+      <c r="C32">
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B33">
-        <v>2040</v>
+        <v>401030</v>
       </c>
       <c r="C33">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B34">
-        <v>12090</v>
+        <v>1070</v>
       </c>
       <c r="C34">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35">
         <v>7</v>
       </c>
-      <c r="B35">
-        <v>412090</v>
-      </c>
-      <c r="C35">
-        <v>26</v>
+      <c r="B35" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -3295,51 +3295,51 @@
         <v>7</v>
       </c>
       <c r="B36">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C36">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37">
-        <v>8</v>
-      </c>
-      <c r="B37" t="s">
-        <v>58</v>
+        <v>7</v>
+      </c>
+      <c r="B37">
+        <v>12090</v>
+      </c>
+      <c r="C37">
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B38">
-        <v>3070</v>
+        <v>412090</v>
       </c>
       <c r="C38">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B39">
-        <v>13060</v>
+        <v>2050</v>
       </c>
       <c r="C39">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40">
         <v>8</v>
       </c>
-      <c r="B40">
-        <v>403070</v>
-      </c>
-      <c r="C40">
-        <v>26</v>
+      <c r="B40" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -3347,51 +3347,51 @@
         <v>8</v>
       </c>
       <c r="B41">
-        <v>3060</v>
+        <v>3070</v>
       </c>
       <c r="C41">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42">
-        <v>9</v>
-      </c>
-      <c r="B42" t="s">
-        <v>59</v>
+        <v>8</v>
+      </c>
+      <c r="B42">
+        <v>13060</v>
+      </c>
+      <c r="C42">
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B43">
-        <v>1050</v>
+        <v>403070</v>
       </c>
       <c r="C43">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B44">
-        <v>11070</v>
+        <v>3060</v>
       </c>
       <c r="C44">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
       <c r="A45">
         <v>9</v>
       </c>
-      <c r="B45">
-        <v>401050</v>
-      </c>
-      <c r="C45">
-        <v>26</v>
+      <c r="B45" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -3399,51 +3399,51 @@
         <v>9</v>
       </c>
       <c r="B46">
-        <v>1080</v>
+        <v>1050</v>
       </c>
       <c r="C46">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
       <c r="A47">
-        <v>10</v>
-      </c>
-      <c r="B47" t="s">
-        <v>60</v>
+        <v>9</v>
+      </c>
+      <c r="B47">
+        <v>11070</v>
+      </c>
+      <c r="C47">
+        <v>11</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B48">
-        <v>2030</v>
+        <v>401050</v>
       </c>
       <c r="C48">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B49">
-        <v>12010</v>
+        <v>1080</v>
       </c>
       <c r="C49">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
       <c r="A50">
         <v>10</v>
       </c>
-      <c r="B50">
-        <v>402030</v>
-      </c>
-      <c r="C50">
-        <v>26</v>
+      <c r="B50" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -3451,51 +3451,51 @@
         <v>10</v>
       </c>
       <c r="B51">
-        <v>2080</v>
+        <v>2030</v>
       </c>
       <c r="C51">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
       <c r="A52">
+        <v>10</v>
+      </c>
+      <c r="B52">
+        <v>12010</v>
+      </c>
+      <c r="C52">
         <v>11</v>
-      </c>
-      <c r="B52" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B53">
-        <v>3050</v>
+        <v>402030</v>
       </c>
       <c r="C53">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B54">
-        <v>13090</v>
+        <v>2080</v>
       </c>
       <c r="C54">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
       <c r="A55">
         <v>11</v>
       </c>
-      <c r="B55">
-        <v>403050</v>
-      </c>
-      <c r="C55">
-        <v>26</v>
+      <c r="B55" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -3503,51 +3503,51 @@
         <v>11</v>
       </c>
       <c r="B56">
-        <v>3080</v>
+        <v>3050</v>
       </c>
       <c r="C56">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
       <c r="A57">
-        <v>101</v>
-      </c>
-      <c r="B57" t="s">
-        <v>53</v>
+        <v>11</v>
+      </c>
+      <c r="B57">
+        <v>13090</v>
+      </c>
+      <c r="C57">
+        <v>11</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>101</v>
+        <v>11</v>
       </c>
       <c r="B58">
-        <v>13100</v>
+        <v>403050</v>
       </c>
       <c r="C58">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>101</v>
+        <v>11</v>
       </c>
       <c r="B59">
-        <v>13080</v>
+        <v>3080</v>
       </c>
       <c r="C59">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
       <c r="A60">
         <v>101</v>
       </c>
-      <c r="B60">
-        <v>403010</v>
-      </c>
-      <c r="C60">
-        <v>26</v>
+      <c r="B60" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -3555,61 +3555,105 @@
         <v>101</v>
       </c>
       <c r="B61">
-        <v>3040</v>
+        <v>13100</v>
       </c>
       <c r="C61">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
       <c r="A62">
-        <v>102</v>
-      </c>
-      <c r="B62" t="s">
-        <v>62</v>
+        <v>101</v>
+      </c>
+      <c r="B62">
+        <v>13080</v>
+      </c>
+      <c r="C62">
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B63">
-        <v>5070</v>
+        <v>13081</v>
       </c>
       <c r="C63">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B64">
-        <v>13090</v>
+        <v>403010</v>
       </c>
       <c r="C64">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B65">
-        <v>403050</v>
+        <v>3040</v>
       </c>
       <c r="C65">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
       <c r="A66">
         <v>102</v>
       </c>
-      <c r="B66">
+      <c r="B66" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67">
+        <v>102</v>
+      </c>
+      <c r="B67">
+        <v>5070</v>
+      </c>
+      <c r="C67">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68">
+        <v>102</v>
+      </c>
+      <c r="B68">
+        <v>13090</v>
+      </c>
+      <c r="C68">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69">
+        <v>102</v>
+      </c>
+      <c r="B69">
+        <v>403050</v>
+      </c>
+      <c r="C69">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70">
+        <v>102</v>
+      </c>
+      <c r="B70">
         <v>3080</v>
       </c>
-      <c r="C66">
+      <c r="C70">
         <v>41</v>
       </c>
     </row>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="106">
   <si>
     <t>Id</t>
   </si>
@@ -203,6 +203,9 @@
   </si>
   <si>
     <t>11,21,31,3010,101110,101120</t>
+  </si>
+  <si>
+    <t>11,21,31,3010,110110,110120</t>
   </si>
   <si>
     <t>11,21,31,5010,5070,100510,100520</t>
@@ -350,10 +353,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -372,32 +375,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -409,7 +389,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -425,6 +420,67 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -439,8 +495,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -452,68 +517,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -521,42 +524,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -572,103 +539,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -686,7 +587,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -698,13 +611,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -715,30 +718,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -757,11 +736,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -773,6 +758,15 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -795,23 +789,32 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -823,145 +826,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1524,13 +1527,13 @@
         <v>1</v>
       </c>
       <c r="X2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y2">
         <v>6</v>
       </c>
       <c r="Z2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA2">
         <v>6</v>
@@ -1633,7 +1636,7 @@
         <v>50</v>
       </c>
       <c r="W3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X3">
         <v>1</v>
@@ -1645,7 +1648,7 @@
         <v>7</v>
       </c>
       <c r="AA3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB3">
         <v>20</v>
@@ -1745,7 +1748,7 @@
         <v>50</v>
       </c>
       <c r="W4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X4">
         <v>6</v>
@@ -1754,7 +1757,7 @@
         <v>1</v>
       </c>
       <c r="Z4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA4">
         <v>6</v>
@@ -1857,10 +1860,10 @@
         <v>50</v>
       </c>
       <c r="W5">
+        <v>5</v>
+      </c>
+      <c r="X5">
         <v>4</v>
-      </c>
-      <c r="X5">
-        <v>3</v>
       </c>
       <c r="Y5">
         <v>3</v>
@@ -1969,13 +1972,13 @@
         <v>50</v>
       </c>
       <c r="W6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X6">
         <v>6</v>
       </c>
       <c r="Y6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z6">
         <v>5</v>
@@ -2756,13 +2759,13 @@
         <v>4</v>
       </c>
       <c r="X13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y13">
         <v>1</v>
       </c>
       <c r="Z13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA13">
         <v>7</v>
@@ -2868,13 +2871,13 @@
         <v>3</v>
       </c>
       <c r="X14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y14">
         <v>5</v>
       </c>
       <c r="Z14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA14">
         <v>1</v>
@@ -2883,10 +2886,10 @@
         <v>0</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="AD14">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AE14">
         <v>0</v>
@@ -3547,7 +3550,7 @@
         <v>101</v>
       </c>
       <c r="B60" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -3610,7 +3613,7 @@
         <v>102</v>
       </c>
       <c r="B66" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -3629,7 +3632,7 @@
         <v>102</v>
       </c>
       <c r="B68">
-        <v>13090</v>
+        <v>15090</v>
       </c>
       <c r="C68">
         <v>11</v>
@@ -3640,7 +3643,7 @@
         <v>102</v>
       </c>
       <c r="B69">
-        <v>403050</v>
+        <v>405070</v>
       </c>
       <c r="C69">
         <v>26</v>
@@ -3651,7 +3654,7 @@
         <v>102</v>
       </c>
       <c r="B70">
-        <v>3080</v>
+        <v>5040</v>
       </c>
       <c r="C70">
         <v>41</v>
@@ -3680,10 +3683,10 @@
         <v>49</v>
       </c>
       <c r="C1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -5541,13 +5544,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" ht="39" spans="1:4">
@@ -5555,13 +5558,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" ht="39" spans="1:4">
@@ -5569,13 +5572,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" ht="39" spans="1:4">
@@ -5583,13 +5586,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" ht="39" spans="1:4">
@@ -5597,13 +5600,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" ht="52" spans="1:4">
@@ -5611,13 +5614,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" ht="39" spans="1:4">
@@ -5625,13 +5628,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" ht="52" spans="1:4">
@@ -5639,13 +5642,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" ht="52" spans="1:4">
@@ -5653,13 +5656,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" ht="39" spans="1:4">
@@ -5667,13 +5670,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" ht="39" spans="1:4">
@@ -5681,13 +5684,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" ht="52" spans="1:4">
@@ -5695,13 +5698,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" ht="39" spans="1:4">
@@ -5709,13 +5712,13 @@
         <v>101</v>
       </c>
       <c r="B13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" ht="39" spans="1:4">
@@ -5723,13 +5726,13 @@
         <v>102</v>
       </c>
       <c r="B14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -353,9 +353,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -375,7 +375,22 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -389,22 +404,70 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -420,7 +483,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -434,38 +497,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -479,40 +511,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -527,7 +527,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -539,7 +557,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -551,13 +587,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -569,13 +617,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -587,7 +629,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -599,7 +659,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -611,43 +671,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -665,25 +689,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -695,19 +707,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -718,6 +718,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -736,21 +751,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -758,6 +758,24 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -786,35 +804,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -826,7 +826,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -835,7 +835,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -844,127 +844,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2920,7 +2920,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="44.2727272727273" style="2" customWidth="1"/>
@@ -3038,29 +3038,29 @@
         <v>2</v>
       </c>
       <c r="B11">
-        <v>12041</v>
+        <v>2060</v>
       </c>
       <c r="C11">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12">
-        <v>2</v>
-      </c>
-      <c r="B12">
-        <v>2060</v>
-      </c>
-      <c r="C12">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13">
         <v>3</v>
       </c>
-      <c r="B13" t="s">
-        <v>53</v>
+      <c r="B13">
+        <v>3030</v>
+      </c>
+      <c r="C13">
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3068,10 +3068,10 @@
         <v>3</v>
       </c>
       <c r="B14">
-        <v>3030</v>
+        <v>13080</v>
       </c>
       <c r="C14">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -3079,10 +3079,10 @@
         <v>3</v>
       </c>
       <c r="B15">
-        <v>13080</v>
+        <v>403010</v>
       </c>
       <c r="C15">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -3090,40 +3090,40 @@
         <v>3</v>
       </c>
       <c r="B16">
-        <v>13081</v>
+        <v>3040</v>
       </c>
       <c r="C16">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17">
-        <v>3</v>
-      </c>
-      <c r="B17">
-        <v>403010</v>
-      </c>
-      <c r="C17">
-        <v>26</v>
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B18">
-        <v>3040</v>
+        <v>4030</v>
       </c>
       <c r="C18">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19">
         <v>4</v>
       </c>
-      <c r="B19" t="s">
-        <v>54</v>
+      <c r="B19">
+        <v>14080</v>
+      </c>
+      <c r="C19">
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -3131,10 +3131,10 @@
         <v>4</v>
       </c>
       <c r="B20">
-        <v>4030</v>
+        <v>404030</v>
       </c>
       <c r="C20">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3142,51 +3142,51 @@
         <v>4</v>
       </c>
       <c r="B21">
-        <v>14080</v>
+        <v>4060</v>
       </c>
       <c r="C21">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22">
-        <v>4</v>
-      </c>
-      <c r="B22">
-        <v>14081</v>
-      </c>
-      <c r="C22">
-        <v>11</v>
+        <v>5</v>
+      </c>
+      <c r="B22" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B23">
-        <v>404030</v>
+        <v>5070</v>
       </c>
       <c r="C23">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B24">
-        <v>4060</v>
+        <v>15090</v>
       </c>
       <c r="C24">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25">
         <v>5</v>
       </c>
-      <c r="B25" t="s">
-        <v>55</v>
+      <c r="B25">
+        <v>405070</v>
+      </c>
+      <c r="C25">
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -3194,51 +3194,51 @@
         <v>5</v>
       </c>
       <c r="B26">
-        <v>5070</v>
+        <v>5040</v>
       </c>
       <c r="C26">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27">
-        <v>5</v>
-      </c>
-      <c r="B27">
-        <v>15090</v>
-      </c>
-      <c r="C27">
-        <v>11</v>
+        <v>6</v>
+      </c>
+      <c r="B27" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
+        <v>6</v>
+      </c>
+      <c r="B28">
+        <v>1030</v>
+      </c>
+      <c r="C28">
         <v>5</v>
-      </c>
-      <c r="B28">
-        <v>405070</v>
-      </c>
-      <c r="C28">
-        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B29">
-        <v>5040</v>
+        <v>11040</v>
       </c>
       <c r="C29">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30">
         <v>6</v>
       </c>
-      <c r="B30" t="s">
-        <v>56</v>
+      <c r="B30">
+        <v>401030</v>
+      </c>
+      <c r="C30">
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -3246,51 +3246,51 @@
         <v>6</v>
       </c>
       <c r="B31">
-        <v>1030</v>
+        <v>1070</v>
       </c>
       <c r="C31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32">
-        <v>6</v>
-      </c>
-      <c r="B32">
-        <v>11040</v>
-      </c>
-      <c r="C32">
-        <v>11</v>
+        <v>7</v>
+      </c>
+      <c r="B32" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B33">
-        <v>401030</v>
+        <v>2040</v>
       </c>
       <c r="C33">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B34">
-        <v>1070</v>
+        <v>12090</v>
       </c>
       <c r="C34">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35">
         <v>7</v>
       </c>
-      <c r="B35" t="s">
-        <v>57</v>
+      <c r="B35">
+        <v>412090</v>
+      </c>
+      <c r="C35">
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -3298,51 +3298,51 @@
         <v>7</v>
       </c>
       <c r="B36">
-        <v>2040</v>
+        <v>2050</v>
       </c>
       <c r="C36">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37">
-        <v>7</v>
-      </c>
-      <c r="B37">
-        <v>12090</v>
-      </c>
-      <c r="C37">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="B37" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B38">
-        <v>412090</v>
+        <v>3070</v>
       </c>
       <c r="C38">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B39">
-        <v>2050</v>
+        <v>13060</v>
       </c>
       <c r="C39">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40">
         <v>8</v>
       </c>
-      <c r="B40" t="s">
-        <v>58</v>
+      <c r="B40">
+        <v>403070</v>
+      </c>
+      <c r="C40">
+        <v>26</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -3350,51 +3350,51 @@
         <v>8</v>
       </c>
       <c r="B41">
-        <v>3070</v>
+        <v>3060</v>
       </c>
       <c r="C41">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
       <c r="A42">
-        <v>8</v>
-      </c>
-      <c r="B42">
-        <v>13060</v>
-      </c>
-      <c r="C42">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="B42" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B43">
-        <v>403070</v>
+        <v>1050</v>
       </c>
       <c r="C43">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B44">
-        <v>3060</v>
+        <v>11070</v>
       </c>
       <c r="C44">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
       <c r="A45">
         <v>9</v>
       </c>
-      <c r="B45" t="s">
-        <v>59</v>
+      <c r="B45">
+        <v>401050</v>
+      </c>
+      <c r="C45">
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -3402,51 +3402,51 @@
         <v>9</v>
       </c>
       <c r="B46">
-        <v>1050</v>
+        <v>1080</v>
       </c>
       <c r="C46">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
       <c r="A47">
-        <v>9</v>
-      </c>
-      <c r="B47">
-        <v>11070</v>
-      </c>
-      <c r="C47">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="B47" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B48">
-        <v>401050</v>
+        <v>2030</v>
       </c>
       <c r="C48">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B49">
-        <v>1080</v>
+        <v>12010</v>
       </c>
       <c r="C49">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50">
         <v>10</v>
       </c>
-      <c r="B50" t="s">
-        <v>60</v>
+      <c r="B50">
+        <v>402030</v>
+      </c>
+      <c r="C50">
+        <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -3454,51 +3454,51 @@
         <v>10</v>
       </c>
       <c r="B51">
-        <v>2030</v>
+        <v>2080</v>
       </c>
       <c r="C51">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
       <c r="A52">
-        <v>10</v>
-      </c>
-      <c r="B52">
-        <v>12010</v>
-      </c>
-      <c r="C52">
         <v>11</v>
+      </c>
+      <c r="B52" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B53">
-        <v>402030</v>
+        <v>3050</v>
       </c>
       <c r="C53">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B54">
-        <v>2080</v>
+        <v>13090</v>
       </c>
       <c r="C54">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
       <c r="A55">
         <v>11</v>
       </c>
-      <c r="B55" t="s">
-        <v>61</v>
+      <c r="B55">
+        <v>403050</v>
+      </c>
+      <c r="C55">
+        <v>26</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -3506,51 +3506,51 @@
         <v>11</v>
       </c>
       <c r="B56">
-        <v>3050</v>
+        <v>3080</v>
       </c>
       <c r="C56">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
       <c r="A57">
-        <v>11</v>
-      </c>
-      <c r="B57">
-        <v>13090</v>
-      </c>
-      <c r="C57">
-        <v>11</v>
+        <v>101</v>
+      </c>
+      <c r="B57" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="B58">
-        <v>403050</v>
+        <v>13100</v>
       </c>
       <c r="C58">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
+        <v>101</v>
+      </c>
+      <c r="B59">
+        <v>13080</v>
+      </c>
+      <c r="C59">
         <v>11</v>
       </c>
-      <c r="B59">
-        <v>3080</v>
-      </c>
-      <c r="C59">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
+    </row>
+    <row r="60" spans="1:3">
       <c r="A60">
         <v>101</v>
       </c>
-      <c r="B60" t="s">
-        <v>62</v>
+      <c r="B60">
+        <v>403010</v>
+      </c>
+      <c r="C60">
+        <v>26</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -3558,105 +3558,61 @@
         <v>101</v>
       </c>
       <c r="B61">
-        <v>13100</v>
+        <v>3040</v>
       </c>
       <c r="C61">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
       <c r="A62">
-        <v>101</v>
-      </c>
-      <c r="B62">
-        <v>13080</v>
-      </c>
-      <c r="C62">
-        <v>11</v>
+        <v>102</v>
+      </c>
+      <c r="B62" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B63">
-        <v>13081</v>
+        <v>5070</v>
       </c>
       <c r="C63">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B64">
-        <v>403010</v>
+        <v>15090</v>
       </c>
       <c r="C64">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B65">
-        <v>3040</v>
+        <v>405070</v>
       </c>
       <c r="C65">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
       <c r="A66">
         <v>102</v>
       </c>
-      <c r="B66" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67">
-        <v>102</v>
-      </c>
-      <c r="B67">
-        <v>5070</v>
-      </c>
-      <c r="C67">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68">
-        <v>102</v>
-      </c>
-      <c r="B68">
-        <v>15090</v>
-      </c>
-      <c r="C68">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69">
-        <v>102</v>
-      </c>
-      <c r="B69">
-        <v>405070</v>
-      </c>
-      <c r="C69">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70">
-        <v>102</v>
-      </c>
-      <c r="B70">
+      <c r="B66">
         <v>5040</v>
       </c>
-      <c r="C70">
+      <c r="C66">
         <v>41</v>
       </c>
     </row>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -353,10 +353,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -375,14 +375,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -390,52 +383,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -450,8 +397,60 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -467,15 +466,30 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -489,22 +503,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -512,7 +512,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -524,30 +524,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -563,7 +539,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -575,19 +581,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -599,7 +635,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -611,25 +689,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -641,73 +707,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -718,6 +718,45 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -736,17 +775,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -758,33 +791,6 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -804,17 +810,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -826,145 +826,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2744,7 +2744,7 @@
         <v>75</v>
       </c>
       <c r="S13">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="T13">
         <v>50</v>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8410"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="110">
   <si>
     <t>Id</t>
   </si>
@@ -161,6 +161,12 @@
   </si>
   <si>
     <t>0102</t>
+  </si>
+  <si>
+    <t>0103</t>
+  </si>
+  <si>
+    <t>0104</t>
   </si>
   <si>
     <t>ActorId</t>
@@ -346,6 +352,12 @@
   </si>
   <si>
     <t>【悲劇の戦乙女】</t>
+  </si>
+  <si>
+    <t>シグムント</t>
+  </si>
+  <si>
+    <t>ヨルディス</t>
   </si>
 </sst>
 </file>
@@ -353,9 +365,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
@@ -375,9 +387,56 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -397,53 +456,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -458,15 +472,36 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -481,7 +516,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -490,29 +525,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -527,7 +539,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -539,175 +713,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -718,6 +730,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -732,6 +753,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -754,8 +799,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -777,44 +822,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -826,145 +838,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1329,7 +1341,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AJ14"/>
+  <dimension ref="A1:AJ16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="3" max="3" width="11.6363636363636" customWidth="1"/>
@@ -2907,6 +2919,230 @@
         <v>0</v>
       </c>
       <c r="AJ14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:36">
+      <c r="A15">
+        <v>103</v>
+      </c>
+      <c r="B15">
+        <v>103</v>
+      </c>
+      <c r="C15" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B15,TextData!A:A))</f>
+        <v>シグムント</v>
+      </c>
+      <c r="D15" t="str">
+        <f>INDEX(TextData!C:C,MATCH(B15,TextData!A:A))</f>
+        <v>【竜殺し】</v>
+      </c>
+      <c r="E15">
+        <v>10</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>99</v>
+      </c>
+      <c r="I15">
+        <v>29</v>
+      </c>
+      <c r="J15">
+        <v>5</v>
+      </c>
+      <c r="K15">
+        <v>17</v>
+      </c>
+      <c r="L15">
+        <v>17</v>
+      </c>
+      <c r="M15">
+        <v>17</v>
+      </c>
+      <c r="N15">
+        <v>3</v>
+      </c>
+      <c r="O15">
+        <v>2</v>
+      </c>
+      <c r="P15">
+        <v>130</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>60</v>
+      </c>
+      <c r="S15">
+        <v>80</v>
+      </c>
+      <c r="T15">
+        <v>60</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>50</v>
+      </c>
+      <c r="W15">
+        <v>4</v>
+      </c>
+      <c r="X15">
+        <v>6</v>
+      </c>
+      <c r="Y15">
+        <v>1</v>
+      </c>
+      <c r="Z15">
+        <v>3</v>
+      </c>
+      <c r="AA15">
+        <v>7</v>
+      </c>
+      <c r="AB15">
+        <v>-4</v>
+      </c>
+      <c r="AC15">
+        <v>-64</v>
+      </c>
+      <c r="AD15">
+        <v>0.86</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>1</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:36">
+      <c r="A16">
+        <v>104</v>
+      </c>
+      <c r="B16">
+        <v>104</v>
+      </c>
+      <c r="C16" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B16,TextData!A:A))</f>
+        <v>ヨルディス</v>
+      </c>
+      <c r="D16" t="str">
+        <f>INDEX(TextData!C:C,MATCH(B16,TextData!A:A))</f>
+        <v>【悲劇の戦乙女】</v>
+      </c>
+      <c r="E16">
+        <v>10</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>99</v>
+      </c>
+      <c r="I16">
+        <v>34</v>
+      </c>
+      <c r="J16">
+        <v>4</v>
+      </c>
+      <c r="K16">
+        <v>15</v>
+      </c>
+      <c r="L16">
+        <v>9</v>
+      </c>
+      <c r="M16">
+        <v>22</v>
+      </c>
+      <c r="N16">
+        <v>3</v>
+      </c>
+      <c r="O16">
+        <v>2</v>
+      </c>
+      <c r="P16">
+        <v>160</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>65</v>
+      </c>
+      <c r="S16">
+        <v>60</v>
+      </c>
+      <c r="T16">
+        <v>65</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>50</v>
+      </c>
+      <c r="W16">
+        <v>5</v>
+      </c>
+      <c r="X16">
+        <v>4</v>
+      </c>
+      <c r="Y16">
+        <v>3</v>
+      </c>
+      <c r="Z16">
+        <v>1</v>
+      </c>
+      <c r="AA16">
+        <v>1</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>-12</v>
+      </c>
+      <c r="AD16">
+        <v>0.8</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>1</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
         <v>0</v>
       </c>
     </row>
@@ -2928,13 +3164,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2942,7 +3178,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -2997,7 +3233,7 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3049,7 +3285,7 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3101,7 +3337,7 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3153,7 +3389,7 @@
         <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -3205,7 +3441,7 @@
         <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -3257,7 +3493,7 @@
         <v>7</v>
       </c>
       <c r="B32" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -3309,7 +3545,7 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -3361,7 +3597,7 @@
         <v>9</v>
       </c>
       <c r="B42" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -3413,7 +3649,7 @@
         <v>10</v>
       </c>
       <c r="B47" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -3465,7 +3701,7 @@
         <v>11</v>
       </c>
       <c r="B52" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -3517,7 +3753,7 @@
         <v>101</v>
       </c>
       <c r="B57" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -3569,7 +3805,7 @@
         <v>102</v>
       </c>
       <c r="B62" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -3633,16 +3869,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -5488,7 +5724,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="3"/>
   <cols>
     <col min="3" max="3" width="20.5454545454545" customWidth="1"/>
@@ -5500,13 +5736,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" ht="39" spans="1:4">
@@ -5514,13 +5750,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" ht="39" spans="1:4">
@@ -5528,13 +5764,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" ht="39" spans="1:4">
@@ -5542,13 +5778,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" ht="39" spans="1:4">
@@ -5556,13 +5792,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" ht="52" spans="1:4">
@@ -5570,13 +5806,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" ht="39" spans="1:4">
@@ -5584,13 +5820,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" ht="52" spans="1:4">
@@ -5598,13 +5834,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" ht="52" spans="1:4">
@@ -5612,13 +5848,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" ht="39" spans="1:4">
@@ -5626,13 +5862,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" ht="39" spans="1:4">
@@ -5640,13 +5876,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" ht="52" spans="1:4">
@@ -5654,13 +5890,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" ht="39" spans="1:4">
@@ -5668,13 +5904,13 @@
         <v>101</v>
       </c>
       <c r="B13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" ht="39" spans="1:4">
@@ -5682,13 +5918,41 @@
         <v>102</v>
       </c>
       <c r="B14" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" t="s">
+        <v>107</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" ht="39" spans="1:4">
+      <c r="A15">
+        <v>103</v>
+      </c>
+      <c r="B15" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" t="s">
+        <v>105</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" ht="39" spans="1:4">
+      <c r="A16">
         <v>104</v>
       </c>
-      <c r="C14" t="s">
-        <v>105</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>74</v>
+      <c r="B16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" t="s">
+        <v>107</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8410"/>
+    <workbookView windowWidth="19200" windowHeight="8410" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -178,19 +178,19 @@
     <t>Level</t>
   </si>
   <si>
-    <t>11,21,31,1010,100110,100120</t>
-  </si>
-  <si>
-    <t>11,21,31,2010,100210,100220</t>
-  </si>
-  <si>
-    <t>11,21,31,3010,100310,100320</t>
-  </si>
-  <si>
-    <t>11,21,31,4010,100410,100420</t>
-  </si>
-  <si>
-    <t>11,21,31,5010,100510,100520</t>
+    <t>11,21,31,1010</t>
+  </si>
+  <si>
+    <t>11,21,31,2010</t>
+  </si>
+  <si>
+    <t>11,21,31,3010</t>
+  </si>
+  <si>
+    <t>11,21,31,4010</t>
+  </si>
+  <si>
+    <t>11,21,31,5010</t>
   </si>
   <si>
     <t>11,21,31,1010,100610,100620</t>
@@ -365,10 +365,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -393,64 +393,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -479,8 +423,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -500,10 +453,57 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -515,16 +515,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -539,7 +539,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -551,7 +569,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -563,7 +611,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -575,151 +713,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -730,15 +730,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -761,7 +752,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -792,6 +783,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -838,145 +838,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8410" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8410" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="123">
   <si>
     <t>Id</t>
   </si>
@@ -230,6 +230,9 @@
   </si>
   <si>
     <t>Feature</t>
+  </si>
+  <si>
+    <t>Releif</t>
   </si>
   <si>
     <t>ロジーナ</t>
@@ -242,6 +245,9 @@
 全体的にステータスが高く、赤属性魔法を習得することでさらに攻撃性能を伸ばすことができる。</t>
   </si>
   <si>
+    <t>立場に縛られて…私は</t>
+  </si>
+  <si>
     <t>エリザベート</t>
   </si>
   <si>
@@ -252,6 +258,9 @@
 打たれ弱いがSPDが高く、回避率をアップする雷属性魔法を習得しやすい。</t>
   </si>
   <si>
+    <t>先陣を切るのはアタシだ！</t>
+  </si>
+  <si>
     <t>アリエス</t>
   </si>
   <si>
@@ -262,6 +271,9 @@
 受けた攻撃ダメージの一部を跳ね返す「カウンターオーラ」を使うことができる。</t>
   </si>
   <si>
+    <t>外の世界は怖いから…ずっとここにいたい</t>
+  </si>
+  <si>
     <t>シイナ</t>
   </si>
   <si>
@@ -272,6 +284,9 @@
 全体的にステータスが低いが、味方のHpを回復する「ヒーリング」を使うことができる。</t>
   </si>
   <si>
+    <t>生きる理由は、もうどこにもないから</t>
+  </si>
+  <si>
     <t>レダ</t>
   </si>
   <si>
@@ -282,6 +297,9 @@
 「シェイディークラウド」で味方が受けるダメージを抑えたり、「毒」でスリップダメージを与える魔法を使うことができる。</t>
   </si>
   <si>
+    <t>知を得るために魂を授けろって…上等じゃない</t>
+  </si>
+  <si>
     <t>リシェリ</t>
   </si>
   <si>
@@ -292,6 +310,9 @@
 CT（魔法を再使用するまでのターン数）を短縮しパーティ全体の補助をすることができる。</t>
   </si>
   <si>
+    <t>このまま待っているだけなんて、嫌だよ</t>
+  </si>
+  <si>
     <t>ユニ</t>
   </si>
   <si>
@@ -302,6 +323,9 @@
 「アウトオブオーダー」で両隣に配置した味方の行動待機時間を短縮したり、味方のATK・DEFをアップするバフ魔法を使うことができる。</t>
   </si>
   <si>
+    <t>ワタシは王子を信じている、たとえ塵になろうとも</t>
+  </si>
+  <si>
     <t>マリーベル</t>
   </si>
   <si>
@@ -312,6 +336,9 @@
 「アクアミラージュ」で一定回数攻撃を無効にしたり、味方の攻撃を代わりに受けパーティの生存率を上げることができる。</t>
   </si>
   <si>
+    <t>ただの傭兵稼業をしているつもりだったんだけどね</t>
+  </si>
+  <si>
     <t>ナツキ</t>
   </si>
   <si>
@@ -322,6 +349,9 @@
 Hpが低いがATKが高く、攻撃回数の多い「フレイムレイン」を使うことができる。</t>
   </si>
   <si>
+    <t>敵、ならば殲滅あるのみ</t>
+  </si>
+  <si>
     <t>メリアドール</t>
   </si>
   <si>
@@ -332,6 +362,9 @@
 「ショックインパルス」で相手を行動不可にすることができる。</t>
   </si>
   <si>
+    <t>あたしはこんな力持ちたくなかったのに</t>
+  </si>
+  <si>
     <t>セリナ</t>
   </si>
   <si>
@@ -342,10 +375,16 @@
 「ディープフリーズ」で攻撃時に一定量のダメージを受ける「凍結」状態にし、凍結効果をさらにアップすることで自滅に追い込むことができる。</t>
   </si>
   <si>
+    <t>どうして…ほおっておいてくれないのでしょうか</t>
+  </si>
+  <si>
     <t>シグルド</t>
   </si>
   <si>
     <t>【竜殺し】</t>
+  </si>
+  <si>
+    <t>""</t>
   </si>
   <si>
     <t>ブリュンヒルデ</t>
@@ -365,10 +404,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -386,6 +425,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -393,6 +440,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -407,17 +455,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -453,24 +492,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -500,6 +523,22 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -509,15 +548,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -539,7 +578,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -551,61 +626,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -623,7 +662,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -635,19 +686,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -659,19 +698,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -683,25 +734,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -713,13 +752,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -750,24 +789,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -790,8 +816,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -799,8 +840,17 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -819,17 +869,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -838,19 +877,19 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -859,64 +898,64 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -925,58 +964,58 @@
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5724,14 +5763,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="3"/>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
     <col min="3" max="3" width="20.5454545454545" customWidth="1"/>
     <col min="4" max="4" width="45.1818181818182" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5744,215 +5784,263 @@
       <c r="D1" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="2" ht="39" spans="1:4">
+      <c r="E1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" ht="39" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="3" ht="39" spans="1:4">
+        <v>74</v>
+      </c>
+      <c r="E2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" ht="39" spans="1:5">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="4" ht="39" spans="1:4">
+        <v>78</v>
+      </c>
+      <c r="E3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" ht="39" spans="1:5">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" ht="39" spans="1:4">
+        <v>82</v>
+      </c>
+      <c r="E4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" ht="39" spans="1:5">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" ht="52" spans="1:4">
+        <v>86</v>
+      </c>
+      <c r="E5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" ht="52" spans="1:5">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="7" ht="39" spans="1:4">
+        <v>90</v>
+      </c>
+      <c r="E6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" ht="39" spans="1:5">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" ht="52" spans="1:4">
+        <v>94</v>
+      </c>
+      <c r="E7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" ht="52" spans="1:5">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="9" ht="52" spans="1:4">
+        <v>98</v>
+      </c>
+      <c r="E8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" ht="52" spans="1:5">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="10" ht="39" spans="1:4">
+        <v>102</v>
+      </c>
+      <c r="E9" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" ht="39" spans="1:5">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="11" ht="39" spans="1:4">
+        <v>106</v>
+      </c>
+      <c r="E10" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" ht="39" spans="1:5">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" ht="52" spans="1:4">
+        <v>110</v>
+      </c>
+      <c r="E11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" ht="52" spans="1:5">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="13" ht="39" spans="1:4">
+        <v>114</v>
+      </c>
+      <c r="E12" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" ht="39" spans="1:5">
       <c r="A13">
         <v>101</v>
       </c>
       <c r="B13" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="14" ht="39" spans="1:4">
+        <v>74</v>
+      </c>
+      <c r="E13" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" ht="39" spans="1:5">
       <c r="A14">
         <v>102</v>
       </c>
       <c r="B14" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="C14" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" ht="39" spans="1:4">
+        <v>78</v>
+      </c>
+      <c r="E14" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="15" ht="39" spans="1:5">
       <c r="A15">
         <v>103</v>
       </c>
       <c r="B15" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="C15" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16" ht="39" spans="1:4">
+        <v>74</v>
+      </c>
+      <c r="E15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="16" ht="39" spans="1:5">
       <c r="A16">
         <v>104</v>
       </c>
       <c r="B16" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
+      </c>
+      <c r="E16" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8410" activeTab="3"/>
+    <workbookView windowWidth="19200" windowHeight="8410" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -405,9 +405,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -425,9 +425,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -440,14 +439,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -455,6 +446,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -479,13 +471,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -494,6 +479,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -517,6 +510,13 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -548,17 +548,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -578,7 +578,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -590,13 +626,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -608,55 +728,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -668,85 +746,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -758,7 +758,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -813,6 +813,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -854,21 +869,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -877,16 +877,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -895,131 +895,131 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1027,6 +1027,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1435,10 +1438,10 @@
       <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="4" t="s">
         <v>13</v>
       </c>
       <c r="P1" t="s">
@@ -1456,10 +1459,10 @@
       <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" s="4" t="s">
         <v>20</v>
       </c>
       <c r="W1" t="s">
@@ -2081,7 +2084,7 @@
         <v>【Faked-Magician】</v>
       </c>
       <c r="E7">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>40</v>
@@ -2193,7 +2196,7 @@
         <v>【奇跡の乙女】</v>
       </c>
       <c r="E8">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>41</v>
@@ -2305,7 +2308,7 @@
         <v>【唯心の在処】</v>
       </c>
       <c r="E9">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>42</v>
@@ -2417,7 +2420,7 @@
         <v>【黄昏ニヒリスト】</v>
       </c>
       <c r="E10">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>43</v>
@@ -2529,7 +2532,7 @@
         <v>【怨嗟の鎖】</v>
       </c>
       <c r="E11">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>44</v>
@@ -2641,7 +2644,7 @@
         <v>【氷雪の勿忘草】</v>
       </c>
       <c r="E12">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>45</v>
@@ -3195,7 +3198,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C76"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="44.2727272727273" style="2" customWidth="1"/>
@@ -3267,34 +3270,34 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:3">
       <c r="A7">
-        <v>2</v>
-      </c>
-      <c r="B7" t="s">
-        <v>54</v>
+        <v>1</v>
+      </c>
+      <c r="B7" s="3">
+        <v>100110</v>
+      </c>
+      <c r="C7">
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>2</v>
-      </c>
-      <c r="B8">
-        <v>12010</v>
+        <v>1</v>
+      </c>
+      <c r="B8" s="3">
+        <v>100120</v>
       </c>
       <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9">
         <v>2</v>
       </c>
-      <c r="B9">
-        <v>12080</v>
-      </c>
-      <c r="C9">
-        <v>11</v>
+      <c r="B9" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3302,10 +3305,10 @@
         <v>2</v>
       </c>
       <c r="B10">
-        <v>12040</v>
+        <v>12010</v>
       </c>
       <c r="C10">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -3313,286 +3316,292 @@
         <v>2</v>
       </c>
       <c r="B11">
-        <v>2060</v>
+        <v>12080</v>
       </c>
       <c r="C11">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>55</v>
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>12040</v>
+      </c>
+      <c r="C12">
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B13">
-        <v>3030</v>
+        <v>2060</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>3</v>
-      </c>
-      <c r="B14">
-        <v>13080</v>
+        <v>2</v>
+      </c>
+      <c r="B14" s="3">
+        <v>100210</v>
       </c>
       <c r="C14">
-        <v>11</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>3</v>
-      </c>
-      <c r="B15">
-        <v>403010</v>
+        <v>2</v>
+      </c>
+      <c r="B15" s="3">
+        <v>100220</v>
       </c>
       <c r="C15">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16">
         <v>3</v>
       </c>
-      <c r="B16">
-        <v>3040</v>
-      </c>
-      <c r="C16">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+      <c r="B16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17">
-        <v>4</v>
-      </c>
-      <c r="B17" t="s">
-        <v>56</v>
+        <v>3</v>
+      </c>
+      <c r="B17">
+        <v>3030</v>
+      </c>
+      <c r="C17">
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B18">
-        <v>4030</v>
+        <v>13080</v>
       </c>
       <c r="C18">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B19">
-        <v>14080</v>
+        <v>403010</v>
       </c>
       <c r="C19">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B20">
-        <v>404030</v>
+        <v>3040</v>
       </c>
       <c r="C20">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21" s="3">
+        <v>100310</v>
+      </c>
+      <c r="C21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22" s="3">
+        <v>100320</v>
+      </c>
+      <c r="C22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
         <v>4</v>
       </c>
-      <c r="B21">
-        <v>4060</v>
-      </c>
-      <c r="C21">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22">
-        <v>5</v>
-      </c>
-      <c r="B22" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23">
-        <v>5</v>
-      </c>
-      <c r="B23">
-        <v>5070</v>
-      </c>
-      <c r="C23">
-        <v>5</v>
+      <c r="B23" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
+        <v>4</v>
+      </c>
+      <c r="B24">
+        <v>4030</v>
+      </c>
+      <c r="C24">
         <v>5</v>
-      </c>
-      <c r="B24">
-        <v>15090</v>
-      </c>
-      <c r="C24">
-        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B25">
-        <v>405070</v>
+        <v>14080</v>
       </c>
       <c r="C25">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B26">
-        <v>5040</v>
+        <v>404030</v>
       </c>
       <c r="C26">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <v>4060</v>
+      </c>
+      <c r="C27">
         <v>41</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27">
-        <v>6</v>
-      </c>
-      <c r="B27" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>6</v>
-      </c>
-      <c r="B28">
-        <v>1030</v>
+        <v>4</v>
+      </c>
+      <c r="B28" s="3">
+        <v>100410</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>6</v>
-      </c>
-      <c r="B29">
-        <v>11040</v>
+        <v>4</v>
+      </c>
+      <c r="B29" s="3">
+        <v>100420</v>
       </c>
       <c r="C29">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30">
-        <v>6</v>
-      </c>
-      <c r="B30">
-        <v>401030</v>
-      </c>
-      <c r="C30">
-        <v>26</v>
+        <v>5</v>
+      </c>
+      <c r="B30" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B31">
-        <v>1070</v>
+        <v>5070</v>
       </c>
       <c r="C31">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32">
-        <v>7</v>
-      </c>
-      <c r="B32" t="s">
-        <v>59</v>
+        <v>5</v>
+      </c>
+      <c r="B32">
+        <v>15090</v>
+      </c>
+      <c r="C32">
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B33">
-        <v>2040</v>
+        <v>405070</v>
       </c>
       <c r="C33">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B34">
-        <v>12090</v>
+        <v>5040</v>
       </c>
       <c r="C34">
-        <v>11</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>7</v>
-      </c>
-      <c r="B35">
-        <v>412090</v>
+        <v>5</v>
+      </c>
+      <c r="B35" s="3">
+        <v>100510</v>
       </c>
       <c r="C35">
-        <v>26</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>7</v>
-      </c>
-      <c r="B36">
-        <v>2050</v>
+        <v>5</v>
+      </c>
+      <c r="B36" s="3">
+        <v>100520</v>
       </c>
       <c r="C36">
-        <v>41</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B38">
-        <v>3070</v>
+        <v>1030</v>
       </c>
       <c r="C38">
         <v>5</v>
@@ -3600,10 +3609,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B39">
-        <v>13060</v>
+        <v>11040</v>
       </c>
       <c r="C39">
         <v>11</v>
@@ -3611,10 +3620,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B40">
-        <v>403070</v>
+        <v>401030</v>
       </c>
       <c r="C40">
         <v>26</v>
@@ -3622,10 +3631,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B41">
-        <v>3060</v>
+        <v>1070</v>
       </c>
       <c r="C41">
         <v>41</v>
@@ -3633,18 +3642,18 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B42" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B43">
-        <v>1050</v>
+        <v>2040</v>
       </c>
       <c r="C43">
         <v>5</v>
@@ -3652,10 +3661,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B44">
-        <v>11070</v>
+        <v>12090</v>
       </c>
       <c r="C44">
         <v>11</v>
@@ -3663,10 +3672,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B45">
-        <v>401050</v>
+        <v>412090</v>
       </c>
       <c r="C45">
         <v>26</v>
@@ -3674,10 +3683,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B46">
-        <v>1080</v>
+        <v>2050</v>
       </c>
       <c r="C46">
         <v>41</v>
@@ -3685,18 +3694,18 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B47" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B48">
-        <v>2030</v>
+        <v>3070</v>
       </c>
       <c r="C48">
         <v>5</v>
@@ -3704,10 +3713,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B49">
-        <v>12010</v>
+        <v>13060</v>
       </c>
       <c r="C49">
         <v>11</v>
@@ -3715,10 +3724,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B50">
-        <v>402030</v>
+        <v>403070</v>
       </c>
       <c r="C50">
         <v>26</v>
@@ -3726,10 +3735,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B51">
-        <v>2080</v>
+        <v>3060</v>
       </c>
       <c r="C51">
         <v>41</v>
@@ -3737,18 +3746,18 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B52" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B53">
-        <v>3050</v>
+        <v>1050</v>
       </c>
       <c r="C53">
         <v>5</v>
@@ -3756,10 +3765,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B54">
-        <v>13090</v>
+        <v>11070</v>
       </c>
       <c r="C54">
         <v>11</v>
@@ -3767,10 +3776,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B55">
-        <v>403050</v>
+        <v>401050</v>
       </c>
       <c r="C55">
         <v>26</v>
@@ -3778,10 +3787,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B56">
-        <v>3080</v>
+        <v>1080</v>
       </c>
       <c r="C56">
         <v>41</v>
@@ -3789,18 +3798,18 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="B57" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="B58">
-        <v>13100</v>
+        <v>2030</v>
       </c>
       <c r="C58">
         <v>5</v>
@@ -3808,10 +3817,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="B59">
-        <v>13080</v>
+        <v>12010</v>
       </c>
       <c r="C59">
         <v>11</v>
@@ -3819,10 +3828,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="B60">
-        <v>403010</v>
+        <v>402030</v>
       </c>
       <c r="C60">
         <v>26</v>
@@ -3830,10 +3839,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="B61">
-        <v>3040</v>
+        <v>2080</v>
       </c>
       <c r="C61">
         <v>41</v>
@@ -3841,18 +3850,18 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62">
-        <v>102</v>
+        <v>11</v>
       </c>
       <c r="B62" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>102</v>
+        <v>11</v>
       </c>
       <c r="B63">
-        <v>5070</v>
+        <v>3050</v>
       </c>
       <c r="C63">
         <v>5</v>
@@ -3860,10 +3869,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>102</v>
+        <v>11</v>
       </c>
       <c r="B64">
-        <v>15090</v>
+        <v>13090</v>
       </c>
       <c r="C64">
         <v>11</v>
@@ -3871,10 +3880,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>102</v>
+        <v>11</v>
       </c>
       <c r="B65">
-        <v>405070</v>
+        <v>403050</v>
       </c>
       <c r="C65">
         <v>26</v>
@@ -3882,12 +3891,116 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
+        <v>11</v>
+      </c>
+      <c r="B66">
+        <v>3080</v>
+      </c>
+      <c r="C66">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67">
+        <v>101</v>
+      </c>
+      <c r="B67" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68">
+        <v>101</v>
+      </c>
+      <c r="B68">
+        <v>13100</v>
+      </c>
+      <c r="C68">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69">
+        <v>101</v>
+      </c>
+      <c r="B69">
+        <v>13080</v>
+      </c>
+      <c r="C69">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70">
+        <v>101</v>
+      </c>
+      <c r="B70">
+        <v>403010</v>
+      </c>
+      <c r="C70">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71">
+        <v>101</v>
+      </c>
+      <c r="B71">
+        <v>3040</v>
+      </c>
+      <c r="C71">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72">
         <v>102</v>
       </c>
-      <c r="B66">
+      <c r="B72" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73">
+        <v>102</v>
+      </c>
+      <c r="B73">
+        <v>5070</v>
+      </c>
+      <c r="C73">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74">
+        <v>102</v>
+      </c>
+      <c r="B74">
+        <v>15090</v>
+      </c>
+      <c r="C74">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75">
+        <v>102</v>
+      </c>
+      <c r="B75">
+        <v>405070</v>
+      </c>
+      <c r="C75">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76">
+        <v>102</v>
+      </c>
+      <c r="B76">
         <v>5040</v>
       </c>
-      <c r="C66">
+      <c r="C76">
         <v>41</v>
       </c>
     </row>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -405,8 +405,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -440,15 +440,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -462,6 +468,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -470,15 +483,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -493,7 +500,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -510,21 +517,6 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -563,7 +555,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -584,7 +584,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -596,31 +614,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -632,31 +650,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -674,13 +668,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -692,7 +704,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -710,43 +740,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -758,7 +758,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -769,6 +769,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -787,13 +796,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -831,30 +844,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
@@ -869,6 +858,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -877,7 +877,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -886,7 +886,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -895,127 +895,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2084,7 +2084,7 @@
         <v>【Faked-Magician】</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>40</v>
@@ -2196,7 +2196,7 @@
         <v>【奇跡の乙女】</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>41</v>
@@ -2308,7 +2308,7 @@
         <v>【唯心の在処】</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>42</v>
@@ -2420,7 +2420,7 @@
         <v>【黄昏ニヒリスト】</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>43</v>
@@ -2532,7 +2532,7 @@
         <v>【怨嗟の鎖】</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>44</v>
@@ -2644,7 +2644,7 @@
         <v>【氷雪の勿忘草】</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>45</v>
@@ -3234,7 +3234,7 @@
         <v>1060</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3308,7 +3308,7 @@
         <v>12010</v>
       </c>
       <c r="C10">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -3382,7 +3382,7 @@
         <v>3030</v>
       </c>
       <c r="C17">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3456,7 +3456,7 @@
         <v>4030</v>
       </c>
       <c r="C24">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -3530,7 +3530,7 @@
         <v>5070</v>
       </c>
       <c r="C31">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -3916,7 +3916,7 @@
         <v>13100</v>
       </c>
       <c r="C68">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -3968,7 +3968,7 @@
         <v>5070</v>
       </c>
       <c r="C73">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:3">

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8410" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8410" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="123">
   <si>
     <t>Id</t>
   </si>
@@ -384,13 +384,13 @@
     <t>【竜殺し】</t>
   </si>
   <si>
+    <t>ブリュンヒルデ</t>
+  </si>
+  <si>
+    <t>【悲劇の戦乙女】</t>
+  </si>
+  <si>
     <t>""</t>
-  </si>
-  <si>
-    <t>ブリュンヒルデ</t>
-  </si>
-  <si>
-    <t>【悲劇の戦乙女】</t>
   </si>
   <si>
     <t>シグムント</t>
@@ -404,9 +404,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -425,22 +425,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -453,8 +440,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -463,13 +480,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -485,32 +495,23 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -522,11 +523,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -546,24 +562,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -578,7 +578,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -590,25 +710,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -626,19 +734,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -650,115 +752,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -772,11 +772,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -796,17 +802,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -826,17 +826,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -844,8 +840,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -859,13 +855,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -877,145 +877,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -6088,7 +6088,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="13" ht="39" spans="1:5">
+    <row r="13" ht="39" spans="1:4">
       <c r="A13">
         <v>101</v>
       </c>
@@ -6100,9 +6100,6 @@
       </c>
       <c r="D13" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="E13" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="14" ht="39" spans="1:5">
@@ -6110,16 +6107,16 @@
         <v>102</v>
       </c>
       <c r="B14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" t="s">
         <v>119</v>
-      </c>
-      <c r="C14" t="s">
-        <v>120</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>78</v>
       </c>
       <c r="E14" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" ht="39" spans="1:5">
@@ -6136,7 +6133,7 @@
         <v>74</v>
       </c>
       <c r="E15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" ht="39" spans="1:5">
@@ -6147,13 +6144,13 @@
         <v>122</v>
       </c>
       <c r="C16" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>78</v>
       </c>
       <c r="E16" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8410" activeTab="3"/>
+    <workbookView windowWidth="19200" windowHeight="8410"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -404,10 +404,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -425,9 +425,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -440,62 +446,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -508,16 +460,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -532,9 +477,48 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -543,6 +527,14 @@
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -556,7 +548,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -578,7 +578,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -590,7 +596,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -602,19 +620,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -632,37 +704,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -674,7 +716,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -686,79 +752,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -769,21 +769,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -805,7 +790,18 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -826,35 +822,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -869,6 +836,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -877,16 +877,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -895,127 +895,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2271,7 +2271,7 @@
         <v>0</v>
       </c>
       <c r="AD8">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AE8">
         <v>0</v>
@@ -2383,7 +2383,7 @@
         <v>0</v>
       </c>
       <c r="AD9">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AE9">
         <v>0</v>
@@ -2495,7 +2495,7 @@
         <v>0</v>
       </c>
       <c r="AD10">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AE10">
         <v>0</v>
@@ -2607,7 +2607,7 @@
         <v>0</v>
       </c>
       <c r="AD11">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AE11">
         <v>0</v>
@@ -2719,7 +2719,7 @@
         <v>0</v>
       </c>
       <c r="AD12">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AE12">
         <v>0</v>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8410"/>
+    <workbookView windowWidth="19200" windowHeight="8410" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -245,7 +245,8 @@
 全体的にステータスが高く、赤属性魔法を習得することでさらに攻撃性能を伸ばすことができる。</t>
   </si>
   <si>
-    <t>立場に縛られて…私は</t>
+    <t>家名を重んじて…
+悪いことなどあるはずがない！</t>
   </si>
   <si>
     <t>エリザベート</t>
@@ -258,7 +259,8 @@
 打たれ弱いがSPDが高く、回避率をアップする雷属性魔法を習得しやすい。</t>
   </si>
   <si>
-    <t>先陣を切るのはアタシだ！</t>
+    <t>また見たかった景色
+…だったはずなのに</t>
   </si>
   <si>
     <t>アリエス</t>
@@ -271,7 +273,8 @@
 受けた攻撃ダメージの一部を跳ね返す「カウンターオーラ」を使うことができる。</t>
   </si>
   <si>
-    <t>外の世界は怖いから…ずっとここにいたい</t>
+    <t>愚かでも良いの
+それが私の答えだから</t>
   </si>
   <si>
     <t>シイナ</t>
@@ -284,7 +287,7 @@
 全体的にステータスが低いが、味方のHpを回復する「ヒーリング」を使うことができる。</t>
   </si>
   <si>
-    <t>生きる理由は、もうどこにもないから</t>
+    <t>もう終わりにしたいんです</t>
   </si>
   <si>
     <t>レダ</t>
@@ -297,10 +300,11 @@
 「シェイディークラウド」で味方が受けるダメージを抑えたり、「毒」でスリップダメージを与える魔法を使うことができる。</t>
   </si>
   <si>
-    <t>知を得るために魂を授けろって…上等じゃない</t>
-  </si>
-  <si>
-    <t>リシェリ</t>
+    <t>何も悪いことしてないのに
+…どうしてこんなことに？</t>
+  </si>
+  <si>
+    <t>カイル</t>
   </si>
   <si>
     <t>【Faked-Magician】</t>
@@ -310,10 +314,11 @@
 CT（魔法を再使用するまでのターン数）を短縮しパーティ全体の補助をすることができる。</t>
   </si>
   <si>
-    <t>このまま待っているだけなんて、嫌だよ</t>
-  </si>
-  <si>
-    <t>ユニ</t>
+    <t>革命を起こしたって
+結局何も変わらないじゃないか…</t>
+  </si>
+  <si>
+    <t>セファル</t>
   </si>
   <si>
     <t>【奇跡の乙女】</t>
@@ -323,10 +328,11 @@
 「アウトオブオーダー」で両隣に配置した味方の行動待機時間を短縮したり、味方のATK・DEFをアップするバフ魔法を使うことができる。</t>
   </si>
   <si>
-    <t>ワタシは王子を信じている、たとえ塵になろうとも</t>
-  </si>
-  <si>
-    <t>マリーベル</t>
+    <t>ちょっと待ってよ！
+アタシにだって良いところあるはずだから！</t>
+  </si>
+  <si>
+    <t>コルト</t>
   </si>
   <si>
     <t>【唯心の在処】</t>
@@ -336,10 +342,10 @@
 「アクアミラージュ」で一定回数攻撃を無効にしたり、味方の攻撃を代わりに受けパーティの生存率を上げることができる。</t>
   </si>
   <si>
-    <t>ただの傭兵稼業をしているつもりだったんだけどね</t>
-  </si>
-  <si>
-    <t>ナツキ</t>
+    <t>僕だけ生き残っても仕方ないから</t>
+  </si>
+  <si>
+    <t>オスカー</t>
   </si>
   <si>
     <t>【黄昏ニヒリスト】</t>
@@ -349,10 +355,11 @@
 Hpが低いがATKが高く、攻撃回数の多い「フレイムレイン」を使うことができる。</t>
   </si>
   <si>
-    <t>敵、ならば殲滅あるのみ</t>
-  </si>
-  <si>
-    <t>メリアドール</t>
+    <t>困ったことに…
+運命に縛られているのは私も同じなのですよ</t>
+  </si>
+  <si>
+    <t>朧</t>
   </si>
   <si>
     <t>【怨嗟の鎖】</t>
@@ -362,7 +369,7 @@
 「ショックインパルス」で相手を行動不可にすることができる。</t>
   </si>
   <si>
-    <t>あたしはこんな力持ちたくなかったのに</t>
+    <t>ただ考えるようにしただけなんだ</t>
   </si>
   <si>
     <t>セリナ</t>
@@ -404,10 +411,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -433,9 +440,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -446,10 +461,43 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -468,8 +516,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -477,15 +526,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -498,17 +539,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -522,48 +561,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -578,7 +585,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -590,13 +699,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -608,25 +717,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -638,31 +729,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -674,25 +753,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -704,61 +765,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -769,6 +776,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -790,34 +806,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
+      <bottom style="medium">
         <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -840,17 +830,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -869,6 +850,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -877,151 +884,154 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1389,7 +1399,7 @@
     <col min="3" max="3" width="11.6363636363636" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
     <col min="5" max="5" width="7.54545454545455" customWidth="1"/>
-    <col min="6" max="6" width="9" style="2"/>
+    <col min="6" max="6" width="9" style="3"/>
     <col min="7" max="7" width="6.18181818181818" customWidth="1"/>
     <col min="8" max="8" width="6.81818181818182" customWidth="1"/>
     <col min="9" max="9" width="6.45454545454545" customWidth="1"/>
@@ -1414,7 +1424,7 @@
       <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G1" t="s">
@@ -1438,10 +1448,10 @@
       <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="5" t="s">
         <v>13</v>
       </c>
       <c r="P1" t="s">
@@ -1459,10 +1469,10 @@
       <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="V1" s="5" t="s">
         <v>20</v>
       </c>
       <c r="W1" t="s">
@@ -1526,7 +1536,7 @@
       <c r="E2">
         <v>20</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G2">
@@ -1638,7 +1648,7 @@
       <c r="E3">
         <v>30</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G3">
@@ -1750,7 +1760,7 @@
       <c r="E4">
         <v>30</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G4">
@@ -1862,7 +1872,7 @@
       <c r="E5">
         <v>30</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>38</v>
       </c>
       <c r="G5">
@@ -1974,7 +1984,7 @@
       <c r="E6">
         <v>30</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G6">
@@ -2077,7 +2087,7 @@
       </c>
       <c r="C7" t="str">
         <f>INDEX(TextData!B:B,MATCH(B7,TextData!A:A))</f>
-        <v>リシェリ</v>
+        <v>カイル</v>
       </c>
       <c r="D7" t="str">
         <f>INDEX(TextData!C:C,MATCH(B7,TextData!A:A))</f>
@@ -2086,7 +2096,7 @@
       <c r="E7">
         <v>99</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>40</v>
       </c>
       <c r="G7">
@@ -2189,7 +2199,7 @@
       </c>
       <c r="C8" t="str">
         <f>INDEX(TextData!B:B,MATCH(B8,TextData!A:A))</f>
-        <v>ユニ</v>
+        <v>セファル</v>
       </c>
       <c r="D8" t="str">
         <f>INDEX(TextData!C:C,MATCH(B8,TextData!A:A))</f>
@@ -2198,7 +2208,7 @@
       <c r="E8">
         <v>99</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>41</v>
       </c>
       <c r="G8">
@@ -2301,7 +2311,7 @@
       </c>
       <c r="C9" t="str">
         <f>INDEX(TextData!B:B,MATCH(B9,TextData!A:A))</f>
-        <v>マリーベル</v>
+        <v>コルト</v>
       </c>
       <c r="D9" t="str">
         <f>INDEX(TextData!C:C,MATCH(B9,TextData!A:A))</f>
@@ -2310,7 +2320,7 @@
       <c r="E9">
         <v>99</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G9">
@@ -2413,7 +2423,7 @@
       </c>
       <c r="C10" t="str">
         <f>INDEX(TextData!B:B,MATCH(B10,TextData!A:A))</f>
-        <v>ナツキ</v>
+        <v>オスカー</v>
       </c>
       <c r="D10" t="str">
         <f>INDEX(TextData!C:C,MATCH(B10,TextData!A:A))</f>
@@ -2422,7 +2432,7 @@
       <c r="E10">
         <v>99</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="3" t="s">
         <v>43</v>
       </c>
       <c r="G10">
@@ -2525,7 +2535,7 @@
       </c>
       <c r="C11" t="str">
         <f>INDEX(TextData!B:B,MATCH(B11,TextData!A:A))</f>
-        <v>メリアドール</v>
+        <v>朧</v>
       </c>
       <c r="D11" t="str">
         <f>INDEX(TextData!C:C,MATCH(B11,TextData!A:A))</f>
@@ -2534,7 +2544,7 @@
       <c r="E11">
         <v>99</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="3" t="s">
         <v>44</v>
       </c>
       <c r="G11">
@@ -2646,7 +2656,7 @@
       <c r="E12">
         <v>99</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="3" t="s">
         <v>45</v>
       </c>
       <c r="G12">
@@ -2758,7 +2768,7 @@
       <c r="E13">
         <v>10</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="3" t="s">
         <v>46</v>
       </c>
       <c r="G13">
@@ -2870,7 +2880,7 @@
       <c r="E14">
         <v>10</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="3" t="s">
         <v>47</v>
       </c>
       <c r="G14">
@@ -2982,7 +2992,7 @@
       <c r="E15">
         <v>10</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="3" t="s">
         <v>48</v>
       </c>
       <c r="G15">
@@ -3094,7 +3104,7 @@
       <c r="E16">
         <v>10</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="3" t="s">
         <v>49</v>
       </c>
       <c r="G16">
@@ -3201,14 +3211,14 @@
   <dimension ref="A1:C76"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
-    <col min="2" max="2" width="44.2727272727273" style="2" customWidth="1"/>
+    <col min="2" max="2" width="44.2727272727273" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C1" t="s">
@@ -3274,7 +3284,7 @@
       <c r="A7">
         <v>1</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="4">
         <v>100110</v>
       </c>
       <c r="C7">
@@ -3285,7 +3295,7 @@
       <c r="A8">
         <v>1</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="4">
         <v>100120</v>
       </c>
       <c r="C8">
@@ -3348,7 +3358,7 @@
       <c r="A14">
         <v>2</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="4">
         <v>100210</v>
       </c>
       <c r="C14">
@@ -3359,7 +3369,7 @@
       <c r="A15">
         <v>2</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="4">
         <v>100220</v>
       </c>
       <c r="C15">
@@ -3422,7 +3432,7 @@
       <c r="A21">
         <v>3</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="4">
         <v>100310</v>
       </c>
       <c r="C21">
@@ -3433,7 +3443,7 @@
       <c r="A22">
         <v>3</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="4">
         <v>100320</v>
       </c>
       <c r="C22">
@@ -3496,7 +3506,7 @@
       <c r="A28">
         <v>4</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="4">
         <v>100410</v>
       </c>
       <c r="C28">
@@ -3507,7 +3517,7 @@
       <c r="A29">
         <v>4</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="4">
         <v>100420</v>
       </c>
       <c r="C29">
@@ -3570,7 +3580,7 @@
       <c r="A35">
         <v>5</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B35" s="4">
         <v>100510</v>
       </c>
       <c r="C35">
@@ -3581,7 +3591,7 @@
       <c r="A36">
         <v>5</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B36" s="4">
         <v>100520</v>
       </c>
       <c r="C36">
@@ -5914,7 +5924,7 @@
       <c r="D2" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>75</v>
       </c>
     </row>
@@ -5931,7 +5941,7 @@
       <c r="D3" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>79</v>
       </c>
     </row>
@@ -5948,7 +5958,7 @@
       <c r="D4" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
         <v>83</v>
       </c>
     </row>
@@ -5982,7 +5992,7 @@
       <c r="D6" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="2" t="s">
         <v>91</v>
       </c>
     </row>
@@ -5999,7 +6009,7 @@
       <c r="D7" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="2" t="s">
         <v>95</v>
       </c>
     </row>
@@ -6016,7 +6026,7 @@
       <c r="D8" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="2" t="s">
         <v>99</v>
       </c>
     </row>
@@ -6050,7 +6060,7 @@
       <c r="D10" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="2" t="s">
         <v>107</v>
       </c>
     </row>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8410" activeTab="3"/>
+    <workbookView windowWidth="19200" windowHeight="8410"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -411,10 +411,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -440,6 +440,60 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -454,8 +508,37 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -470,22 +553,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -494,75 +561,8 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -591,13 +591,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -609,7 +621,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -627,13 +729,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -645,25 +741,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -675,97 +753,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -779,11 +779,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -803,26 +809,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -832,6 +838,15 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -847,21 +862,6 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -884,154 +884,151 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1399,7 +1396,7 @@
     <col min="3" max="3" width="11.6363636363636" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
     <col min="5" max="5" width="7.54545454545455" customWidth="1"/>
-    <col min="6" max="6" width="9" style="3"/>
+    <col min="6" max="6" width="9" style="2"/>
     <col min="7" max="7" width="6.18181818181818" customWidth="1"/>
     <col min="8" max="8" width="6.81818181818182" customWidth="1"/>
     <col min="9" max="9" width="6.45454545454545" customWidth="1"/>
@@ -1424,7 +1421,7 @@
       <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G1" t="s">
@@ -1448,10 +1445,10 @@
       <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="4" t="s">
         <v>13</v>
       </c>
       <c r="P1" t="s">
@@ -1469,10 +1466,10 @@
       <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="U1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="V1" s="4" t="s">
         <v>20</v>
       </c>
       <c r="W1" t="s">
@@ -1536,7 +1533,7 @@
       <c r="E2">
         <v>20</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G2">
@@ -1648,7 +1645,7 @@
       <c r="E3">
         <v>30</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>36</v>
       </c>
       <c r="G3">
@@ -1760,7 +1757,7 @@
       <c r="E4">
         <v>30</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>37</v>
       </c>
       <c r="G4">
@@ -1872,7 +1869,7 @@
       <c r="E5">
         <v>30</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>38</v>
       </c>
       <c r="G5">
@@ -1984,7 +1981,7 @@
       <c r="E6">
         <v>30</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="2" t="s">
         <v>39</v>
       </c>
       <c r="G6">
@@ -2096,7 +2093,7 @@
       <c r="E7">
         <v>99</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G7">
@@ -2208,7 +2205,7 @@
       <c r="E8">
         <v>99</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="2" t="s">
         <v>41</v>
       </c>
       <c r="G8">
@@ -2320,7 +2317,7 @@
       <c r="E9">
         <v>99</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="2" t="s">
         <v>42</v>
       </c>
       <c r="G9">
@@ -2432,7 +2429,7 @@
       <c r="E10">
         <v>99</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G10">
@@ -2544,7 +2541,7 @@
       <c r="E11">
         <v>99</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="2" t="s">
         <v>44</v>
       </c>
       <c r="G11">
@@ -2656,7 +2653,7 @@
       <c r="E12">
         <v>99</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="2" t="s">
         <v>45</v>
       </c>
       <c r="G12">
@@ -2768,7 +2765,7 @@
       <c r="E13">
         <v>10</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="2" t="s">
         <v>46</v>
       </c>
       <c r="G13">
@@ -2778,7 +2775,7 @@
         <v>99</v>
       </c>
       <c r="I13">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J13">
         <v>4</v>
@@ -2799,7 +2796,7 @@
         <v>2</v>
       </c>
       <c r="P13">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2880,7 +2877,7 @@
       <c r="E14">
         <v>10</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="2" t="s">
         <v>47</v>
       </c>
       <c r="G14">
@@ -2992,7 +2989,7 @@
       <c r="E15">
         <v>10</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="2" t="s">
         <v>48</v>
       </c>
       <c r="G15">
@@ -3104,7 +3101,7 @@
       <c r="E16">
         <v>10</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="2" t="s">
         <v>49</v>
       </c>
       <c r="G16">
@@ -3211,14 +3208,14 @@
   <dimension ref="A1:C76"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
-    <col min="2" max="2" width="44.2727272727273" style="3" customWidth="1"/>
+    <col min="2" max="2" width="44.2727272727273" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C1" t="s">
@@ -3284,7 +3281,7 @@
       <c r="A7">
         <v>1</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="3">
         <v>100110</v>
       </c>
       <c r="C7">
@@ -3295,7 +3292,7 @@
       <c r="A8">
         <v>1</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="3">
         <v>100120</v>
       </c>
       <c r="C8">
@@ -3358,7 +3355,7 @@
       <c r="A14">
         <v>2</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="3">
         <v>100210</v>
       </c>
       <c r="C14">
@@ -3369,7 +3366,7 @@
       <c r="A15">
         <v>2</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="3">
         <v>100220</v>
       </c>
       <c r="C15">
@@ -3432,7 +3429,7 @@
       <c r="A21">
         <v>3</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="3">
         <v>100310</v>
       </c>
       <c r="C21">
@@ -3443,7 +3440,7 @@
       <c r="A22">
         <v>3</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="3">
         <v>100320</v>
       </c>
       <c r="C22">
@@ -3506,7 +3503,7 @@
       <c r="A28">
         <v>4</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28" s="3">
         <v>100410</v>
       </c>
       <c r="C28">
@@ -3517,7 +3514,7 @@
       <c r="A29">
         <v>4</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29" s="3">
         <v>100420</v>
       </c>
       <c r="C29">
@@ -3580,7 +3577,7 @@
       <c r="A35">
         <v>5</v>
       </c>
-      <c r="B35" s="4">
+      <c r="B35" s="3">
         <v>100510</v>
       </c>
       <c r="C35">
@@ -3591,7 +3588,7 @@
       <c r="A36">
         <v>5</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B36" s="3">
         <v>100520</v>
       </c>
       <c r="C36">
@@ -5924,7 +5921,7 @@
       <c r="D2" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>75</v>
       </c>
     </row>
@@ -5941,7 +5938,7 @@
       <c r="D3" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>79</v>
       </c>
     </row>
@@ -5958,7 +5955,7 @@
       <c r="D4" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>83</v>
       </c>
     </row>
@@ -5992,7 +5989,7 @@
       <c r="D6" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1" t="s">
         <v>91</v>
       </c>
     </row>
@@ -6009,7 +6006,7 @@
       <c r="D7" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="1" t="s">
         <v>95</v>
       </c>
     </row>
@@ -6026,7 +6023,7 @@
       <c r="D8" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="1" t="s">
         <v>99</v>
       </c>
     </row>
@@ -6060,7 +6057,7 @@
       <c r="D10" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="1" t="s">
         <v>107</v>
       </c>
     </row>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -411,8 +411,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
@@ -433,6 +433,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -446,25 +453,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -485,58 +483,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -545,7 +491,7 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -562,7 +508,37 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -575,6 +551,30 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -582,54 +582,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -645,7 +597,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -657,19 +639,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -687,13 +681,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -705,67 +765,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -780,6 +780,48 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -790,21 +832,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -826,26 +853,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -865,17 +876,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -884,7 +884,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -893,7 +893,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -902,127 +902,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2787,7 +2787,7 @@
         <v>19</v>
       </c>
       <c r="M13">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="N13">
         <v>3</v>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="118">
   <si>
     <t>Id</t>
   </si>
@@ -40,6 +40,9 @@
     <t>MaxLv</t>
   </si>
   <si>
+    <t>AttributeType</t>
+  </si>
+  <si>
     <t>InitHp</t>
   </si>
   <si>
@@ -154,9 +157,6 @@
     <t>0010</t>
   </si>
   <si>
-    <t>0011</t>
-  </si>
-  <si>
     <t>0101</t>
   </si>
   <si>
@@ -206,9 +206,6 @@
   </si>
   <si>
     <t>11,21,31,2010,101010,101020</t>
-  </si>
-  <si>
-    <t>11,21,31,3010,101110,101120</t>
   </si>
   <si>
     <t>11,21,31,3010,110110,110120</t>
@@ -370,19 +367,6 @@
   </si>
   <si>
     <t>ただ考えるようにしただけなんだ</t>
-  </si>
-  <si>
-    <t>セリナ</t>
-  </si>
-  <si>
-    <t>【氷雪の勿忘草】</t>
-  </si>
-  <si>
-    <t>凍結攻撃を主体とするアタッカー。
-「ディープフリーズ」で攻撃時に一定量のダメージを受ける「凍結」状態にし、凍結効果をさらにアップすることで自滅に追い込むことができる。</t>
-  </si>
-  <si>
-    <t>どうして…ほおっておいてくれないのでしょうか</t>
   </si>
   <si>
     <t>シグルド</t>
@@ -411,10 +395,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -432,8 +416,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -447,83 +432,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -531,14 +447,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -554,7 +462,60 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -575,6 +536,29 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -585,79 +569,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -675,13 +599,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -693,31 +701,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -729,25 +731,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -759,13 +749,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -776,6 +760,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -796,26 +795,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -853,26 +836,27 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -884,145 +868,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1390,7 +1374,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AJ16"/>
+  <dimension ref="A1:AK15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="3" max="3" width="11.6363636363636" customWidth="1"/>
@@ -1398,14 +1382,14 @@
     <col min="5" max="5" width="7.54545454545455" customWidth="1"/>
     <col min="6" max="6" width="9" style="2"/>
     <col min="7" max="7" width="6.18181818181818" customWidth="1"/>
-    <col min="8" max="8" width="6.81818181818182" customWidth="1"/>
-    <col min="9" max="9" width="6.45454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6.63636363636364" customWidth="1"/>
-    <col min="11" max="12" width="7.09090909090909" customWidth="1"/>
-    <col min="13" max="15" width="7.36363636363636" customWidth="1"/>
+    <col min="8" max="9" width="6.81818181818182" customWidth="1"/>
+    <col min="10" max="10" width="6.45454545454545" customWidth="1"/>
+    <col min="11" max="11" width="6.63636363636364" customWidth="1"/>
+    <col min="12" max="13" width="7.09090909090909" customWidth="1"/>
+    <col min="14" max="16" width="7.36363636363636" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36">
+    <row r="1" spans="1:37">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1445,13 +1429,13 @@
       <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="4" t="s">
         <v>14</v>
       </c>
       <c r="Q1" t="s">
@@ -1466,13 +1450,13 @@
       <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" t="s">
         <v>19</v>
       </c>
       <c r="V1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="4" t="s">
         <v>21</v>
       </c>
       <c r="X1" t="s">
@@ -1514,8 +1498,11 @@
       <c r="AJ1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="2" spans="1:36">
+      <c r="AK1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:37">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1534,7 +1521,7 @@
         <v>20</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -1543,91 +1530,94 @@
         <v>99</v>
       </c>
       <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
         <v>32</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>4</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>30</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>15</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>16</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>3</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>2</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>135</v>
       </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
       <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
         <v>100</v>
       </c>
-      <c r="S2">
+      <c r="T2">
         <v>65</v>
       </c>
-      <c r="T2">
+      <c r="U2">
         <v>55</v>
       </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
       <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
         <v>50</v>
       </c>
-      <c r="W2">
-        <v>1</v>
-      </c>
       <c r="X2">
+        <v>1</v>
+      </c>
+      <c r="Y2">
         <v>3</v>
       </c>
-      <c r="Y2">
+      <c r="Z2">
         <v>6</v>
       </c>
-      <c r="Z2">
+      <c r="AA2">
         <v>4</v>
       </c>
-      <c r="AA2">
+      <c r="AB2">
         <v>6</v>
       </c>
-      <c r="AB2">
+      <c r="AC2">
         <v>-12</v>
       </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
       <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
         <v>0.8</v>
       </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
       <c r="AF2">
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH2">
+        <v>1</v>
+      </c>
+      <c r="AI2">
         <v>3</v>
       </c>
-      <c r="AI2">
-        <v>0</v>
-      </c>
       <c r="AJ2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:36">
+      <c r="AK2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1646,7 +1636,7 @@
         <v>30</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -1655,91 +1645,94 @@
         <v>99</v>
       </c>
       <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
         <v>24</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>5</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>22</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>6</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>28</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>4</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>2</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>115</v>
       </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
       <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
         <v>80</v>
       </c>
-      <c r="S3">
+      <c r="T3">
         <v>55</v>
       </c>
-      <c r="T3">
+      <c r="U3">
         <v>80</v>
       </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
       <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
         <v>50</v>
       </c>
-      <c r="W3">
+      <c r="X3">
         <v>3</v>
       </c>
-      <c r="X3">
-        <v>1</v>
-      </c>
       <c r="Y3">
+        <v>1</v>
+      </c>
+      <c r="Z3">
         <v>5</v>
       </c>
-      <c r="Z3">
+      <c r="AA3">
         <v>7</v>
       </c>
-      <c r="AA3">
+      <c r="AB3">
         <v>4</v>
       </c>
-      <c r="AB3">
+      <c r="AC3">
         <v>20</v>
       </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
       <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
         <v>0.8</v>
       </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
       <c r="AF3">
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH3">
         <v>1</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:36">
+      <c r="AK3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1758,7 +1751,7 @@
         <v>30</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -1767,13 +1760,13 @@
         <v>99</v>
       </c>
       <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4">
         <v>29</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>5</v>
-      </c>
-      <c r="K4">
-        <v>17</v>
       </c>
       <c r="L4">
         <v>17</v>
@@ -1782,76 +1775,79 @@
         <v>17</v>
       </c>
       <c r="N4">
+        <v>17</v>
+      </c>
+      <c r="O4">
         <v>3</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>2</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>130</v>
       </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
       <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
         <v>60</v>
       </c>
-      <c r="S4">
+      <c r="T4">
         <v>80</v>
       </c>
-      <c r="T4">
+      <c r="U4">
         <v>60</v>
       </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
       <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
         <v>50</v>
       </c>
-      <c r="W4">
+      <c r="X4">
         <v>4</v>
       </c>
-      <c r="X4">
+      <c r="Y4">
         <v>6</v>
       </c>
-      <c r="Y4">
-        <v>1</v>
-      </c>
       <c r="Z4">
+        <v>1</v>
+      </c>
+      <c r="AA4">
         <v>3</v>
       </c>
-      <c r="AA4">
+      <c r="AB4">
         <v>6</v>
       </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
       <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
         <v>-16</v>
       </c>
-      <c r="AD4">
+      <c r="AE4">
         <v>0.77</v>
       </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
       <c r="AF4">
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH4">
+        <v>1</v>
+      </c>
+      <c r="AI4">
         <v>2</v>
       </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
       <c r="AJ4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:36">
+      <c r="AK4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1870,7 +1866,7 @@
         <v>30</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1879,91 +1875,94 @@
         <v>99</v>
       </c>
       <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
         <v>34</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>4</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>15</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>9</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>22</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>3</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>2</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>160</v>
       </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
       <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
         <v>65</v>
       </c>
-      <c r="S5">
+      <c r="T5">
         <v>60</v>
       </c>
-      <c r="T5">
+      <c r="U5">
         <v>65</v>
       </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
       <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
         <v>50</v>
       </c>
-      <c r="W5">
+      <c r="X5">
         <v>5</v>
       </c>
-      <c r="X5">
+      <c r="Y5">
         <v>4</v>
       </c>
-      <c r="Y5">
+      <c r="Z5">
         <v>3</v>
       </c>
-      <c r="Z5">
-        <v>1</v>
-      </c>
       <c r="AA5">
+        <v>1</v>
+      </c>
+      <c r="AB5">
         <v>7</v>
       </c>
-      <c r="AB5">
+      <c r="AC5">
         <v>-16</v>
       </c>
-      <c r="AC5">
+      <c r="AD5">
         <v>16</v>
       </c>
-      <c r="AD5">
+      <c r="AE5">
         <v>0.77</v>
       </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
       <c r="AF5">
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH5">
+        <v>1</v>
+      </c>
+      <c r="AI5">
         <v>5</v>
       </c>
-      <c r="AI5">
-        <v>0</v>
-      </c>
       <c r="AJ5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:36">
+      <c r="AK5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1982,7 +1981,7 @@
         <v>30</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1991,91 +1990,94 @@
         <v>99</v>
       </c>
       <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
         <v>30</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>4</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>20</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>11</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>19</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>3</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>2</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>120</v>
       </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
       <c r="R6">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="S6">
         <v>80</v>
       </c>
       <c r="T6">
+        <v>80</v>
+      </c>
+      <c r="U6">
         <v>65</v>
       </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
       <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
         <v>50</v>
       </c>
-      <c r="W6">
+      <c r="X6">
         <v>5</v>
       </c>
-      <c r="X6">
+      <c r="Y6">
         <v>6</v>
       </c>
-      <c r="Y6">
+      <c r="Z6">
         <v>3</v>
       </c>
-      <c r="Z6">
+      <c r="AA6">
         <v>5</v>
       </c>
-      <c r="AA6">
-        <v>1</v>
-      </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
         <v>-24</v>
       </c>
-      <c r="AD6">
+      <c r="AE6">
         <v>0.8</v>
       </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
       <c r="AF6">
         <v>0</v>
       </c>
       <c r="AG6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH6">
+        <v>1</v>
+      </c>
+      <c r="AI6">
         <v>4</v>
       </c>
-      <c r="AI6">
-        <v>0</v>
-      </c>
       <c r="AJ6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:36">
+      <c r="AK6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2094,7 +2096,7 @@
         <v>99</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -2103,91 +2105,94 @@
         <v>99</v>
       </c>
       <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
         <v>30</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>4</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>18</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>12</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>20</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>3</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>2</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>100</v>
       </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
       <c r="R7">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <v>80</v>
       </c>
       <c r="T7">
+        <v>80</v>
+      </c>
+      <c r="U7">
         <v>70</v>
       </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
       <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
         <v>50</v>
       </c>
-      <c r="W7">
-        <v>1</v>
-      </c>
       <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="Y7">
         <v>6</v>
       </c>
-      <c r="Y7">
+      <c r="Z7">
         <v>2</v>
       </c>
-      <c r="Z7">
+      <c r="AA7">
         <v>6</v>
       </c>
-      <c r="AA7">
+      <c r="AB7">
         <v>3</v>
       </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
       <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
         <v>16</v>
       </c>
-      <c r="AD7">
+      <c r="AE7">
         <v>0.77</v>
       </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
       <c r="AF7">
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH7">
+        <v>1</v>
+      </c>
+      <c r="AI7">
         <v>3</v>
       </c>
-      <c r="AI7">
-        <v>0</v>
-      </c>
       <c r="AJ7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:36">
+      <c r="AK7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2206,7 +2211,7 @@
         <v>99</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -2215,91 +2220,94 @@
         <v>99</v>
       </c>
       <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8">
         <v>32</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>4</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>18</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>15</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>16</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>4</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>2</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>120</v>
       </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
       <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
         <v>80</v>
       </c>
-      <c r="S8">
+      <c r="T8">
         <v>75</v>
       </c>
-      <c r="T8">
+      <c r="U8">
         <v>55</v>
       </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
       <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
         <v>50</v>
       </c>
-      <c r="W8">
+      <c r="X8">
         <v>4</v>
       </c>
-      <c r="X8">
-        <v>1</v>
-      </c>
       <c r="Y8">
+        <v>1</v>
+      </c>
+      <c r="Z8">
         <v>4</v>
       </c>
-      <c r="Z8">
+      <c r="AA8">
         <v>3</v>
       </c>
-      <c r="AA8">
+      <c r="AB8">
         <v>4</v>
       </c>
-      <c r="AB8">
-        <v>0</v>
-      </c>
       <c r="AC8">
         <v>0</v>
       </c>
       <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
         <v>0.8</v>
       </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
       <c r="AF8">
         <v>0</v>
       </c>
       <c r="AG8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH8">
         <v>1</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:36">
+      <c r="AK8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2318,7 +2326,7 @@
         <v>99</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -2327,91 +2335,94 @@
         <v>99</v>
       </c>
       <c r="I9">
+        <v>3</v>
+      </c>
+      <c r="J9">
         <v>35</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>4</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>12</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>19</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>14</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>3</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>2</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>120</v>
       </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
       <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
         <v>60</v>
       </c>
-      <c r="S9">
+      <c r="T9">
         <v>95</v>
       </c>
-      <c r="T9">
+      <c r="U9">
         <v>55</v>
       </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
       <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
         <v>50</v>
       </c>
-      <c r="W9">
+      <c r="X9">
         <v>6</v>
       </c>
-      <c r="X9">
+      <c r="Y9">
         <v>2</v>
       </c>
-      <c r="Y9">
-        <v>1</v>
-      </c>
       <c r="Z9">
+        <v>1</v>
+      </c>
+      <c r="AA9">
         <v>5</v>
       </c>
-      <c r="AA9">
+      <c r="AB9">
         <v>4</v>
       </c>
-      <c r="AB9">
-        <v>0</v>
-      </c>
       <c r="AC9">
         <v>0</v>
       </c>
       <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
         <v>0.8</v>
       </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
       <c r="AF9">
         <v>0</v>
       </c>
       <c r="AG9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH9">
+        <v>1</v>
+      </c>
+      <c r="AI9">
         <v>2</v>
       </c>
-      <c r="AI9">
-        <v>0</v>
-      </c>
       <c r="AJ9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:36">
+      <c r="AK9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2430,7 +2441,7 @@
         <v>99</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -2439,91 +2450,94 @@
         <v>99</v>
       </c>
       <c r="I10">
+        <v>4</v>
+      </c>
+      <c r="J10">
         <v>26</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>4</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>25</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>8</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>21</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>3</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>2</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>90</v>
       </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
       <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
         <v>110</v>
       </c>
-      <c r="S10">
+      <c r="T10">
         <v>60</v>
       </c>
-      <c r="T10">
+      <c r="U10">
         <v>70</v>
       </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
       <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
         <v>50</v>
       </c>
-      <c r="W10">
-        <v>1</v>
-      </c>
       <c r="X10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y10">
         <v>4</v>
       </c>
       <c r="Z10">
+        <v>4</v>
+      </c>
+      <c r="AA10">
         <v>7</v>
       </c>
-      <c r="AA10">
+      <c r="AB10">
         <v>2</v>
       </c>
-      <c r="AB10">
-        <v>0</v>
-      </c>
       <c r="AC10">
         <v>0</v>
       </c>
       <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
         <v>0.8</v>
       </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
       <c r="AF10">
         <v>0</v>
       </c>
       <c r="AG10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH10">
+        <v>1</v>
+      </c>
+      <c r="AI10">
         <v>3</v>
       </c>
-      <c r="AI10">
-        <v>0</v>
-      </c>
       <c r="AJ10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:36">
+      <c r="AK10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2542,7 +2556,7 @@
         <v>99</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -2551,110 +2565,113 @@
         <v>99</v>
       </c>
       <c r="I11">
+        <v>5</v>
+      </c>
+      <c r="J11">
         <v>25</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>4</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>17</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>7</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>31</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>4</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>2</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>100</v>
       </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
       <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
         <v>70</v>
       </c>
-      <c r="S11">
+      <c r="T11">
         <v>60</v>
       </c>
-      <c r="T11">
+      <c r="U11">
         <v>85</v>
       </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
       <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
         <v>50</v>
       </c>
-      <c r="W11">
+      <c r="X11">
         <v>4</v>
       </c>
-      <c r="X11">
-        <v>1</v>
-      </c>
       <c r="Y11">
+        <v>1</v>
+      </c>
+      <c r="Z11">
         <v>6</v>
       </c>
-      <c r="Z11">
+      <c r="AA11">
         <v>5</v>
       </c>
-      <c r="AA11">
+      <c r="AB11">
         <v>2</v>
       </c>
-      <c r="AB11">
-        <v>0</v>
-      </c>
       <c r="AC11">
         <v>0</v>
       </c>
       <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
         <v>0.8</v>
       </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
       <c r="AF11">
         <v>0</v>
       </c>
       <c r="AG11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH11">
         <v>1</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:36">
+      <c r="AK11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37">
       <c r="A12">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="B12">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="C12" t="str">
         <f>INDEX(TextData!B:B,MATCH(B12,TextData!A:A))</f>
-        <v>セリナ</v>
+        <v>シグルド</v>
       </c>
       <c r="D12" t="str">
         <f>INDEX(TextData!C:C,MATCH(B12,TextData!A:A))</f>
-        <v>【氷雪の勿忘草】</v>
+        <v>【竜殺し】</v>
       </c>
       <c r="E12">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -2663,82 +2680,82 @@
         <v>99</v>
       </c>
       <c r="I12">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="J12">
+        <v>41</v>
+      </c>
+      <c r="K12">
         <v>4</v>
       </c>
-      <c r="K12">
+      <c r="L12">
+        <v>25</v>
+      </c>
+      <c r="M12">
+        <v>19</v>
+      </c>
+      <c r="N12">
         <v>18</v>
       </c>
-      <c r="L12">
-        <v>15</v>
-      </c>
-      <c r="M12">
-        <v>17</v>
-      </c>
-      <c r="N12">
+      <c r="O12">
         <v>3</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>2</v>
       </c>
-      <c r="P12">
-        <v>115</v>
-      </c>
       <c r="Q12">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="R12">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="T12">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
         <v>50</v>
       </c>
-      <c r="W12">
+      <c r="X12">
+        <v>4</v>
+      </c>
+      <c r="Y12">
         <v>6</v>
       </c>
-      <c r="X12">
-        <v>6</v>
-      </c>
-      <c r="Y12">
-        <v>1</v>
-      </c>
       <c r="Z12">
+        <v>1</v>
+      </c>
+      <c r="AA12">
         <v>3</v>
       </c>
-      <c r="AA12">
-        <v>2</v>
-      </c>
       <c r="AB12">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AD12">
-        <v>0.8</v>
+        <v>-64</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AF12">
         <v>0</v>
       </c>
       <c r="AG12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI12">
         <v>0</v>
@@ -2746,27 +2763,30 @@
       <c r="AJ12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:36">
+      <c r="AK12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37">
       <c r="A13">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B13">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C13" t="str">
         <f>INDEX(TextData!B:B,MATCH(B13,TextData!A:A))</f>
-        <v>シグルド</v>
+        <v>ブリュンヒルデ</v>
       </c>
       <c r="D13" t="str">
         <f>INDEX(TextData!C:C,MATCH(B13,TextData!A:A))</f>
-        <v>【竜殺し】</v>
+        <v>【悲劇の戦乙女】</v>
       </c>
       <c r="E13">
         <v>10</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -2775,82 +2795,82 @@
         <v>99</v>
       </c>
       <c r="I13">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="J13">
+        <v>34</v>
+      </c>
+      <c r="K13">
         <v>4</v>
       </c>
-      <c r="K13">
+      <c r="L13">
+        <v>32</v>
+      </c>
+      <c r="M13">
+        <v>6</v>
+      </c>
+      <c r="N13">
         <v>25</v>
       </c>
-      <c r="L13">
-        <v>19</v>
-      </c>
-      <c r="M13">
-        <v>18</v>
-      </c>
-      <c r="N13">
-        <v>3</v>
-      </c>
       <c r="O13">
+        <v>4</v>
+      </c>
+      <c r="P13">
         <v>2</v>
       </c>
-      <c r="P13">
-        <v>160</v>
-      </c>
       <c r="Q13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="R13">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="T13">
         <v>50</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
         <v>50</v>
       </c>
-      <c r="W13">
+      <c r="X13">
+        <v>3</v>
+      </c>
+      <c r="Y13">
         <v>4</v>
       </c>
-      <c r="X13">
-        <v>6</v>
-      </c>
-      <c r="Y13">
-        <v>1</v>
-      </c>
       <c r="Z13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB13">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="AC13">
-        <v>-64</v>
+        <v>0</v>
       </c>
       <c r="AD13">
-        <v>0.86</v>
+        <v>-12</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AF13">
         <v>0</v>
       </c>
       <c r="AG13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI13">
         <v>0</v>
@@ -2858,27 +2878,30 @@
       <c r="AJ13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:36">
+      <c r="AK13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37">
       <c r="A14">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B14">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C14" t="str">
         <f>INDEX(TextData!B:B,MATCH(B14,TextData!A:A))</f>
-        <v>ブリュンヒルデ</v>
+        <v>シグムント</v>
       </c>
       <c r="D14" t="str">
         <f>INDEX(TextData!C:C,MATCH(B14,TextData!A:A))</f>
-        <v>【悲劇の戦乙女】</v>
+        <v>【竜殺し】</v>
       </c>
       <c r="E14">
         <v>10</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -2887,82 +2910,82 @@
         <v>99</v>
       </c>
       <c r="I14">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="J14">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="K14">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="L14">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="M14">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N14">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="O14">
+        <v>3</v>
+      </c>
+      <c r="P14">
         <v>2</v>
       </c>
-      <c r="P14">
-        <v>120</v>
-      </c>
       <c r="Q14">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="R14">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="S14">
+        <v>60</v>
+      </c>
+      <c r="T14">
+        <v>80</v>
+      </c>
+      <c r="U14">
+        <v>60</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
         <v>50</v>
-      </c>
-      <c r="T14">
-        <v>110</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14">
-        <v>50</v>
-      </c>
-      <c r="W14">
-        <v>3</v>
       </c>
       <c r="X14">
         <v>4</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AC14">
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="AD14">
-        <v>0.8</v>
+        <v>-64</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AF14">
         <v>0</v>
       </c>
       <c r="AG14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI14">
         <v>0</v>
@@ -2970,27 +2993,30 @@
       <c r="AJ14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:36">
+      <c r="AK14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37">
       <c r="A15">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B15">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C15" t="str">
         <f>INDEX(TextData!B:B,MATCH(B15,TextData!A:A))</f>
-        <v>シグムント</v>
+        <v>ヨルディス</v>
       </c>
       <c r="D15" t="str">
         <f>INDEX(TextData!C:C,MATCH(B15,TextData!A:A))</f>
-        <v>【竜殺し】</v>
+        <v>【悲劇の戦乙女】</v>
       </c>
       <c r="E15">
         <v>10</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -2999,82 +3025,82 @@
         <v>99</v>
       </c>
       <c r="I15">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J15">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="K15">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="L15">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M15">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="N15">
+        <v>22</v>
+      </c>
+      <c r="O15">
         <v>3</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>2</v>
       </c>
-      <c r="P15">
-        <v>130</v>
-      </c>
       <c r="Q15">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="R15">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="T15">
         <v>60</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
         <v>50</v>
       </c>
-      <c r="W15">
+      <c r="X15">
+        <v>5</v>
+      </c>
+      <c r="Y15">
         <v>4</v>
-      </c>
-      <c r="X15">
-        <v>6</v>
-      </c>
-      <c r="Y15">
-        <v>1</v>
       </c>
       <c r="Z15">
         <v>3</v>
       </c>
       <c r="AA15">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AB15">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="AC15">
-        <v>-64</v>
+        <v>0</v>
       </c>
       <c r="AD15">
-        <v>0.86</v>
+        <v>-12</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AF15">
         <v>0</v>
       </c>
       <c r="AG15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI15">
         <v>0</v>
@@ -3082,116 +3108,7 @@
       <c r="AJ15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:36">
-      <c r="A16">
-        <v>104</v>
-      </c>
-      <c r="B16">
-        <v>104</v>
-      </c>
-      <c r="C16" t="str">
-        <f>INDEX(TextData!B:B,MATCH(B16,TextData!A:A))</f>
-        <v>ヨルディス</v>
-      </c>
-      <c r="D16" t="str">
-        <f>INDEX(TextData!C:C,MATCH(B16,TextData!A:A))</f>
-        <v>【悲劇の戦乙女】</v>
-      </c>
-      <c r="E16">
-        <v>10</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-      <c r="H16">
-        <v>99</v>
-      </c>
-      <c r="I16">
-        <v>34</v>
-      </c>
-      <c r="J16">
-        <v>4</v>
-      </c>
-      <c r="K16">
-        <v>15</v>
-      </c>
-      <c r="L16">
-        <v>9</v>
-      </c>
-      <c r="M16">
-        <v>22</v>
-      </c>
-      <c r="N16">
-        <v>3</v>
-      </c>
-      <c r="O16">
-        <v>2</v>
-      </c>
-      <c r="P16">
-        <v>160</v>
-      </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>65</v>
-      </c>
-      <c r="S16">
-        <v>60</v>
-      </c>
-      <c r="T16">
-        <v>65</v>
-      </c>
-      <c r="U16">
-        <v>0</v>
-      </c>
-      <c r="V16">
-        <v>50</v>
-      </c>
-      <c r="W16">
-        <v>5</v>
-      </c>
-      <c r="X16">
-        <v>4</v>
-      </c>
-      <c r="Y16">
-        <v>3</v>
-      </c>
-      <c r="Z16">
-        <v>1</v>
-      </c>
-      <c r="AA16">
-        <v>1</v>
-      </c>
-      <c r="AB16">
-        <v>0</v>
-      </c>
-      <c r="AC16">
-        <v>-12</v>
-      </c>
-      <c r="AD16">
-        <v>0.8</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>0</v>
-      </c>
-      <c r="AG16">
-        <v>1</v>
-      </c>
-      <c r="AH16">
-        <v>0</v>
-      </c>
-      <c r="AI16">
-        <v>0</v>
-      </c>
-      <c r="AJ16">
+      <c r="AK15">
         <v>0</v>
       </c>
     </row>
@@ -3205,7 +3122,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C76"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="44.2727272727273" style="2" customWidth="1"/>
@@ -3857,7 +3774,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="B62" t="s">
         <v>63</v>
@@ -3865,21 +3782,21 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="B63">
-        <v>3050</v>
+        <v>13100</v>
       </c>
       <c r="C63">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="B64">
-        <v>13090</v>
+        <v>13080</v>
       </c>
       <c r="C64">
         <v>11</v>
@@ -3887,10 +3804,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="B65">
-        <v>403050</v>
+        <v>403010</v>
       </c>
       <c r="C65">
         <v>26</v>
@@ -3898,10 +3815,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="B66">
-        <v>3080</v>
+        <v>3040</v>
       </c>
       <c r="C66">
         <v>41</v>
@@ -3909,7 +3826,7 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B67" t="s">
         <v>64</v>
@@ -3917,10 +3834,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B68">
-        <v>13100</v>
+        <v>5070</v>
       </c>
       <c r="C68">
         <v>3</v>
@@ -3928,10 +3845,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B69">
-        <v>13080</v>
+        <v>15090</v>
       </c>
       <c r="C69">
         <v>11</v>
@@ -3939,10 +3856,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B70">
-        <v>403010</v>
+        <v>405070</v>
       </c>
       <c r="C70">
         <v>26</v>
@@ -3950,64 +3867,12 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B71">
-        <v>3040</v>
+        <v>5040</v>
       </c>
       <c r="C71">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
-      <c r="A72">
-        <v>102</v>
-      </c>
-      <c r="B72" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73">
-        <v>102</v>
-      </c>
-      <c r="B73">
-        <v>5070</v>
-      </c>
-      <c r="C73">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="A74">
-        <v>102</v>
-      </c>
-      <c r="B74">
-        <v>15090</v>
-      </c>
-      <c r="C74">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
-      <c r="A75">
-        <v>102</v>
-      </c>
-      <c r="B75">
-        <v>405070</v>
-      </c>
-      <c r="C75">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="A76">
-        <v>102</v>
-      </c>
-      <c r="B76">
-        <v>5040</v>
-      </c>
-      <c r="C76">
         <v>41</v>
       </c>
     </row>
@@ -4020,7 +3885,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D132"/>
+  <dimension ref="A1:D121"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="3"/>
   <cols>
     <col min="3" max="4" width="12.9090909090909" customWidth="1"/>
@@ -4034,10 +3899,10 @@
         <v>51</v>
       </c>
       <c r="C1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" t="s">
         <v>66</v>
-      </c>
-      <c r="D1" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -5442,13 +5307,13 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="B102">
-        <v>3050</v>
+        <v>3010</v>
       </c>
       <c r="C102">
-        <v>6712</v>
+        <v>0</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -5456,10 +5321,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="B103">
-        <v>101120</v>
+        <v>100320</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -5470,10 +5335,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="B104">
-        <v>3010</v>
+        <v>13100</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -5484,10 +5349,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="B105">
-        <v>101110</v>
+        <v>100310</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -5498,7 +5363,7 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -5512,7 +5377,7 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -5526,7 +5391,7 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -5540,7 +5405,7 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -5554,7 +5419,7 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -5568,7 +5433,7 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -5582,10 +5447,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112">
-        <v>11</v>
+        <v>102</v>
       </c>
       <c r="B112">
-        <v>0</v>
+        <v>100520</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -5596,10 +5461,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B113">
-        <v>3010</v>
+        <v>5070</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -5610,10 +5475,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B114">
-        <v>100320</v>
+        <v>5010</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -5624,10 +5489,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B115">
-        <v>13100</v>
+        <v>100510</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -5638,10 +5503,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B116">
-        <v>100310</v>
+        <v>0</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -5652,7 +5517,7 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -5666,7 +5531,7 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -5680,7 +5545,7 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -5694,7 +5559,7 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -5708,7 +5573,7 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -5717,160 +5582,6 @@
         <v>0</v>
       </c>
       <c r="D121">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4">
-      <c r="A122">
-        <v>101</v>
-      </c>
-      <c r="B122">
-        <v>0</v>
-      </c>
-      <c r="C122">
-        <v>0</v>
-      </c>
-      <c r="D122">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4">
-      <c r="A123">
-        <v>102</v>
-      </c>
-      <c r="B123">
-        <v>100520</v>
-      </c>
-      <c r="C123">
-        <v>0</v>
-      </c>
-      <c r="D123">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4">
-      <c r="A124">
-        <v>102</v>
-      </c>
-      <c r="B124">
-        <v>5070</v>
-      </c>
-      <c r="C124">
-        <v>0</v>
-      </c>
-      <c r="D124">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4">
-      <c r="A125">
-        <v>102</v>
-      </c>
-      <c r="B125">
-        <v>5010</v>
-      </c>
-      <c r="C125">
-        <v>0</v>
-      </c>
-      <c r="D125">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4">
-      <c r="A126">
-        <v>102</v>
-      </c>
-      <c r="B126">
-        <v>100510</v>
-      </c>
-      <c r="C126">
-        <v>0</v>
-      </c>
-      <c r="D126">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4">
-      <c r="A127">
-        <v>102</v>
-      </c>
-      <c r="B127">
-        <v>0</v>
-      </c>
-      <c r="C127">
-        <v>0</v>
-      </c>
-      <c r="D127">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4">
-      <c r="A128">
-        <v>102</v>
-      </c>
-      <c r="B128">
-        <v>0</v>
-      </c>
-      <c r="C128">
-        <v>0</v>
-      </c>
-      <c r="D128">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4">
-      <c r="A129">
-        <v>102</v>
-      </c>
-      <c r="B129">
-        <v>0</v>
-      </c>
-      <c r="C129">
-        <v>0</v>
-      </c>
-      <c r="D129">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4">
-      <c r="A130">
-        <v>102</v>
-      </c>
-      <c r="B130">
-        <v>0</v>
-      </c>
-      <c r="C130">
-        <v>0</v>
-      </c>
-      <c r="D130">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4">
-      <c r="A131">
-        <v>102</v>
-      </c>
-      <c r="B131">
-        <v>0</v>
-      </c>
-      <c r="C131">
-        <v>0</v>
-      </c>
-      <c r="D131">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4">
-      <c r="A132">
-        <v>102</v>
-      </c>
-      <c r="B132">
-        <v>0</v>
-      </c>
-      <c r="C132">
-        <v>0</v>
-      </c>
-      <c r="D132">
         <v>0</v>
       </c>
     </row>
@@ -5883,7 +5594,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
     <col min="3" max="3" width="20.5454545454545" customWidth="1"/>
@@ -5896,16 +5607,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" t="s">
         <v>68</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>69</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>70</v>
-      </c>
-      <c r="E1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="2" ht="39" spans="1:5">
@@ -5913,16 +5624,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" t="s">
         <v>72</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="3" ht="39" spans="1:5">
@@ -5930,16 +5641,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" t="s">
         <v>76</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="4" ht="39" spans="1:5">
@@ -5947,16 +5658,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" t="s">
         <v>80</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="5" ht="39" spans="1:5">
@@ -5964,16 +5675,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" t="s">
         <v>84</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" t="s">
         <v>86</v>
-      </c>
-      <c r="E5" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="6" ht="52" spans="1:5">
@@ -5981,16 +5692,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" t="s">
         <v>88</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="7" ht="39" spans="1:5">
@@ -5998,16 +5709,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" t="s">
         <v>92</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="8" ht="52" spans="1:5">
@@ -6015,16 +5726,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C8" t="s">
         <v>96</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="9" ht="52" spans="1:5">
@@ -6032,16 +5743,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" t="s">
         <v>100</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" t="s">
         <v>102</v>
-      </c>
-      <c r="E9" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="10" ht="39" spans="1:5">
@@ -6049,16 +5760,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" t="s">
         <v>104</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="11" ht="39" spans="1:5">
@@ -6066,98 +5777,81 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" t="s">
         <v>108</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" t="s">
         <v>110</v>
       </c>
-      <c r="E11" t="s">
+    </row>
+    <row r="12" ht="39" spans="1:4">
+      <c r="A12">
+        <v>101</v>
+      </c>
+      <c r="B12" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="12" ht="52" spans="1:5">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>112</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" ht="39" spans="1:5">
+      <c r="A13">
+        <v>102</v>
+      </c>
+      <c r="B13" t="s">
         <v>113</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="C13" t="s">
         <v>114</v>
       </c>
-      <c r="E12" t="s">
+      <c r="D13" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E13" t="s">
         <v>115</v>
-      </c>
-    </row>
-    <row r="13" ht="39" spans="1:4">
-      <c r="A13">
-        <v>101</v>
-      </c>
-      <c r="B13" t="s">
-        <v>116</v>
-      </c>
-      <c r="C13" t="s">
-        <v>117</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="14" ht="39" spans="1:5">
       <c r="A14">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B14" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C14" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E14" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" ht="39" spans="1:5">
       <c r="A15">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B15" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C15" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="16" ht="39" spans="1:5">
-      <c r="A16">
-        <v>104</v>
-      </c>
-      <c r="B16" t="s">
-        <v>122</v>
-      </c>
-      <c r="C16" t="s">
-        <v>119</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E16" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -395,10 +395,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -413,50 +413,6 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -477,8 +433,53 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -492,37 +493,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -537,11 +516,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -550,13 +557,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -569,13 +569,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -587,7 +581,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -599,43 +635,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -653,7 +653,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -665,43 +725,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -713,31 +737,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -749,7 +749,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -760,21 +760,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -837,8 +822,23 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -846,8 +846,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -868,145 +868,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -395,8 +395,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
@@ -416,14 +416,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -432,23 +424,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -463,7 +447,59 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -477,24 +513,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -509,22 +538,15 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -537,28 +559,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -569,7 +569,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -581,7 +581,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -593,19 +593,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -617,25 +611,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -653,19 +647,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -683,43 +677,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -737,19 +713,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -778,13 +778,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -804,17 +817,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -823,7 +841,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -842,24 +860,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -868,7 +868,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -877,7 +877,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -886,127 +886,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8410"/>
+    <workbookView windowWidth="18600" windowHeight="8120" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -395,8 +395,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
@@ -416,9 +416,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -431,17 +430,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -450,6 +451,90 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -474,91 +559,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -569,7 +569,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -581,13 +665,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -599,7 +689,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -611,13 +707,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -629,37 +737,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -671,85 +749,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -763,17 +763,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -796,8 +805,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -817,11 +826,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -840,23 +855,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -868,7 +868,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -877,136 +877,136 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1035,12 +1035,12 @@
     <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
     <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
     <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="20% - アクセント 4" xfId="7" builtinId="42"/>
+    <cellStyle name="メモ" xfId="8" builtinId="10"/>
+    <cellStyle name="パーセント" xfId="9" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="10" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="11" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="12" builtinId="9"/>
     <cellStyle name="良い" xfId="13" builtinId="26"/>
     <cellStyle name="警告文" xfId="14" builtinId="11"/>
     <cellStyle name="リンクセル" xfId="15" builtinId="24"/>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18600" windowHeight="8120" activeTab="3"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -396,8 +396,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -416,8 +416,77 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -425,6 +494,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -439,61 +515,7 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -509,30 +531,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -547,14 +546,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -569,7 +569,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -581,103 +725,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -689,67 +749,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -763,25 +763,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -806,7 +793,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -822,6 +809,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -843,20 +839,24 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -868,145 +868,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -395,10 +395,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -416,9 +416,60 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -433,45 +484,8 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -484,14 +498,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -499,8 +506,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -515,44 +546,13 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -569,19 +569,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -599,7 +689,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -611,145 +749,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -760,17 +760,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -793,7 +782,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -809,15 +798,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -839,9 +819,20 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -860,6 +851,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -868,145 +868,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -260,7 +260,7 @@
 …だったはずなのに</t>
   </si>
   <si>
-    <t>アリエス</t>
+    <t>ユウナギ</t>
   </si>
   <si>
     <t>【怠惰な守護少女】</t>
@@ -329,7 +329,7 @@
 アタシにだって良いところあるはずだから！</t>
   </si>
   <si>
-    <t>コルト</t>
+    <t>ハヤテ</t>
   </si>
   <si>
     <t>【唯心の在処】</t>
@@ -395,10 +395,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -416,35 +416,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -454,45 +425,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -507,7 +440,45 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -523,15 +494,36 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -547,16 +539,24 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -569,7 +569,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -581,7 +587,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -593,7 +617,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -605,97 +713,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -713,6 +737,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -720,36 +750,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -780,24 +780,29 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -819,20 +824,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -852,11 +846,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -868,7 +868,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -877,136 +877,136 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="C4" t="str">
         <f>INDEX(TextData!B:B,MATCH(B4,TextData!A:A))</f>
-        <v>アリエス</v>
+        <v>ユウナギ</v>
       </c>
       <c r="D4" t="str">
         <f>INDEX(TextData!C:C,MATCH(B4,TextData!A:A))</f>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="C9" t="str">
         <f>INDEX(TextData!B:B,MATCH(B9,TextData!A:A))</f>
-        <v>コルト</v>
+        <v>ハヤテ</v>
       </c>
       <c r="D9" t="str">
         <f>INDEX(TextData!C:C,MATCH(B9,TextData!A:A))</f>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="3"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="117">
   <si>
     <t>Id</t>
   </si>
@@ -206,9 +206,6 @@
   </si>
   <si>
     <t>11,21,31,2010,101010,101020</t>
-  </si>
-  <si>
-    <t>11,21,31,3010,110110,110120</t>
   </si>
   <si>
     <t>11,21,31,5010,5070,100510,100520</t>
@@ -395,10 +392,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -416,16 +413,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -440,7 +429,7 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -448,22 +437,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -478,7 +459,15 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -493,6 +482,28 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -501,8 +512,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -522,24 +534,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -553,10 +550,10 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -569,13 +566,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -593,7 +632,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -605,19 +644,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -629,127 +740,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -760,6 +757,17 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -780,11 +788,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -801,8 +807,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -822,11 +828,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -845,21 +857,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -868,7 +865,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -877,136 +874,136 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3122,7 +3119,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C71"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="44.2727272727273" style="2" customWidth="1"/>
@@ -3777,7 +3774,7 @@
         <v>101</v>
       </c>
       <c r="B62" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -3824,34 +3821,34 @@
         <v>41</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:3">
       <c r="A67">
-        <v>102</v>
-      </c>
-      <c r="B67" t="s">
-        <v>64</v>
+        <v>101</v>
+      </c>
+      <c r="B67" s="3">
+        <v>110110</v>
+      </c>
+      <c r="C67">
+        <v>-1</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>102</v>
-      </c>
-      <c r="B68">
-        <v>5070</v>
+        <v>101</v>
+      </c>
+      <c r="B68" s="3">
+        <v>110120</v>
       </c>
       <c r="C68">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
       <c r="A69">
         <v>102</v>
       </c>
-      <c r="B69">
-        <v>15090</v>
-      </c>
-      <c r="C69">
-        <v>11</v>
+      <c r="B69" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -3859,10 +3856,10 @@
         <v>102</v>
       </c>
       <c r="B70">
-        <v>405070</v>
+        <v>5070</v>
       </c>
       <c r="C70">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -3870,9 +3867,31 @@
         <v>102</v>
       </c>
       <c r="B71">
+        <v>15090</v>
+      </c>
+      <c r="C71">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72">
+        <v>102</v>
+      </c>
+      <c r="B72">
+        <v>405070</v>
+      </c>
+      <c r="C72">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73">
+        <v>102</v>
+      </c>
+      <c r="B73">
         <v>5040</v>
       </c>
-      <c r="C71">
+      <c r="C73">
         <v>41</v>
       </c>
     </row>
@@ -3899,10 +3918,10 @@
         <v>51</v>
       </c>
       <c r="C1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" t="s">
         <v>65</v>
-      </c>
-      <c r="D1" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -5607,16 +5626,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" t="s">
         <v>67</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>68</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>69</v>
-      </c>
-      <c r="E1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="2" ht="39" spans="1:5">
@@ -5624,16 +5643,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" t="s">
         <v>71</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="3" ht="39" spans="1:5">
@@ -5641,16 +5660,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" t="s">
         <v>75</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="4" ht="39" spans="1:5">
@@ -5658,16 +5677,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" t="s">
         <v>79</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="5" ht="39" spans="1:5">
@@ -5675,16 +5694,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" t="s">
         <v>83</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" t="s">
         <v>85</v>
-      </c>
-      <c r="E5" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="6" ht="52" spans="1:5">
@@ -5692,16 +5711,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" t="s">
         <v>87</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="7" ht="39" spans="1:5">
@@ -5709,16 +5728,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" t="s">
         <v>91</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="8" ht="52" spans="1:5">
@@ -5726,16 +5745,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" t="s">
         <v>95</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="9" ht="52" spans="1:5">
@@ -5743,16 +5762,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" t="s">
         <v>99</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" t="s">
         <v>101</v>
-      </c>
-      <c r="E9" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="10" ht="39" spans="1:5">
@@ -5760,16 +5779,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" t="s">
         <v>103</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="11" ht="39" spans="1:5">
@@ -5777,16 +5796,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" t="s">
         <v>107</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" t="s">
         <v>109</v>
-      </c>
-      <c r="E11" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="12" ht="39" spans="1:4">
@@ -5794,13 +5813,13 @@
         <v>101</v>
       </c>
       <c r="B12" t="s">
+        <v>110</v>
+      </c>
+      <c r="C12" t="s">
         <v>111</v>
       </c>
-      <c r="C12" t="s">
-        <v>112</v>
-      </c>
       <c r="D12" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" ht="39" spans="1:5">
@@ -5808,16 +5827,16 @@
         <v>102</v>
       </c>
       <c r="B13" t="s">
+        <v>112</v>
+      </c>
+      <c r="C13" t="s">
         <v>113</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E13" t="s">
         <v>114</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E13" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="14" ht="39" spans="1:5">
@@ -5825,16 +5844,16 @@
         <v>103</v>
       </c>
       <c r="B14" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" ht="39" spans="1:5">
@@ -5842,16 +5861,16 @@
         <v>104</v>
       </c>
       <c r="B15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C15" t="s">
+        <v>113</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15" t="s">
         <v>114</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E15" t="s">
-        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -271,7 +271,7 @@
 それが私の答えだから</t>
   </si>
   <si>
-    <t>シイナ</t>
+    <t>スノウ</t>
   </si>
   <si>
     <t>【イノセント・リメディ】</t>
@@ -392,10 +392,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -414,6 +414,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -422,22 +429,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -450,9 +457,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -474,52 +511,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -534,6 +525,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -542,18 +549,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -566,7 +566,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,7 +602,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -590,7 +620,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -602,19 +692,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -626,43 +710,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -674,79 +728,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -760,13 +760,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -789,41 +808,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -843,17 +829,31 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -865,145 +865,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="C5" t="str">
         <f>INDEX(TextData!B:B,MATCH(B5,TextData!A:A))</f>
-        <v>シイナ</v>
+        <v>スノウ</v>
       </c>
       <c r="D5" t="str">
         <f>INDEX(TextData!C:C,MATCH(B5,TextData!A:A))</f>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="3"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -394,8 +394,8 @@
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -410,6 +410,83 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -429,7 +506,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -443,6 +520,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -450,69 +535,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -525,35 +550,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -566,7 +566,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,175 +746,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -757,6 +757,45 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -771,6 +810,15 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -790,45 +838,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -843,17 +852,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -865,25 +865,25 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -892,118 +892,118 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3119,7 +3119,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C73"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="44.2727272727273" style="2" customWidth="1"/>
@@ -3155,7 +3155,7 @@
         <v>1060</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3173,52 +3173,52 @@
       <c r="A5">
         <v>1</v>
       </c>
-      <c r="B5">
-        <v>401060</v>
+      <c r="B5" s="3">
+        <v>100110</v>
       </c>
       <c r="C5">
-        <v>26</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
         <v>1</v>
       </c>
-      <c r="B6">
-        <v>1020</v>
+      <c r="B6" s="3">
+        <v>100120</v>
       </c>
       <c r="C6">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7">
-        <v>1</v>
-      </c>
-      <c r="B7" s="3">
-        <v>100110</v>
-      </c>
-      <c r="C7">
-        <v>-1</v>
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="B8" s="3">
-        <v>100120</v>
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <v>12010</v>
       </c>
       <c r="C8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9">
         <v>2</v>
       </c>
-      <c r="B9" t="s">
-        <v>54</v>
+      <c r="B9">
+        <v>12080</v>
+      </c>
+      <c r="C9">
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3226,10 +3226,10 @@
         <v>2</v>
       </c>
       <c r="B10">
-        <v>12010</v>
+        <v>12040</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -3237,62 +3237,62 @@
         <v>2</v>
       </c>
       <c r="B11">
-        <v>12080</v>
+        <v>2060</v>
       </c>
       <c r="C11">
-        <v>11</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
         <v>2</v>
       </c>
-      <c r="B12">
-        <v>12040</v>
+      <c r="B12" s="3">
+        <v>100210</v>
       </c>
       <c r="C12">
-        <v>26</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
         <v>2</v>
       </c>
-      <c r="B13">
-        <v>2060</v>
+      <c r="B13" s="3">
+        <v>100220</v>
       </c>
       <c r="C13">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14">
-        <v>2</v>
-      </c>
-      <c r="B14" s="3">
-        <v>100210</v>
-      </c>
-      <c r="C14">
-        <v>-1</v>
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>2</v>
-      </c>
-      <c r="B15" s="3">
-        <v>100220</v>
+        <v>3</v>
+      </c>
+      <c r="B15">
+        <v>3030</v>
       </c>
       <c r="C15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16">
         <v>3</v>
       </c>
-      <c r="B16" t="s">
-        <v>55</v>
+      <c r="B16">
+        <v>13080</v>
+      </c>
+      <c r="C16">
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3300,10 +3300,10 @@
         <v>3</v>
       </c>
       <c r="B17">
-        <v>3030</v>
+        <v>403010</v>
       </c>
       <c r="C17">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3311,62 +3311,62 @@
         <v>3</v>
       </c>
       <c r="B18">
-        <v>13080</v>
+        <v>3040</v>
       </c>
       <c r="C18">
-        <v>11</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
         <v>3</v>
       </c>
-      <c r="B19">
-        <v>403010</v>
+      <c r="B19" s="3">
+        <v>100310</v>
       </c>
       <c r="C19">
-        <v>26</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
         <v>3</v>
       </c>
-      <c r="B20">
-        <v>3040</v>
+      <c r="B20" s="3">
+        <v>100320</v>
       </c>
       <c r="C20">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21">
-        <v>3</v>
-      </c>
-      <c r="B21" s="3">
-        <v>100310</v>
-      </c>
-      <c r="C21">
-        <v>-1</v>
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
+        <v>4</v>
+      </c>
+      <c r="B22">
+        <v>4030</v>
+      </c>
+      <c r="C22">
         <v>3</v>
       </c>
-      <c r="B22" s="3">
-        <v>100320</v>
-      </c>
-      <c r="C22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23">
         <v>4</v>
       </c>
-      <c r="B23" t="s">
-        <v>56</v>
+      <c r="B23">
+        <v>14080</v>
+      </c>
+      <c r="C23">
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -3374,10 +3374,10 @@
         <v>4</v>
       </c>
       <c r="B24">
-        <v>4030</v>
+        <v>404030</v>
       </c>
       <c r="C24">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -3385,62 +3385,62 @@
         <v>4</v>
       </c>
       <c r="B25">
-        <v>14080</v>
+        <v>4060</v>
       </c>
       <c r="C25">
-        <v>11</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
         <v>4</v>
       </c>
-      <c r="B26">
-        <v>404030</v>
+      <c r="B26" s="3">
+        <v>100410</v>
       </c>
       <c r="C26">
-        <v>26</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
         <v>4</v>
       </c>
-      <c r="B27">
-        <v>4060</v>
+      <c r="B27" s="3">
+        <v>100420</v>
       </c>
       <c r="C27">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28">
-        <v>4</v>
-      </c>
-      <c r="B28" s="3">
-        <v>100410</v>
-      </c>
-      <c r="C28">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+      <c r="B28" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>4</v>
-      </c>
-      <c r="B29" s="3">
-        <v>100420</v>
+        <v>5</v>
+      </c>
+      <c r="B29">
+        <v>5070</v>
       </c>
       <c r="C29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30">
         <v>5</v>
       </c>
-      <c r="B30" t="s">
-        <v>57</v>
+      <c r="B30">
+        <v>15090</v>
+      </c>
+      <c r="C30">
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -3448,10 +3448,10 @@
         <v>5</v>
       </c>
       <c r="B31">
-        <v>5070</v>
+        <v>405070</v>
       </c>
       <c r="C31">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -3459,62 +3459,62 @@
         <v>5</v>
       </c>
       <c r="B32">
-        <v>15090</v>
+        <v>5040</v>
       </c>
       <c r="C32">
-        <v>11</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
         <v>5</v>
       </c>
-      <c r="B33">
-        <v>405070</v>
+      <c r="B33" s="3">
+        <v>100510</v>
       </c>
       <c r="C33">
-        <v>26</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
         <v>5</v>
       </c>
-      <c r="B34">
-        <v>5040</v>
+      <c r="B34" s="3">
+        <v>100520</v>
       </c>
       <c r="C34">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35">
-        <v>5</v>
-      </c>
-      <c r="B35" s="3">
-        <v>100510</v>
-      </c>
-      <c r="C35">
-        <v>-1</v>
+        <v>6</v>
+      </c>
+      <c r="B35" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
+        <v>6</v>
+      </c>
+      <c r="B36">
+        <v>1030</v>
+      </c>
+      <c r="C36">
         <v>5</v>
       </c>
-      <c r="B36" s="3">
-        <v>100520</v>
-      </c>
-      <c r="C36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37">
         <v>6</v>
       </c>
-      <c r="B37" t="s">
-        <v>58</v>
+      <c r="B37">
+        <v>11040</v>
+      </c>
+      <c r="C37">
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -3522,10 +3522,10 @@
         <v>6</v>
       </c>
       <c r="B38">
-        <v>1030</v>
+        <v>401030</v>
       </c>
       <c r="C38">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -3533,40 +3533,40 @@
         <v>6</v>
       </c>
       <c r="B39">
-        <v>11040</v>
+        <v>1070</v>
       </c>
       <c r="C39">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40">
-        <v>6</v>
-      </c>
-      <c r="B40">
-        <v>401030</v>
-      </c>
-      <c r="C40">
-        <v>26</v>
+        <v>7</v>
+      </c>
+      <c r="B40" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B41">
-        <v>1070</v>
+        <v>2040</v>
       </c>
       <c r="C41">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42">
         <v>7</v>
       </c>
-      <c r="B42" t="s">
-        <v>59</v>
+      <c r="B42">
+        <v>12090</v>
+      </c>
+      <c r="C42">
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -3574,10 +3574,10 @@
         <v>7</v>
       </c>
       <c r="B43">
-        <v>2040</v>
+        <v>412090</v>
       </c>
       <c r="C43">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -3585,40 +3585,40 @@
         <v>7</v>
       </c>
       <c r="B44">
-        <v>12090</v>
+        <v>2050</v>
       </c>
       <c r="C44">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
       <c r="A45">
-        <v>7</v>
-      </c>
-      <c r="B45">
-        <v>412090</v>
-      </c>
-      <c r="C45">
-        <v>26</v>
+        <v>8</v>
+      </c>
+      <c r="B45" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B46">
-        <v>2050</v>
+        <v>3070</v>
       </c>
       <c r="C46">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
       <c r="A47">
         <v>8</v>
       </c>
-      <c r="B47" t="s">
-        <v>60</v>
+      <c r="B47">
+        <v>13060</v>
+      </c>
+      <c r="C47">
+        <v>11</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -3626,10 +3626,10 @@
         <v>8</v>
       </c>
       <c r="B48">
-        <v>3070</v>
+        <v>403070</v>
       </c>
       <c r="C48">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -3637,40 +3637,40 @@
         <v>8</v>
       </c>
       <c r="B49">
-        <v>13060</v>
+        <v>3060</v>
       </c>
       <c r="C49">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
       <c r="A50">
-        <v>8</v>
-      </c>
-      <c r="B50">
-        <v>403070</v>
-      </c>
-      <c r="C50">
-        <v>26</v>
+        <v>9</v>
+      </c>
+      <c r="B50" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B51">
-        <v>3060</v>
+        <v>1050</v>
       </c>
       <c r="C51">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
       <c r="A52">
         <v>9</v>
       </c>
-      <c r="B52" t="s">
-        <v>61</v>
+      <c r="B52">
+        <v>11070</v>
+      </c>
+      <c r="C52">
+        <v>11</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -3678,10 +3678,10 @@
         <v>9</v>
       </c>
       <c r="B53">
-        <v>1050</v>
+        <v>401050</v>
       </c>
       <c r="C53">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -3689,40 +3689,40 @@
         <v>9</v>
       </c>
       <c r="B54">
-        <v>11070</v>
+        <v>1080</v>
       </c>
       <c r="C54">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
       <c r="A55">
-        <v>9</v>
-      </c>
-      <c r="B55">
-        <v>401050</v>
-      </c>
-      <c r="C55">
-        <v>26</v>
+        <v>10</v>
+      </c>
+      <c r="B55" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B56">
-        <v>1080</v>
+        <v>2030</v>
       </c>
       <c r="C56">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
       <c r="A57">
         <v>10</v>
       </c>
-      <c r="B57" t="s">
-        <v>62</v>
+      <c r="B57">
+        <v>12010</v>
+      </c>
+      <c r="C57">
+        <v>11</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -3730,10 +3730,10 @@
         <v>10</v>
       </c>
       <c r="B58">
-        <v>2030</v>
+        <v>402030</v>
       </c>
       <c r="C58">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -3741,157 +3741,113 @@
         <v>10</v>
       </c>
       <c r="B59">
-        <v>12010</v>
+        <v>2080</v>
       </c>
       <c r="C59">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
       <c r="A60">
-        <v>10</v>
-      </c>
-      <c r="B60">
-        <v>402030</v>
-      </c>
-      <c r="C60">
-        <v>26</v>
+        <v>101</v>
+      </c>
+      <c r="B60" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="B61">
-        <v>2080</v>
+        <v>13100</v>
       </c>
       <c r="C61">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
       <c r="A62">
         <v>101</v>
       </c>
-      <c r="B62" t="s">
-        <v>55</v>
+      <c r="B62">
+        <v>13080</v>
+      </c>
+      <c r="C62">
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
         <v>101</v>
       </c>
-      <c r="B63">
-        <v>13100</v>
+      <c r="B63" s="3">
+        <v>110110</v>
       </c>
       <c r="C63">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
         <v>101</v>
       </c>
-      <c r="B64">
-        <v>13080</v>
+      <c r="B64" s="3">
+        <v>110120</v>
       </c>
       <c r="C64">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
       <c r="A65">
-        <v>101</v>
-      </c>
-      <c r="B65">
-        <v>403010</v>
-      </c>
-      <c r="C65">
-        <v>26</v>
+        <v>102</v>
+      </c>
+      <c r="B65" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B66">
-        <v>3040</v>
+        <v>5070</v>
       </c>
       <c r="C66">
-        <v>41</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>101</v>
-      </c>
-      <c r="B67" s="3">
-        <v>110110</v>
+        <v>102</v>
+      </c>
+      <c r="B67">
+        <v>15090</v>
       </c>
       <c r="C67">
-        <v>-1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>101</v>
-      </c>
-      <c r="B68" s="3">
-        <v>110120</v>
+        <v>102</v>
+      </c>
+      <c r="B68">
+        <v>405070</v>
       </c>
       <c r="C68">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
       <c r="A69">
         <v>102</v>
       </c>
-      <c r="B69" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70">
-        <v>102</v>
-      </c>
-      <c r="B70">
-        <v>5070</v>
-      </c>
-      <c r="C70">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="A71">
-        <v>102</v>
-      </c>
-      <c r="B71">
-        <v>15090</v>
-      </c>
-      <c r="C71">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
-      <c r="A72">
-        <v>102</v>
-      </c>
-      <c r="B72">
-        <v>405070</v>
-      </c>
-      <c r="C72">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73">
-        <v>102</v>
-      </c>
-      <c r="B73">
+      <c r="B69">
         <v>5040</v>
       </c>
-      <c r="C73">
+      <c r="C69">
         <v>41</v>
       </c>
     </row>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -393,9 +393,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -415,30 +415,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -454,9 +438,24 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -468,23 +467,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -498,9 +482,47 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -514,20 +536,13 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -535,23 +550,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -566,19 +566,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -590,19 +584,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -614,13 +602,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -638,13 +632,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -668,7 +680,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -680,19 +722,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -710,43 +740,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -757,30 +757,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -799,17 +775,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -840,11 +816,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -857,6 +831,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -865,145 +865,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3119,7 +3119,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C69"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="44.2727272727273" style="2" customWidth="1"/>
@@ -3207,7 +3207,7 @@
         <v>12010</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -3225,629 +3225,541 @@
       <c r="A10">
         <v>2</v>
       </c>
-      <c r="B10">
-        <v>12040</v>
+      <c r="B10" s="3">
+        <v>100210</v>
       </c>
       <c r="C10">
-        <v>26</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
         <v>2</v>
       </c>
-      <c r="B11">
-        <v>2060</v>
+      <c r="B11" s="3">
+        <v>100220</v>
       </c>
       <c r="C11">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12">
-        <v>2</v>
-      </c>
-      <c r="B12" s="3">
-        <v>100210</v>
-      </c>
-      <c r="C12">
-        <v>-1</v>
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>2</v>
-      </c>
-      <c r="B13" s="3">
-        <v>100220</v>
+        <v>3</v>
+      </c>
+      <c r="B13">
+        <v>3030</v>
       </c>
       <c r="C13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14">
         <v>3</v>
       </c>
-      <c r="B14" t="s">
-        <v>55</v>
+      <c r="B14">
+        <v>13080</v>
+      </c>
+      <c r="C14">
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
         <v>3</v>
       </c>
-      <c r="B15">
-        <v>3030</v>
+      <c r="B15" s="3">
+        <v>100310</v>
       </c>
       <c r="C15">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
         <v>3</v>
       </c>
-      <c r="B16">
-        <v>13080</v>
+      <c r="B16" s="3">
+        <v>100320</v>
       </c>
       <c r="C16">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17">
-        <v>3</v>
-      </c>
-      <c r="B17">
-        <v>403010</v>
-      </c>
-      <c r="C17">
-        <v>26</v>
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B18">
-        <v>3040</v>
+        <v>4030</v>
       </c>
       <c r="C18">
-        <v>41</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>3</v>
-      </c>
-      <c r="B19" s="3">
-        <v>100310</v>
+        <v>4</v>
+      </c>
+      <c r="B19">
+        <v>14080</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B20" s="3">
-        <v>100320</v>
+        <v>100410</v>
       </c>
       <c r="C20">
         <v>-1</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:3">
       <c r="A21">
         <v>4</v>
       </c>
-      <c r="B21" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="B21" s="3">
+        <v>100420</v>
+      </c>
+      <c r="C21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22">
-        <v>4</v>
-      </c>
-      <c r="B22">
-        <v>4030</v>
-      </c>
-      <c r="C22">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="B22" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B23">
-        <v>14080</v>
+        <v>5070</v>
       </c>
       <c r="C23">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B24">
-        <v>404030</v>
+        <v>15090</v>
       </c>
       <c r="C24">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>4</v>
-      </c>
-      <c r="B25">
-        <v>4060</v>
+        <v>5</v>
+      </c>
+      <c r="B25" s="3">
+        <v>100510</v>
       </c>
       <c r="C25">
-        <v>41</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B26" s="3">
-        <v>100410</v>
+        <v>100520</v>
       </c>
       <c r="C26">
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:2">
       <c r="A27">
-        <v>4</v>
-      </c>
-      <c r="B27" s="3">
-        <v>100420</v>
-      </c>
-      <c r="C27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
+        <v>6</v>
+      </c>
+      <c r="B27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28">
+        <v>6</v>
+      </c>
+      <c r="B28">
+        <v>1030</v>
+      </c>
+      <c r="C28">
         <v>5</v>
-      </c>
-      <c r="B28" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B29">
-        <v>5070</v>
+        <v>11040</v>
       </c>
       <c r="C29">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B30">
-        <v>15090</v>
+        <v>401030</v>
       </c>
       <c r="C30">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B31">
-        <v>405070</v>
+        <v>1070</v>
       </c>
       <c r="C31">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32">
-        <v>5</v>
-      </c>
-      <c r="B32">
-        <v>5040</v>
-      </c>
-      <c r="C32">
-        <v>41</v>
+        <v>7</v>
+      </c>
+      <c r="B32" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
+        <v>7</v>
+      </c>
+      <c r="B33">
+        <v>2040</v>
+      </c>
+      <c r="C33">
         <v>5</v>
-      </c>
-      <c r="B33" s="3">
-        <v>100510</v>
-      </c>
-      <c r="C33">
-        <v>-1</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>5</v>
-      </c>
-      <c r="B34" s="3">
-        <v>100520</v>
+        <v>7</v>
+      </c>
+      <c r="B34">
+        <v>12090</v>
       </c>
       <c r="C34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35">
-        <v>6</v>
-      </c>
-      <c r="B35" t="s">
-        <v>58</v>
+        <v>7</v>
+      </c>
+      <c r="B35">
+        <v>412090</v>
+      </c>
+      <c r="C35">
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B36">
-        <v>1030</v>
+        <v>2050</v>
       </c>
       <c r="C36">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37">
-        <v>6</v>
-      </c>
-      <c r="B37">
-        <v>11040</v>
-      </c>
-      <c r="C37">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="B37" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B38">
-        <v>401030</v>
+        <v>3070</v>
       </c>
       <c r="C38">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B39">
-        <v>1070</v>
+        <v>13060</v>
       </c>
       <c r="C39">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40">
-        <v>7</v>
-      </c>
-      <c r="B40" t="s">
-        <v>59</v>
+        <v>8</v>
+      </c>
+      <c r="B40">
+        <v>403070</v>
+      </c>
+      <c r="C40">
+        <v>26</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B41">
-        <v>2040</v>
+        <v>3060</v>
       </c>
       <c r="C41">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
       <c r="A42">
-        <v>7</v>
-      </c>
-      <c r="B42">
-        <v>12090</v>
-      </c>
-      <c r="C42">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="B42" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B43">
-        <v>412090</v>
+        <v>1050</v>
       </c>
       <c r="C43">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B44">
-        <v>2050</v>
+        <v>11070</v>
       </c>
       <c r="C44">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
       <c r="A45">
-        <v>8</v>
-      </c>
-      <c r="B45" t="s">
-        <v>60</v>
+        <v>9</v>
+      </c>
+      <c r="B45">
+        <v>401050</v>
+      </c>
+      <c r="C45">
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B46">
-        <v>3070</v>
+        <v>1080</v>
       </c>
       <c r="C46">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
       <c r="A47">
-        <v>8</v>
-      </c>
-      <c r="B47">
-        <v>13060</v>
-      </c>
-      <c r="C47">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="B47" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B48">
-        <v>403070</v>
+        <v>2030</v>
       </c>
       <c r="C48">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B49">
-        <v>3060</v>
+        <v>12010</v>
       </c>
       <c r="C49">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50">
-        <v>9</v>
-      </c>
-      <c r="B50" t="s">
-        <v>61</v>
+        <v>10</v>
+      </c>
+      <c r="B50">
+        <v>402030</v>
+      </c>
+      <c r="C50">
+        <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B51">
-        <v>1050</v>
+        <v>2080</v>
       </c>
       <c r="C51">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
       <c r="A52">
-        <v>9</v>
-      </c>
-      <c r="B52">
-        <v>11070</v>
-      </c>
-      <c r="C52">
-        <v>11</v>
+        <v>101</v>
+      </c>
+      <c r="B52" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>9</v>
+        <v>101</v>
       </c>
       <c r="B53">
-        <v>401050</v>
+        <v>13100</v>
       </c>
       <c r="C53">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>9</v>
+        <v>101</v>
       </c>
       <c r="B54">
-        <v>1080</v>
+        <v>13080</v>
       </c>
       <c r="C54">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
       <c r="A55">
-        <v>10</v>
-      </c>
-      <c r="B55" t="s">
-        <v>62</v>
+        <v>101</v>
+      </c>
+      <c r="B55" s="3">
+        <v>110110</v>
+      </c>
+      <c r="C55">
+        <v>-1</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>10</v>
-      </c>
-      <c r="B56">
-        <v>2030</v>
+        <v>101</v>
+      </c>
+      <c r="B56" s="3">
+        <v>110120</v>
       </c>
       <c r="C56">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
       <c r="A57">
-        <v>10</v>
-      </c>
-      <c r="B57">
-        <v>12010</v>
-      </c>
-      <c r="C57">
-        <v>11</v>
+        <v>102</v>
+      </c>
+      <c r="B57" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="B58">
-        <v>402030</v>
+        <v>5070</v>
       </c>
       <c r="C58">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="B59">
-        <v>2080</v>
+        <v>15090</v>
       </c>
       <c r="C59">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
       <c r="A60">
-        <v>101</v>
-      </c>
-      <c r="B60" t="s">
-        <v>55</v>
+        <v>102</v>
+      </c>
+      <c r="B60">
+        <v>405070</v>
+      </c>
+      <c r="C60">
+        <v>26</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B61">
-        <v>13100</v>
+        <v>5040</v>
       </c>
       <c r="C61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62">
-        <v>101</v>
-      </c>
-      <c r="B62">
-        <v>13080</v>
-      </c>
-      <c r="C62">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63">
-        <v>101</v>
-      </c>
-      <c r="B63" s="3">
-        <v>110110</v>
-      </c>
-      <c r="C63">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64">
-        <v>101</v>
-      </c>
-      <c r="B64" s="3">
-        <v>110120</v>
-      </c>
-      <c r="C64">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65">
-        <v>102</v>
-      </c>
-      <c r="B65" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66">
-        <v>102</v>
-      </c>
-      <c r="B66">
-        <v>5070</v>
-      </c>
-      <c r="C66">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67">
-        <v>102</v>
-      </c>
-      <c r="B67">
-        <v>15090</v>
-      </c>
-      <c r="C67">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68">
-        <v>102</v>
-      </c>
-      <c r="B68">
-        <v>405070</v>
-      </c>
-      <c r="C68">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69">
-        <v>102</v>
-      </c>
-      <c r="B69">
-        <v>5040</v>
-      </c>
-      <c r="C69">
         <v>41</v>
       </c>
     </row>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -284,7 +284,7 @@
     <t>もう終わりにしたいんです</t>
   </si>
   <si>
-    <t>レダ</t>
+    <t>フィリーネ</t>
   </si>
   <si>
     <t>【Self-sacrifice】</t>
@@ -312,7 +312,7 @@
 結局何も変わらないじゃないか…</t>
   </si>
   <si>
-    <t>セファル</t>
+    <t>リーゼロッテ</t>
   </si>
   <si>
     <t>【奇跡の乙女】</t>
@@ -393,9 +393,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -415,6 +415,97 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -429,37 +520,6 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -467,15 +527,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -488,47 +542,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -536,22 +551,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -566,7 +566,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,13 +632,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -596,115 +716,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -722,31 +734,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -760,17 +760,50 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -794,40 +827,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -842,21 +857,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -865,145 +865,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="C6" t="str">
         <f>INDEX(TextData!B:B,MATCH(B6,TextData!A:A))</f>
-        <v>レダ</v>
+        <v>フィリーネ</v>
       </c>
       <c r="D6" t="str">
         <f>INDEX(TextData!C:C,MATCH(B6,TextData!A:A))</f>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="C8" t="str">
         <f>INDEX(TextData!B:B,MATCH(B8,TextData!A:A))</f>
-        <v>セファル</v>
+        <v>リーゼロッテ</v>
       </c>
       <c r="D8" t="str">
         <f>INDEX(TextData!C:C,MATCH(B8,TextData!A:A))</f>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="3"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -415,7 +415,23 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -423,36 +439,12 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -468,10 +460,42 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -483,7 +507,29 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -504,54 +550,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -563,6 +563,18 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -578,7 +590,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -590,25 +650,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -620,19 +662,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -644,43 +680,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -693,24 +693,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -734,7 +716,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -746,7 +746,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -760,50 +760,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -827,7 +790,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -847,13 +810,50 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -865,7 +865,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -874,136 +874,136 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -392,10 +392,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -413,7 +413,42 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -421,8 +456,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -438,15 +489,16 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -460,9 +512,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -470,14 +528,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -492,59 +543,8 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -566,7 +566,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,19 +656,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
  